--- a/packages/server/src/arpa_reporter/data/treasury/project519521BulkUpload.xlsx
+++ b/packages/server/src/arpa_reporter/data/treasury/project519521BulkUpload.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29602"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mac\Home\Documents\Projects\arpa-reporter\packages\server\src\arpa_reporter\data\treasury\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kgu82\Desktop\SLFRFBulkUploadTemplates\SLFRFBulkUploadTemplates\SLFRFBulkUploadTemplates\SLFRFBulkUploadTemplates\Quarter 4 2025 Project Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC92684-4DB8-4010-8DA8-D7092DF02DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{9E5C7303-8CBB-4B5C-9D34-9FDD53FDA4A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{855FE8E0-F3E6-4B32-8215-04694FAD2AE3}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22875" windowHeight="13141" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -703,7 +703,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -774,7 +774,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -784,6 +784,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -928,7 +934,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1163,7 +1169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BE1000"/>
-  <sheetFormatPr defaultColWidth="23.375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="23.375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="7" width="23.375" style="2"/>
     <col min="8" max="9" width="35.5" style="2" customWidth="1"/>
@@ -1172,7 +1178,7 @@
     <col min="58" max="16384" width="23.375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:57" ht="13.15">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -1231,7 +1237,7 @@
       <c r="BD1" s="4"/>
       <c r="BE1" s="4"/>
     </row>
-    <row r="2" spans="1:57" ht="38.25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:57" ht="39.6">
       <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
@@ -1290,7 +1296,7 @@
       <c r="BD2" s="4"/>
       <c r="BE2" s="4"/>
     </row>
-    <row r="3" spans="1:57" ht="213.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:57" ht="213.95" customHeight="1">
       <c r="A3" s="17" t="s">
         <v>2</v>
       </c>
@@ -1349,7 +1355,7 @@
       <c r="BD3" s="4"/>
       <c r="BE3" s="4"/>
     </row>
-    <row r="4" spans="1:57" s="4" customFormat="1" ht="70.7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:57" s="4" customFormat="1" ht="70.7" customHeight="1">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
@@ -1522,7 +1528,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:57" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:57" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>60</v>
       </c>
@@ -1695,7 +1701,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:57" ht="229.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:57" ht="237.6">
       <c r="A6" s="8" t="s">
         <v>64</v>
       </c>
@@ -1868,7 +1874,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:57" s="9" customFormat="1" ht="178.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:57" s="9" customFormat="1" ht="184.9">
       <c r="A7" s="8" t="s">
         <v>121</v>
       </c>
@@ -2041,7 +2047,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="8" spans="1:57" ht="96.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:57" ht="96.95" customHeight="1">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -2065,7 +2071,7 @@
       <c r="BD8" s="4"/>
       <c r="BE8" s="4"/>
     </row>
-    <row r="9" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:57" ht="13.15">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -2089,7 +2095,7 @@
       <c r="BD9" s="4"/>
       <c r="BE9" s="4"/>
     </row>
-    <row r="10" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:57" ht="13.15">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -2113,7 +2119,7 @@
       <c r="BD10" s="4"/>
       <c r="BE10" s="4"/>
     </row>
-    <row r="11" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:57" ht="13.15">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -2137,7 +2143,7 @@
       <c r="BD11" s="4"/>
       <c r="BE11" s="4"/>
     </row>
-    <row r="12" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:57" ht="13.15">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -2161,7 +2167,7 @@
       <c r="BD12" s="4"/>
       <c r="BE12" s="4"/>
     </row>
-    <row r="13" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:57" ht="13.15">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -2185,7 +2191,7 @@
       <c r="BD13" s="4"/>
       <c r="BE13" s="4"/>
     </row>
-    <row r="14" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:57" ht="13.15">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -2209,7 +2215,7 @@
       <c r="BD14" s="4"/>
       <c r="BE14" s="4"/>
     </row>
-    <row r="15" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:57" ht="13.15">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -2233,7 +2239,7 @@
       <c r="BD15" s="4"/>
       <c r="BE15" s="4"/>
     </row>
-    <row r="16" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:57" ht="13.15">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -2257,7 +2263,7 @@
       <c r="BD16" s="4"/>
       <c r="BE16" s="4"/>
     </row>
-    <row r="17" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:57" ht="13.15">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -2281,7 +2287,7 @@
       <c r="BD17" s="4"/>
       <c r="BE17" s="4"/>
     </row>
-    <row r="18" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:57" ht="13.15">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -2305,7 +2311,7 @@
       <c r="BD18" s="4"/>
       <c r="BE18" s="4"/>
     </row>
-    <row r="19" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:57" ht="13.15">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -2329,7 +2335,7 @@
       <c r="BD19" s="4"/>
       <c r="BE19" s="4"/>
     </row>
-    <row r="20" spans="1:57" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:57" ht="13.15">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -2353,7 +2359,7 @@
       <c r="BD20" s="4"/>
       <c r="BE20" s="4"/>
     </row>
-    <row r="21" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:57" ht="15.95" customHeight="1">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -2377,7 +2383,7 @@
       <c r="BD21" s="4"/>
       <c r="BE21" s="4"/>
     </row>
-    <row r="22" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:57" ht="15.95" customHeight="1">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -2401,7 +2407,7 @@
       <c r="BD22" s="4"/>
       <c r="BE22" s="4"/>
     </row>
-    <row r="23" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:57" ht="15.95" customHeight="1">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -2425,7 +2431,7 @@
       <c r="BD23" s="4"/>
       <c r="BE23" s="4"/>
     </row>
-    <row r="24" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:57" ht="15.95" customHeight="1">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -2449,7 +2455,7 @@
       <c r="BD24" s="4"/>
       <c r="BE24" s="4"/>
     </row>
-    <row r="25" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:57" ht="15.95" customHeight="1">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -2473,7 +2479,7 @@
       <c r="BD25" s="4"/>
       <c r="BE25" s="4"/>
     </row>
-    <row r="26" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:57" ht="15.95" customHeight="1">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -2497,7 +2503,7 @@
       <c r="BD26" s="4"/>
       <c r="BE26" s="4"/>
     </row>
-    <row r="27" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:57" ht="15.95" customHeight="1">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -2521,7 +2527,7 @@
       <c r="BD27" s="4"/>
       <c r="BE27" s="4"/>
     </row>
-    <row r="28" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:57" ht="15.95" customHeight="1">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -2545,7 +2551,7 @@
       <c r="BD28" s="4"/>
       <c r="BE28" s="4"/>
     </row>
-    <row r="29" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:57" ht="15.95" customHeight="1">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -2569,7 +2575,7 @@
       <c r="BD29" s="4"/>
       <c r="BE29" s="4"/>
     </row>
-    <row r="30" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:57" ht="15.95" customHeight="1">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -2593,7 +2599,7 @@
       <c r="BD30" s="4"/>
       <c r="BE30" s="4"/>
     </row>
-    <row r="31" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:57" ht="15.95" customHeight="1">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -2617,7 +2623,7 @@
       <c r="BD31" s="4"/>
       <c r="BE31" s="4"/>
     </row>
-    <row r="32" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:57" ht="15.95" customHeight="1">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -2641,7 +2647,7 @@
       <c r="BD32" s="4"/>
       <c r="BE32" s="4"/>
     </row>
-    <row r="33" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:57" ht="15.95" customHeight="1">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -2665,7 +2671,7 @@
       <c r="BD33" s="4"/>
       <c r="BE33" s="4"/>
     </row>
-    <row r="34" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:57" ht="15.95" customHeight="1">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -2689,7 +2695,7 @@
       <c r="BD34" s="4"/>
       <c r="BE34" s="4"/>
     </row>
-    <row r="35" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:57" ht="15.95" customHeight="1">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -2713,7 +2719,7 @@
       <c r="BD35" s="4"/>
       <c r="BE35" s="4"/>
     </row>
-    <row r="36" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:57" ht="15.95" customHeight="1">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -2737,7 +2743,7 @@
       <c r="BD36" s="4"/>
       <c r="BE36" s="4"/>
     </row>
-    <row r="37" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:57" ht="15.95" customHeight="1">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -2761,7 +2767,7 @@
       <c r="BD37" s="4"/>
       <c r="BE37" s="4"/>
     </row>
-    <row r="38" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:57" ht="15.95" customHeight="1">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -2785,7 +2791,7 @@
       <c r="BD38" s="4"/>
       <c r="BE38" s="4"/>
     </row>
-    <row r="39" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:57" ht="15.95" customHeight="1">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -2809,7 +2815,7 @@
       <c r="BD39" s="4"/>
       <c r="BE39" s="4"/>
     </row>
-    <row r="40" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:57" ht="15.95" customHeight="1">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -2833,7 +2839,7 @@
       <c r="BD40" s="4"/>
       <c r="BE40" s="4"/>
     </row>
-    <row r="41" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:57" ht="15.95" customHeight="1">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -2857,7 +2863,7 @@
       <c r="BD41" s="4"/>
       <c r="BE41" s="4"/>
     </row>
-    <row r="42" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:57" ht="15.95" customHeight="1">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -2881,7 +2887,7 @@
       <c r="BD42" s="4"/>
       <c r="BE42" s="4"/>
     </row>
-    <row r="43" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:57" ht="15.95" customHeight="1">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -2905,7 +2911,7 @@
       <c r="BD43" s="4"/>
       <c r="BE43" s="4"/>
     </row>
-    <row r="44" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:57" ht="15.95" customHeight="1">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -2929,7 +2935,7 @@
       <c r="BD44" s="4"/>
       <c r="BE44" s="4"/>
     </row>
-    <row r="45" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:57" ht="15.95" customHeight="1">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -2953,7 +2959,7 @@
       <c r="BD45" s="4"/>
       <c r="BE45" s="4"/>
     </row>
-    <row r="46" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:57" ht="15.95" customHeight="1">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -2977,7 +2983,7 @@
       <c r="BD46" s="4"/>
       <c r="BE46" s="4"/>
     </row>
-    <row r="47" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:57" ht="15.95" customHeight="1">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -3001,7 +3007,7 @@
       <c r="BD47" s="4"/>
       <c r="BE47" s="4"/>
     </row>
-    <row r="48" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:57" ht="15.95" customHeight="1">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -3025,7 +3031,7 @@
       <c r="BD48" s="4"/>
       <c r="BE48" s="4"/>
     </row>
-    <row r="49" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:57" ht="15.95" customHeight="1">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -3049,7 +3055,7 @@
       <c r="BD49" s="4"/>
       <c r="BE49" s="4"/>
     </row>
-    <row r="50" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:57" ht="15.95" customHeight="1">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -3073,7 +3079,7 @@
       <c r="BD50" s="4"/>
       <c r="BE50" s="4"/>
     </row>
-    <row r="51" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:57" ht="15.95" customHeight="1">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -3097,7 +3103,7 @@
       <c r="BD51" s="4"/>
       <c r="BE51" s="4"/>
     </row>
-    <row r="52" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:57" ht="15.95" customHeight="1">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -3121,7 +3127,7 @@
       <c r="BD52" s="4"/>
       <c r="BE52" s="4"/>
     </row>
-    <row r="53" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:57" ht="15.95" customHeight="1">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -3145,7 +3151,7 @@
       <c r="BD53" s="4"/>
       <c r="BE53" s="4"/>
     </row>
-    <row r="54" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:57" ht="15.95" customHeight="1">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -3169,7 +3175,7 @@
       <c r="BD54" s="4"/>
       <c r="BE54" s="4"/>
     </row>
-    <row r="55" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:57" ht="15.95" customHeight="1">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -3193,7 +3199,7 @@
       <c r="BD55" s="4"/>
       <c r="BE55" s="4"/>
     </row>
-    <row r="56" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:57" ht="15.95" customHeight="1">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -3217,7 +3223,7 @@
       <c r="BD56" s="4"/>
       <c r="BE56" s="4"/>
     </row>
-    <row r="57" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:57" ht="15.95" customHeight="1">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -3241,7 +3247,7 @@
       <c r="BD57" s="4"/>
       <c r="BE57" s="4"/>
     </row>
-    <row r="58" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:57" ht="15.95" customHeight="1">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -3265,7 +3271,7 @@
       <c r="BD58" s="4"/>
       <c r="BE58" s="4"/>
     </row>
-    <row r="59" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:57" ht="15.95" customHeight="1">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -3289,7 +3295,7 @@
       <c r="BD59" s="4"/>
       <c r="BE59" s="4"/>
     </row>
-    <row r="60" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:57" ht="15.95" customHeight="1">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -3313,7 +3319,7 @@
       <c r="BD60" s="4"/>
       <c r="BE60" s="4"/>
     </row>
-    <row r="61" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:57" ht="15.95" customHeight="1">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -3337,7 +3343,7 @@
       <c r="BD61" s="4"/>
       <c r="BE61" s="4"/>
     </row>
-    <row r="62" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:57" ht="15.95" customHeight="1">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -3361,7 +3367,7 @@
       <c r="BD62" s="4"/>
       <c r="BE62" s="4"/>
     </row>
-    <row r="63" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:57" ht="15.95" customHeight="1">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -3385,7 +3391,7 @@
       <c r="BD63" s="4"/>
       <c r="BE63" s="4"/>
     </row>
-    <row r="64" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:57" ht="15.95" customHeight="1">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -3409,7 +3415,7 @@
       <c r="BD64" s="4"/>
       <c r="BE64" s="4"/>
     </row>
-    <row r="65" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:57" ht="15.95" customHeight="1">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -3433,7 +3439,7 @@
       <c r="BD65" s="4"/>
       <c r="BE65" s="4"/>
     </row>
-    <row r="66" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:57" ht="15.95" customHeight="1">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -3457,7 +3463,7 @@
       <c r="BD66" s="4"/>
       <c r="BE66" s="4"/>
     </row>
-    <row r="67" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:57" ht="15.95" customHeight="1">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -3481,7 +3487,7 @@
       <c r="BD67" s="4"/>
       <c r="BE67" s="4"/>
     </row>
-    <row r="68" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:57" ht="15.95" customHeight="1">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -3505,7 +3511,7 @@
       <c r="BD68" s="4"/>
       <c r="BE68" s="4"/>
     </row>
-    <row r="69" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:57" ht="15.95" customHeight="1">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -3529,7 +3535,7 @@
       <c r="BD69" s="4"/>
       <c r="BE69" s="4"/>
     </row>
-    <row r="70" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:57" ht="15.95" customHeight="1">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -3553,7 +3559,7 @@
       <c r="BD70" s="4"/>
       <c r="BE70" s="4"/>
     </row>
-    <row r="71" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:57" ht="15.95" customHeight="1">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -3577,7 +3583,7 @@
       <c r="BD71" s="4"/>
       <c r="BE71" s="4"/>
     </row>
-    <row r="72" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:57" ht="15.95" customHeight="1">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -3601,7 +3607,7 @@
       <c r="BD72" s="4"/>
       <c r="BE72" s="4"/>
     </row>
-    <row r="73" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:57" ht="15.95" customHeight="1">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -3625,7 +3631,7 @@
       <c r="BD73" s="4"/>
       <c r="BE73" s="4"/>
     </row>
-    <row r="74" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:57" ht="15.95" customHeight="1">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -3649,7 +3655,7 @@
       <c r="BD74" s="4"/>
       <c r="BE74" s="4"/>
     </row>
-    <row r="75" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:57" ht="15.95" customHeight="1">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -3673,7 +3679,7 @@
       <c r="BD75" s="4"/>
       <c r="BE75" s="4"/>
     </row>
-    <row r="76" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:57" ht="15.95" customHeight="1">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -3697,7 +3703,7 @@
       <c r="BD76" s="4"/>
       <c r="BE76" s="4"/>
     </row>
-    <row r="77" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:57" ht="15.95" customHeight="1">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -3721,7 +3727,7 @@
       <c r="BD77" s="4"/>
       <c r="BE77" s="4"/>
     </row>
-    <row r="78" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:57" ht="15.95" customHeight="1">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -3745,7 +3751,7 @@
       <c r="BD78" s="4"/>
       <c r="BE78" s="4"/>
     </row>
-    <row r="79" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:57" ht="15.95" customHeight="1">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -3769,7 +3775,7 @@
       <c r="BD79" s="4"/>
       <c r="BE79" s="4"/>
     </row>
-    <row r="80" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:57" ht="15.95" customHeight="1">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -3793,7 +3799,7 @@
       <c r="BD80" s="4"/>
       <c r="BE80" s="4"/>
     </row>
-    <row r="81" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:57" ht="15.95" customHeight="1">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -3817,7 +3823,7 @@
       <c r="BD81" s="4"/>
       <c r="BE81" s="4"/>
     </row>
-    <row r="82" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:57" ht="15.95" customHeight="1">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -3841,7 +3847,7 @@
       <c r="BD82" s="4"/>
       <c r="BE82" s="4"/>
     </row>
-    <row r="83" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:57" ht="15.95" customHeight="1">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -3865,7 +3871,7 @@
       <c r="BD83" s="4"/>
       <c r="BE83" s="4"/>
     </row>
-    <row r="84" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:57" ht="15.95" customHeight="1">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -3889,7 +3895,7 @@
       <c r="BD84" s="4"/>
       <c r="BE84" s="4"/>
     </row>
-    <row r="85" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:57" ht="15.95" customHeight="1">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -3913,7 +3919,7 @@
       <c r="BD85" s="4"/>
       <c r="BE85" s="4"/>
     </row>
-    <row r="86" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:57" ht="15.95" customHeight="1">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -3937,7 +3943,7 @@
       <c r="BD86" s="4"/>
       <c r="BE86" s="4"/>
     </row>
-    <row r="87" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:57" ht="15.95" customHeight="1">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -3961,7 +3967,7 @@
       <c r="BD87" s="4"/>
       <c r="BE87" s="4"/>
     </row>
-    <row r="88" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:57" ht="15.95" customHeight="1">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -3985,7 +3991,7 @@
       <c r="BD88" s="4"/>
       <c r="BE88" s="4"/>
     </row>
-    <row r="89" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:57" ht="15.95" customHeight="1">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -4009,7 +4015,7 @@
       <c r="BD89" s="4"/>
       <c r="BE89" s="4"/>
     </row>
-    <row r="90" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:57" ht="15.95" customHeight="1">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -4033,7 +4039,7 @@
       <c r="BD90" s="4"/>
       <c r="BE90" s="4"/>
     </row>
-    <row r="91" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:57" ht="15.95" customHeight="1">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -4057,7 +4063,7 @@
       <c r="BD91" s="4"/>
       <c r="BE91" s="4"/>
     </row>
-    <row r="92" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:57" ht="15.95" customHeight="1">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -4081,7 +4087,7 @@
       <c r="BD92" s="4"/>
       <c r="BE92" s="4"/>
     </row>
-    <row r="93" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:57" ht="15.95" customHeight="1">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -4105,7 +4111,7 @@
       <c r="BD93" s="4"/>
       <c r="BE93" s="4"/>
     </row>
-    <row r="94" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:57" ht="15.95" customHeight="1">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -4129,7 +4135,7 @@
       <c r="BD94" s="4"/>
       <c r="BE94" s="4"/>
     </row>
-    <row r="95" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:57" ht="15.95" customHeight="1">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -4153,7 +4159,7 @@
       <c r="BD95" s="4"/>
       <c r="BE95" s="4"/>
     </row>
-    <row r="96" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:57" ht="15.95" customHeight="1">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -4177,7 +4183,7 @@
       <c r="BD96" s="4"/>
       <c r="BE96" s="4"/>
     </row>
-    <row r="97" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:57" ht="15.95" customHeight="1">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -4201,7 +4207,7 @@
       <c r="BD97" s="4"/>
       <c r="BE97" s="4"/>
     </row>
-    <row r="98" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:57" ht="15.95" customHeight="1">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -4225,7 +4231,7 @@
       <c r="BD98" s="4"/>
       <c r="BE98" s="4"/>
     </row>
-    <row r="99" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:57" ht="15.95" customHeight="1">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -4249,7 +4255,7 @@
       <c r="BD99" s="4"/>
       <c r="BE99" s="4"/>
     </row>
-    <row r="100" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:57" ht="15.95" customHeight="1">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -4273,7 +4279,7 @@
       <c r="BD100" s="4"/>
       <c r="BE100" s="4"/>
     </row>
-    <row r="101" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:57" ht="15.95" customHeight="1">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -4297,7 +4303,7 @@
       <c r="BD101" s="4"/>
       <c r="BE101" s="4"/>
     </row>
-    <row r="102" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:57" ht="15.95" customHeight="1">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -4321,7 +4327,7 @@
       <c r="BD102" s="4"/>
       <c r="BE102" s="4"/>
     </row>
-    <row r="103" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:57" ht="15.95" customHeight="1">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -4345,7 +4351,7 @@
       <c r="BD103" s="4"/>
       <c r="BE103" s="4"/>
     </row>
-    <row r="104" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:57" ht="15.95" customHeight="1">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -4369,7 +4375,7 @@
       <c r="BD104" s="4"/>
       <c r="BE104" s="4"/>
     </row>
-    <row r="105" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:57" ht="15.95" customHeight="1">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -4393,7 +4399,7 @@
       <c r="BD105" s="4"/>
       <c r="BE105" s="4"/>
     </row>
-    <row r="106" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:57" ht="15.95" customHeight="1">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -4417,7 +4423,7 @@
       <c r="BD106" s="4"/>
       <c r="BE106" s="4"/>
     </row>
-    <row r="107" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:57" ht="15.95" customHeight="1">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -4441,7 +4447,7 @@
       <c r="BD107" s="4"/>
       <c r="BE107" s="4"/>
     </row>
-    <row r="108" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:57" ht="15.95" customHeight="1">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -4465,7 +4471,7 @@
       <c r="BD108" s="4"/>
       <c r="BE108" s="4"/>
     </row>
-    <row r="109" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:57" ht="15.95" customHeight="1">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -4489,7 +4495,7 @@
       <c r="BD109" s="4"/>
       <c r="BE109" s="4"/>
     </row>
-    <row r="110" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:57" ht="15.95" customHeight="1">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -4513,7 +4519,7 @@
       <c r="BD110" s="4"/>
       <c r="BE110" s="4"/>
     </row>
-    <row r="111" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:57" ht="15.95" customHeight="1">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -4537,7 +4543,7 @@
       <c r="BD111" s="4"/>
       <c r="BE111" s="4"/>
     </row>
-    <row r="112" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:57" ht="15.95" customHeight="1">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -4561,7 +4567,7 @@
       <c r="BD112" s="4"/>
       <c r="BE112" s="4"/>
     </row>
-    <row r="113" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:57" ht="15.95" customHeight="1">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -4585,7 +4591,7 @@
       <c r="BD113" s="4"/>
       <c r="BE113" s="4"/>
     </row>
-    <row r="114" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:57" ht="15.95" customHeight="1">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -4609,7 +4615,7 @@
       <c r="BD114" s="4"/>
       <c r="BE114" s="4"/>
     </row>
-    <row r="115" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:57" ht="15.95" customHeight="1">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -4633,7 +4639,7 @@
       <c r="BD115" s="4"/>
       <c r="BE115" s="4"/>
     </row>
-    <row r="116" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:57" ht="15.95" customHeight="1">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -4657,7 +4663,7 @@
       <c r="BD116" s="4"/>
       <c r="BE116" s="4"/>
     </row>
-    <row r="117" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:57" ht="15.95" customHeight="1">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -4681,7 +4687,7 @@
       <c r="BD117" s="4"/>
       <c r="BE117" s="4"/>
     </row>
-    <row r="118" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:57" ht="15.95" customHeight="1">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -4705,7 +4711,7 @@
       <c r="BD118" s="4"/>
       <c r="BE118" s="4"/>
     </row>
-    <row r="119" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:57" ht="15.95" customHeight="1">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -4729,7 +4735,7 @@
       <c r="BD119" s="4"/>
       <c r="BE119" s="4"/>
     </row>
-    <row r="120" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:57" ht="15.95" customHeight="1">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -4753,7 +4759,7 @@
       <c r="BD120" s="4"/>
       <c r="BE120" s="4"/>
     </row>
-    <row r="121" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:57" ht="15.95" customHeight="1">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -4777,7 +4783,7 @@
       <c r="BD121" s="4"/>
       <c r="BE121" s="4"/>
     </row>
-    <row r="122" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:57" ht="15.95" customHeight="1">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -4801,7 +4807,7 @@
       <c r="BD122" s="4"/>
       <c r="BE122" s="4"/>
     </row>
-    <row r="123" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:57" ht="15.95" customHeight="1">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -4825,7 +4831,7 @@
       <c r="BD123" s="4"/>
       <c r="BE123" s="4"/>
     </row>
-    <row r="124" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:57" ht="15.95" customHeight="1">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -4849,7 +4855,7 @@
       <c r="BD124" s="4"/>
       <c r="BE124" s="4"/>
     </row>
-    <row r="125" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:57" ht="15.95" customHeight="1">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -4873,7 +4879,7 @@
       <c r="BD125" s="4"/>
       <c r="BE125" s="4"/>
     </row>
-    <row r="126" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:57" ht="15.95" customHeight="1">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -4897,7 +4903,7 @@
       <c r="BD126" s="4"/>
       <c r="BE126" s="4"/>
     </row>
-    <row r="127" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:57" ht="15.95" customHeight="1">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -4921,7 +4927,7 @@
       <c r="BD127" s="4"/>
       <c r="BE127" s="4"/>
     </row>
-    <row r="128" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:57" ht="15.95" customHeight="1">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -4945,7 +4951,7 @@
       <c r="BD128" s="4"/>
       <c r="BE128" s="4"/>
     </row>
-    <row r="129" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:57" ht="15.95" customHeight="1">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -4969,7 +4975,7 @@
       <c r="BD129" s="4"/>
       <c r="BE129" s="4"/>
     </row>
-    <row r="130" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:57" ht="15.95" customHeight="1">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -4993,7 +4999,7 @@
       <c r="BD130" s="4"/>
       <c r="BE130" s="4"/>
     </row>
-    <row r="131" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:57" ht="15.95" customHeight="1">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -5017,7 +5023,7 @@
       <c r="BD131" s="4"/>
       <c r="BE131" s="4"/>
     </row>
-    <row r="132" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:57" ht="15.95" customHeight="1">
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
@@ -5041,7 +5047,7 @@
       <c r="BD132" s="4"/>
       <c r="BE132" s="4"/>
     </row>
-    <row r="133" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:57" ht="15.95" customHeight="1">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -5065,7 +5071,7 @@
       <c r="BD133" s="4"/>
       <c r="BE133" s="4"/>
     </row>
-    <row r="134" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:57" ht="15.95" customHeight="1">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -5089,7 +5095,7 @@
       <c r="BD134" s="4"/>
       <c r="BE134" s="4"/>
     </row>
-    <row r="135" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:57" ht="15.95" customHeight="1">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -5113,7 +5119,7 @@
       <c r="BD135" s="4"/>
       <c r="BE135" s="4"/>
     </row>
-    <row r="136" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:57" ht="15.95" customHeight="1">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -5137,7 +5143,7 @@
       <c r="BD136" s="4"/>
       <c r="BE136" s="4"/>
     </row>
-    <row r="137" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:57" ht="15.95" customHeight="1">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -5161,7 +5167,7 @@
       <c r="BD137" s="4"/>
       <c r="BE137" s="4"/>
     </row>
-    <row r="138" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:57" ht="15.95" customHeight="1">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -5185,7 +5191,7 @@
       <c r="BD138" s="4"/>
       <c r="BE138" s="4"/>
     </row>
-    <row r="139" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:57" ht="15.95" customHeight="1">
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -5209,7 +5215,7 @@
       <c r="BD139" s="4"/>
       <c r="BE139" s="4"/>
     </row>
-    <row r="140" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:57" ht="15.95" customHeight="1">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -5233,7 +5239,7 @@
       <c r="BD140" s="4"/>
       <c r="BE140" s="4"/>
     </row>
-    <row r="141" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:57" ht="15.95" customHeight="1">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -5257,7 +5263,7 @@
       <c r="BD141" s="4"/>
       <c r="BE141" s="4"/>
     </row>
-    <row r="142" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:57" ht="15.95" customHeight="1">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -5281,7 +5287,7 @@
       <c r="BD142" s="4"/>
       <c r="BE142" s="4"/>
     </row>
-    <row r="143" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:57" ht="15.95" customHeight="1">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
@@ -5305,7 +5311,7 @@
       <c r="BD143" s="4"/>
       <c r="BE143" s="4"/>
     </row>
-    <row r="144" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:57" ht="15.95" customHeight="1">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -5329,7 +5335,7 @@
       <c r="BD144" s="4"/>
       <c r="BE144" s="4"/>
     </row>
-    <row r="145" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:57" ht="15.95" customHeight="1">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -5353,7 +5359,7 @@
       <c r="BD145" s="4"/>
       <c r="BE145" s="4"/>
     </row>
-    <row r="146" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:57" ht="15.95" customHeight="1">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -5377,7 +5383,7 @@
       <c r="BD146" s="4"/>
       <c r="BE146" s="4"/>
     </row>
-    <row r="147" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:57" ht="15.95" customHeight="1">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -5401,7 +5407,7 @@
       <c r="BD147" s="4"/>
       <c r="BE147" s="4"/>
     </row>
-    <row r="148" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:57" ht="15.95" customHeight="1">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -5425,7 +5431,7 @@
       <c r="BD148" s="4"/>
       <c r="BE148" s="4"/>
     </row>
-    <row r="149" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:57" ht="15.95" customHeight="1">
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -5449,7 +5455,7 @@
       <c r="BD149" s="4"/>
       <c r="BE149" s="4"/>
     </row>
-    <row r="150" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:57" ht="15.95" customHeight="1">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -5473,7 +5479,7 @@
       <c r="BD150" s="4"/>
       <c r="BE150" s="4"/>
     </row>
-    <row r="151" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:57" ht="15.95" customHeight="1">
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -5497,7 +5503,7 @@
       <c r="BD151" s="4"/>
       <c r="BE151" s="4"/>
     </row>
-    <row r="152" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:57" ht="15.95" customHeight="1">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -5521,7 +5527,7 @@
       <c r="BD152" s="4"/>
       <c r="BE152" s="4"/>
     </row>
-    <row r="153" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:57" ht="15.95" customHeight="1">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
@@ -5545,7 +5551,7 @@
       <c r="BD153" s="4"/>
       <c r="BE153" s="4"/>
     </row>
-    <row r="154" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:57" ht="15.95" customHeight="1">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4"/>
@@ -5569,7 +5575,7 @@
       <c r="BD154" s="4"/>
       <c r="BE154" s="4"/>
     </row>
-    <row r="155" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:57" ht="15.95" customHeight="1">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
@@ -5593,7 +5599,7 @@
       <c r="BD155" s="4"/>
       <c r="BE155" s="4"/>
     </row>
-    <row r="156" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:57" ht="15.95" customHeight="1">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -5617,7 +5623,7 @@
       <c r="BD156" s="4"/>
       <c r="BE156" s="4"/>
     </row>
-    <row r="157" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:57" ht="15.95" customHeight="1">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -5641,7 +5647,7 @@
       <c r="BD157" s="4"/>
       <c r="BE157" s="4"/>
     </row>
-    <row r="158" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:57" ht="15.95" customHeight="1">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -5665,7 +5671,7 @@
       <c r="BD158" s="4"/>
       <c r="BE158" s="4"/>
     </row>
-    <row r="159" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:57" ht="15.95" customHeight="1">
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
@@ -5689,7 +5695,7 @@
       <c r="BD159" s="4"/>
       <c r="BE159" s="4"/>
     </row>
-    <row r="160" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:57" ht="15.95" customHeight="1">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -5713,7 +5719,7 @@
       <c r="BD160" s="4"/>
       <c r="BE160" s="4"/>
     </row>
-    <row r="161" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:57" ht="15.95" customHeight="1">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -5737,7 +5743,7 @@
       <c r="BD161" s="4"/>
       <c r="BE161" s="4"/>
     </row>
-    <row r="162" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:57" ht="15.95" customHeight="1">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -5761,7 +5767,7 @@
       <c r="BD162" s="4"/>
       <c r="BE162" s="4"/>
     </row>
-    <row r="163" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:57" ht="15.95" customHeight="1">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -5785,7 +5791,7 @@
       <c r="BD163" s="4"/>
       <c r="BE163" s="4"/>
     </row>
-    <row r="164" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:57" ht="15.95" customHeight="1">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -5809,7 +5815,7 @@
       <c r="BD164" s="4"/>
       <c r="BE164" s="4"/>
     </row>
-    <row r="165" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:57" ht="15.95" customHeight="1">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -5833,7 +5839,7 @@
       <c r="BD165" s="4"/>
       <c r="BE165" s="4"/>
     </row>
-    <row r="166" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:57" ht="15.95" customHeight="1">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -5857,7 +5863,7 @@
       <c r="BD166" s="4"/>
       <c r="BE166" s="4"/>
     </row>
-    <row r="167" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:57" ht="15.95" customHeight="1">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -5881,7 +5887,7 @@
       <c r="BD167" s="4"/>
       <c r="BE167" s="4"/>
     </row>
-    <row r="168" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:57" ht="15.95" customHeight="1">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -5905,7 +5911,7 @@
       <c r="BD168" s="4"/>
       <c r="BE168" s="4"/>
     </row>
-    <row r="169" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:57" ht="15.95" customHeight="1">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
@@ -5929,7 +5935,7 @@
       <c r="BD169" s="4"/>
       <c r="BE169" s="4"/>
     </row>
-    <row r="170" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:57" ht="15.95" customHeight="1">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
@@ -5953,7 +5959,7 @@
       <c r="BD170" s="4"/>
       <c r="BE170" s="4"/>
     </row>
-    <row r="171" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:57" ht="15.95" customHeight="1">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
@@ -5977,7 +5983,7 @@
       <c r="BD171" s="4"/>
       <c r="BE171" s="4"/>
     </row>
-    <row r="172" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:57" ht="15.95" customHeight="1">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -6001,7 +6007,7 @@
       <c r="BD172" s="4"/>
       <c r="BE172" s="4"/>
     </row>
-    <row r="173" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:57" ht="15.95" customHeight="1">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -6025,7 +6031,7 @@
       <c r="BD173" s="4"/>
       <c r="BE173" s="4"/>
     </row>
-    <row r="174" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:57" ht="15.95" customHeight="1">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -6049,7 +6055,7 @@
       <c r="BD174" s="4"/>
       <c r="BE174" s="4"/>
     </row>
-    <row r="175" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:57" ht="15.95" customHeight="1">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -6073,7 +6079,7 @@
       <c r="BD175" s="4"/>
       <c r="BE175" s="4"/>
     </row>
-    <row r="176" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:57" ht="15.95" customHeight="1">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -6097,7 +6103,7 @@
       <c r="BD176" s="4"/>
       <c r="BE176" s="4"/>
     </row>
-    <row r="177" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:57" ht="15.95" customHeight="1">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -6121,7 +6127,7 @@
       <c r="BD177" s="4"/>
       <c r="BE177" s="4"/>
     </row>
-    <row r="178" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:57" ht="15.95" customHeight="1">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -6145,7 +6151,7 @@
       <c r="BD178" s="4"/>
       <c r="BE178" s="4"/>
     </row>
-    <row r="179" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:57" ht="15.95" customHeight="1">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
@@ -6169,7 +6175,7 @@
       <c r="BD179" s="4"/>
       <c r="BE179" s="4"/>
     </row>
-    <row r="180" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:57" ht="15.95" customHeight="1">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -6193,7 +6199,7 @@
       <c r="BD180" s="4"/>
       <c r="BE180" s="4"/>
     </row>
-    <row r="181" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:57" ht="15.95" customHeight="1">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -6217,7 +6223,7 @@
       <c r="BD181" s="4"/>
       <c r="BE181" s="4"/>
     </row>
-    <row r="182" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:57" ht="15.95" customHeight="1">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -6241,7 +6247,7 @@
       <c r="BD182" s="4"/>
       <c r="BE182" s="4"/>
     </row>
-    <row r="183" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:57" ht="15.95" customHeight="1">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -6265,7 +6271,7 @@
       <c r="BD183" s="4"/>
       <c r="BE183" s="4"/>
     </row>
-    <row r="184" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:57" ht="15.95" customHeight="1">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -6289,7 +6295,7 @@
       <c r="BD184" s="4"/>
       <c r="BE184" s="4"/>
     </row>
-    <row r="185" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:57" ht="15.95" customHeight="1">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -6313,7 +6319,7 @@
       <c r="BD185" s="4"/>
       <c r="BE185" s="4"/>
     </row>
-    <row r="186" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:57" ht="15.95" customHeight="1">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
@@ -6337,7 +6343,7 @@
       <c r="BD186" s="4"/>
       <c r="BE186" s="4"/>
     </row>
-    <row r="187" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:57" ht="15.95" customHeight="1">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
@@ -6361,7 +6367,7 @@
       <c r="BD187" s="4"/>
       <c r="BE187" s="4"/>
     </row>
-    <row r="188" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:57" ht="15.95" customHeight="1">
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
@@ -6385,7 +6391,7 @@
       <c r="BD188" s="4"/>
       <c r="BE188" s="4"/>
     </row>
-    <row r="189" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:57" ht="15.95" customHeight="1">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -6409,7 +6415,7 @@
       <c r="BD189" s="4"/>
       <c r="BE189" s="4"/>
     </row>
-    <row r="190" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:57" ht="15.95" customHeight="1">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -6433,7 +6439,7 @@
       <c r="BD190" s="4"/>
       <c r="BE190" s="4"/>
     </row>
-    <row r="191" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:57" ht="15.95" customHeight="1">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -6457,7 +6463,7 @@
       <c r="BD191" s="4"/>
       <c r="BE191" s="4"/>
     </row>
-    <row r="192" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:57" ht="15.95" customHeight="1">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -6481,7 +6487,7 @@
       <c r="BD192" s="4"/>
       <c r="BE192" s="4"/>
     </row>
-    <row r="193" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:57" ht="15.95" customHeight="1">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -6505,7 +6511,7 @@
       <c r="BD193" s="4"/>
       <c r="BE193" s="4"/>
     </row>
-    <row r="194" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:57" ht="15.95" customHeight="1">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -6529,7 +6535,7 @@
       <c r="BD194" s="4"/>
       <c r="BE194" s="4"/>
     </row>
-    <row r="195" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:57" ht="15.95" customHeight="1">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -6553,7 +6559,7 @@
       <c r="BD195" s="4"/>
       <c r="BE195" s="4"/>
     </row>
-    <row r="196" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:57" ht="15.95" customHeight="1">
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
@@ -6577,7 +6583,7 @@
       <c r="BD196" s="4"/>
       <c r="BE196" s="4"/>
     </row>
-    <row r="197" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:57" ht="15.95" customHeight="1">
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
       <c r="C197" s="4"/>
@@ -6601,7 +6607,7 @@
       <c r="BD197" s="4"/>
       <c r="BE197" s="4"/>
     </row>
-    <row r="198" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:57" ht="15.95" customHeight="1">
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
@@ -6625,7 +6631,7 @@
       <c r="BD198" s="4"/>
       <c r="BE198" s="4"/>
     </row>
-    <row r="199" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:57" ht="15.95" customHeight="1">
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
@@ -6649,7 +6655,7 @@
       <c r="BD199" s="4"/>
       <c r="BE199" s="4"/>
     </row>
-    <row r="200" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:57" ht="15.95" customHeight="1">
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
@@ -6673,7 +6679,7 @@
       <c r="BD200" s="4"/>
       <c r="BE200" s="4"/>
     </row>
-    <row r="201" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:57" ht="15.95" customHeight="1">
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
@@ -6697,7 +6703,7 @@
       <c r="BD201" s="4"/>
       <c r="BE201" s="4"/>
     </row>
-    <row r="202" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:57" ht="15.95" customHeight="1">
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
@@ -6721,7 +6727,7 @@
       <c r="BD202" s="4"/>
       <c r="BE202" s="4"/>
     </row>
-    <row r="203" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:57" ht="15.95" customHeight="1">
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -6745,7 +6751,7 @@
       <c r="BD203" s="4"/>
       <c r="BE203" s="4"/>
     </row>
-    <row r="204" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:57" ht="15.95" customHeight="1">
       <c r="A204" s="4"/>
       <c r="B204" s="4"/>
       <c r="C204" s="4"/>
@@ -6769,7 +6775,7 @@
       <c r="BD204" s="4"/>
       <c r="BE204" s="4"/>
     </row>
-    <row r="205" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:57" ht="15.95" customHeight="1">
       <c r="A205" s="4"/>
       <c r="B205" s="4"/>
       <c r="C205" s="4"/>
@@ -6793,7 +6799,7 @@
       <c r="BD205" s="4"/>
       <c r="BE205" s="4"/>
     </row>
-    <row r="206" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:57" ht="15.95" customHeight="1">
       <c r="A206" s="4"/>
       <c r="B206" s="4"/>
       <c r="C206" s="4"/>
@@ -6817,7 +6823,7 @@
       <c r="BD206" s="4"/>
       <c r="BE206" s="4"/>
     </row>
-    <row r="207" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:57" ht="15.95" customHeight="1">
       <c r="A207" s="4"/>
       <c r="B207" s="4"/>
       <c r="C207" s="4"/>
@@ -6841,7 +6847,7 @@
       <c r="BD207" s="4"/>
       <c r="BE207" s="4"/>
     </row>
-    <row r="208" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:57" ht="15.95" customHeight="1">
       <c r="A208" s="4"/>
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
@@ -6865,7 +6871,7 @@
       <c r="BD208" s="4"/>
       <c r="BE208" s="4"/>
     </row>
-    <row r="209" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:57" ht="15.95" customHeight="1">
       <c r="A209" s="4"/>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
@@ -6889,7 +6895,7 @@
       <c r="BD209" s="4"/>
       <c r="BE209" s="4"/>
     </row>
-    <row r="210" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:57" ht="15.95" customHeight="1">
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
@@ -6913,7 +6919,7 @@
       <c r="BD210" s="4"/>
       <c r="BE210" s="4"/>
     </row>
-    <row r="211" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:57" ht="15.95" customHeight="1">
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
@@ -6937,7 +6943,7 @@
       <c r="BD211" s="4"/>
       <c r="BE211" s="4"/>
     </row>
-    <row r="212" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:57" ht="15.95" customHeight="1">
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
@@ -6961,7 +6967,7 @@
       <c r="BD212" s="4"/>
       <c r="BE212" s="4"/>
     </row>
-    <row r="213" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:57" ht="15.95" customHeight="1">
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
@@ -6985,7 +6991,7 @@
       <c r="BD213" s="4"/>
       <c r="BE213" s="4"/>
     </row>
-    <row r="214" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:57" ht="15.95" customHeight="1">
       <c r="A214" s="4"/>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
@@ -7009,7 +7015,7 @@
       <c r="BD214" s="4"/>
       <c r="BE214" s="4"/>
     </row>
-    <row r="215" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:57" ht="15.95" customHeight="1">
       <c r="A215" s="4"/>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
@@ -7033,7 +7039,7 @@
       <c r="BD215" s="4"/>
       <c r="BE215" s="4"/>
     </row>
-    <row r="216" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:57" ht="15.95" customHeight="1">
       <c r="A216" s="4"/>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
@@ -7057,7 +7063,7 @@
       <c r="BD216" s="4"/>
       <c r="BE216" s="4"/>
     </row>
-    <row r="217" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:57" ht="15.95" customHeight="1">
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
@@ -7081,7 +7087,7 @@
       <c r="BD217" s="4"/>
       <c r="BE217" s="4"/>
     </row>
-    <row r="218" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:57" ht="15.95" customHeight="1">
       <c r="A218" s="4"/>
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
@@ -7105,7 +7111,7 @@
       <c r="BD218" s="4"/>
       <c r="BE218" s="4"/>
     </row>
-    <row r="219" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:57" ht="15.95" customHeight="1">
       <c r="A219" s="4"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
@@ -7129,7 +7135,7 @@
       <c r="BD219" s="4"/>
       <c r="BE219" s="4"/>
     </row>
-    <row r="220" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:57" ht="15.95" customHeight="1">
       <c r="A220" s="4"/>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
@@ -7153,7 +7159,7 @@
       <c r="BD220" s="4"/>
       <c r="BE220" s="4"/>
     </row>
-    <row r="221" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:57" ht="15.95" customHeight="1">
       <c r="A221" s="4"/>
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
@@ -7177,7 +7183,7 @@
       <c r="BD221" s="4"/>
       <c r="BE221" s="4"/>
     </row>
-    <row r="222" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:57" ht="15.95" customHeight="1">
       <c r="A222" s="4"/>
       <c r="B222" s="4"/>
       <c r="C222" s="4"/>
@@ -7201,7 +7207,7 @@
       <c r="BD222" s="4"/>
       <c r="BE222" s="4"/>
     </row>
-    <row r="223" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:57" ht="15.95" customHeight="1">
       <c r="A223" s="4"/>
       <c r="B223" s="4"/>
       <c r="C223" s="4"/>
@@ -7225,7 +7231,7 @@
       <c r="BD223" s="4"/>
       <c r="BE223" s="4"/>
     </row>
-    <row r="224" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:57" ht="15.95" customHeight="1">
       <c r="A224" s="4"/>
       <c r="B224" s="4"/>
       <c r="C224" s="4"/>
@@ -7249,7 +7255,7 @@
       <c r="BD224" s="4"/>
       <c r="BE224" s="4"/>
     </row>
-    <row r="225" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:57" ht="15.95" customHeight="1">
       <c r="A225" s="4"/>
       <c r="B225" s="4"/>
       <c r="C225" s="4"/>
@@ -7273,7 +7279,7 @@
       <c r="BD225" s="4"/>
       <c r="BE225" s="4"/>
     </row>
-    <row r="226" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:57" ht="15.95" customHeight="1">
       <c r="A226" s="4"/>
       <c r="B226" s="4"/>
       <c r="C226" s="4"/>
@@ -7297,7 +7303,7 @@
       <c r="BD226" s="4"/>
       <c r="BE226" s="4"/>
     </row>
-    <row r="227" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:57" ht="15.95" customHeight="1">
       <c r="A227" s="4"/>
       <c r="B227" s="4"/>
       <c r="C227" s="4"/>
@@ -7321,7 +7327,7 @@
       <c r="BD227" s="4"/>
       <c r="BE227" s="4"/>
     </row>
-    <row r="228" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:57" ht="15.95" customHeight="1">
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
@@ -7345,7 +7351,7 @@
       <c r="BD228" s="4"/>
       <c r="BE228" s="4"/>
     </row>
-    <row r="229" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:57" ht="15.95" customHeight="1">
       <c r="A229" s="4"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
@@ -7369,7 +7375,7 @@
       <c r="BD229" s="4"/>
       <c r="BE229" s="4"/>
     </row>
-    <row r="230" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:57" ht="15.95" customHeight="1">
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
@@ -7393,7 +7399,7 @@
       <c r="BD230" s="4"/>
       <c r="BE230" s="4"/>
     </row>
-    <row r="231" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:57" ht="15.95" customHeight="1">
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
@@ -7417,7 +7423,7 @@
       <c r="BD231" s="4"/>
       <c r="BE231" s="4"/>
     </row>
-    <row r="232" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:57" ht="15.95" customHeight="1">
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
@@ -7441,7 +7447,7 @@
       <c r="BD232" s="4"/>
       <c r="BE232" s="4"/>
     </row>
-    <row r="233" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:57" ht="15.95" customHeight="1">
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
@@ -7465,7 +7471,7 @@
       <c r="BD233" s="4"/>
       <c r="BE233" s="4"/>
     </row>
-    <row r="234" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:57" ht="15.95" customHeight="1">
       <c r="A234" s="4"/>
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
@@ -7489,7 +7495,7 @@
       <c r="BD234" s="4"/>
       <c r="BE234" s="4"/>
     </row>
-    <row r="235" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:57" ht="15.95" customHeight="1">
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
@@ -7513,7 +7519,7 @@
       <c r="BD235" s="4"/>
       <c r="BE235" s="4"/>
     </row>
-    <row r="236" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:57" ht="15.95" customHeight="1">
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
@@ -7537,7 +7543,7 @@
       <c r="BD236" s="4"/>
       <c r="BE236" s="4"/>
     </row>
-    <row r="237" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:57" ht="15.95" customHeight="1">
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
@@ -7561,7 +7567,7 @@
       <c r="BD237" s="4"/>
       <c r="BE237" s="4"/>
     </row>
-    <row r="238" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:57" ht="15.95" customHeight="1">
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
@@ -7585,7 +7591,7 @@
       <c r="BD238" s="4"/>
       <c r="BE238" s="4"/>
     </row>
-    <row r="239" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:57" ht="15.95" customHeight="1">
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
@@ -7609,7 +7615,7 @@
       <c r="BD239" s="4"/>
       <c r="BE239" s="4"/>
     </row>
-    <row r="240" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:57" ht="15.95" customHeight="1">
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
@@ -7633,7 +7639,7 @@
       <c r="BD240" s="4"/>
       <c r="BE240" s="4"/>
     </row>
-    <row r="241" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:57" ht="15.95" customHeight="1">
       <c r="A241" s="4"/>
       <c r="B241" s="4"/>
       <c r="C241" s="4"/>
@@ -7657,7 +7663,7 @@
       <c r="BD241" s="4"/>
       <c r="BE241" s="4"/>
     </row>
-    <row r="242" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:57" ht="15.95" customHeight="1">
       <c r="A242" s="4"/>
       <c r="B242" s="4"/>
       <c r="C242" s="4"/>
@@ -7681,7 +7687,7 @@
       <c r="BD242" s="4"/>
       <c r="BE242" s="4"/>
     </row>
-    <row r="243" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:57" ht="15.95" customHeight="1">
       <c r="A243" s="4"/>
       <c r="B243" s="4"/>
       <c r="C243" s="4"/>
@@ -7705,7 +7711,7 @@
       <c r="BD243" s="4"/>
       <c r="BE243" s="4"/>
     </row>
-    <row r="244" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:57" ht="15.95" customHeight="1">
       <c r="A244" s="4"/>
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
@@ -7729,7 +7735,7 @@
       <c r="BD244" s="4"/>
       <c r="BE244" s="4"/>
     </row>
-    <row r="245" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:57" ht="15.95" customHeight="1">
       <c r="A245" s="4"/>
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
@@ -7753,7 +7759,7 @@
       <c r="BD245" s="4"/>
       <c r="BE245" s="4"/>
     </row>
-    <row r="246" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:57" ht="15.95" customHeight="1">
       <c r="A246" s="4"/>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
@@ -7777,7 +7783,7 @@
       <c r="BD246" s="4"/>
       <c r="BE246" s="4"/>
     </row>
-    <row r="247" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:57" ht="15.95" customHeight="1">
       <c r="A247" s="4"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
@@ -7801,7 +7807,7 @@
       <c r="BD247" s="4"/>
       <c r="BE247" s="4"/>
     </row>
-    <row r="248" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:57" ht="15.95" customHeight="1">
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
@@ -7825,7 +7831,7 @@
       <c r="BD248" s="4"/>
       <c r="BE248" s="4"/>
     </row>
-    <row r="249" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:57" ht="15.95" customHeight="1">
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
@@ -7849,7 +7855,7 @@
       <c r="BD249" s="4"/>
       <c r="BE249" s="4"/>
     </row>
-    <row r="250" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:57" ht="15.95" customHeight="1">
       <c r="A250" s="4"/>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
@@ -7873,7 +7879,7 @@
       <c r="BD250" s="4"/>
       <c r="BE250" s="4"/>
     </row>
-    <row r="251" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:57" ht="15.95" customHeight="1">
       <c r="A251" s="4"/>
       <c r="B251" s="4"/>
       <c r="C251" s="4"/>
@@ -7897,7 +7903,7 @@
       <c r="BD251" s="4"/>
       <c r="BE251" s="4"/>
     </row>
-    <row r="252" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:57" ht="15.95" customHeight="1">
       <c r="A252" s="4"/>
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
@@ -7921,7 +7927,7 @@
       <c r="BD252" s="4"/>
       <c r="BE252" s="4"/>
     </row>
-    <row r="253" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:57" ht="15.95" customHeight="1">
       <c r="A253" s="4"/>
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
@@ -7945,7 +7951,7 @@
       <c r="BD253" s="4"/>
       <c r="BE253" s="4"/>
     </row>
-    <row r="254" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:57" ht="15.95" customHeight="1">
       <c r="A254" s="4"/>
       <c r="B254" s="4"/>
       <c r="C254" s="4"/>
@@ -7969,7 +7975,7 @@
       <c r="BD254" s="4"/>
       <c r="BE254" s="4"/>
     </row>
-    <row r="255" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:57" ht="15.95" customHeight="1">
       <c r="A255" s="4"/>
       <c r="B255" s="4"/>
       <c r="C255" s="4"/>
@@ -7993,7 +7999,7 @@
       <c r="BD255" s="4"/>
       <c r="BE255" s="4"/>
     </row>
-    <row r="256" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:57" ht="15.95" customHeight="1">
       <c r="A256" s="4"/>
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
@@ -8017,7 +8023,7 @@
       <c r="BD256" s="4"/>
       <c r="BE256" s="4"/>
     </row>
-    <row r="257" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:57" ht="15.95" customHeight="1">
       <c r="A257" s="4"/>
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
@@ -8041,7 +8047,7 @@
       <c r="BD257" s="4"/>
       <c r="BE257" s="4"/>
     </row>
-    <row r="258" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:57" ht="15.95" customHeight="1">
       <c r="A258" s="4"/>
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
@@ -8065,7 +8071,7 @@
       <c r="BD258" s="4"/>
       <c r="BE258" s="4"/>
     </row>
-    <row r="259" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:57" ht="15.95" customHeight="1">
       <c r="A259" s="4"/>
       <c r="B259" s="4"/>
       <c r="C259" s="4"/>
@@ -8089,7 +8095,7 @@
       <c r="BD259" s="4"/>
       <c r="BE259" s="4"/>
     </row>
-    <row r="260" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:57" ht="15.95" customHeight="1">
       <c r="A260" s="4"/>
       <c r="B260" s="4"/>
       <c r="C260" s="4"/>
@@ -8113,7 +8119,7 @@
       <c r="BD260" s="4"/>
       <c r="BE260" s="4"/>
     </row>
-    <row r="261" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:57" ht="15.95" customHeight="1">
       <c r="A261" s="4"/>
       <c r="B261" s="4"/>
       <c r="C261" s="4"/>
@@ -8137,7 +8143,7 @@
       <c r="BD261" s="4"/>
       <c r="BE261" s="4"/>
     </row>
-    <row r="262" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:57" ht="15.95" customHeight="1">
       <c r="A262" s="4"/>
       <c r="B262" s="4"/>
       <c r="C262" s="4"/>
@@ -8161,7 +8167,7 @@
       <c r="BD262" s="4"/>
       <c r="BE262" s="4"/>
     </row>
-    <row r="263" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:57" ht="15.95" customHeight="1">
       <c r="A263" s="4"/>
       <c r="B263" s="4"/>
       <c r="C263" s="4"/>
@@ -8185,7 +8191,7 @@
       <c r="BD263" s="4"/>
       <c r="BE263" s="4"/>
     </row>
-    <row r="264" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:57" ht="15.95" customHeight="1">
       <c r="A264" s="4"/>
       <c r="B264" s="4"/>
       <c r="C264" s="4"/>
@@ -8209,7 +8215,7 @@
       <c r="BD264" s="4"/>
       <c r="BE264" s="4"/>
     </row>
-    <row r="265" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:57" ht="15.95" customHeight="1">
       <c r="A265" s="4"/>
       <c r="B265" s="4"/>
       <c r="C265" s="4"/>
@@ -8233,7 +8239,7 @@
       <c r="BD265" s="4"/>
       <c r="BE265" s="4"/>
     </row>
-    <row r="266" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:57" ht="15.95" customHeight="1">
       <c r="A266" s="4"/>
       <c r="B266" s="4"/>
       <c r="C266" s="4"/>
@@ -8257,7 +8263,7 @@
       <c r="BD266" s="4"/>
       <c r="BE266" s="4"/>
     </row>
-    <row r="267" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:57" ht="15.95" customHeight="1">
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
@@ -8281,7 +8287,7 @@
       <c r="BD267" s="4"/>
       <c r="BE267" s="4"/>
     </row>
-    <row r="268" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:57" ht="15.95" customHeight="1">
       <c r="A268" s="4"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
@@ -8305,7 +8311,7 @@
       <c r="BD268" s="4"/>
       <c r="BE268" s="4"/>
     </row>
-    <row r="269" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:57" ht="15.95" customHeight="1">
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
@@ -8329,7 +8335,7 @@
       <c r="BD269" s="4"/>
       <c r="BE269" s="4"/>
     </row>
-    <row r="270" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:57" ht="15.95" customHeight="1">
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
@@ -8353,7 +8359,7 @@
       <c r="BD270" s="4"/>
       <c r="BE270" s="4"/>
     </row>
-    <row r="271" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:57" ht="15.95" customHeight="1">
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
@@ -8377,7 +8383,7 @@
       <c r="BD271" s="4"/>
       <c r="BE271" s="4"/>
     </row>
-    <row r="272" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:57" ht="15.95" customHeight="1">
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
@@ -8401,7 +8407,7 @@
       <c r="BD272" s="4"/>
       <c r="BE272" s="4"/>
     </row>
-    <row r="273" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:57" ht="15.95" customHeight="1">
       <c r="A273" s="4"/>
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
@@ -8425,7 +8431,7 @@
       <c r="BD273" s="4"/>
       <c r="BE273" s="4"/>
     </row>
-    <row r="274" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:57" ht="15.95" customHeight="1">
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
@@ -8449,7 +8455,7 @@
       <c r="BD274" s="4"/>
       <c r="BE274" s="4"/>
     </row>
-    <row r="275" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:57" ht="15.95" customHeight="1">
       <c r="A275" s="4"/>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
@@ -8473,7 +8479,7 @@
       <c r="BD275" s="4"/>
       <c r="BE275" s="4"/>
     </row>
-    <row r="276" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:57" ht="15.95" customHeight="1">
       <c r="A276" s="4"/>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
@@ -8497,7 +8503,7 @@
       <c r="BD276" s="4"/>
       <c r="BE276" s="4"/>
     </row>
-    <row r="277" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:57" ht="15.95" customHeight="1">
       <c r="A277" s="4"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
@@ -8521,7 +8527,7 @@
       <c r="BD277" s="4"/>
       <c r="BE277" s="4"/>
     </row>
-    <row r="278" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:57" ht="15.95" customHeight="1">
       <c r="A278" s="4"/>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
@@ -8545,7 +8551,7 @@
       <c r="BD278" s="4"/>
       <c r="BE278" s="4"/>
     </row>
-    <row r="279" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:57" ht="15.95" customHeight="1">
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
@@ -8569,7 +8575,7 @@
       <c r="BD279" s="4"/>
       <c r="BE279" s="4"/>
     </row>
-    <row r="280" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:57" ht="15.95" customHeight="1">
       <c r="A280" s="4"/>
       <c r="B280" s="4"/>
       <c r="C280" s="4"/>
@@ -8593,7 +8599,7 @@
       <c r="BD280" s="4"/>
       <c r="BE280" s="4"/>
     </row>
-    <row r="281" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:57" ht="15.95" customHeight="1">
       <c r="A281" s="4"/>
       <c r="B281" s="4"/>
       <c r="C281" s="4"/>
@@ -8617,7 +8623,7 @@
       <c r="BD281" s="4"/>
       <c r="BE281" s="4"/>
     </row>
-    <row r="282" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:57" ht="15.95" customHeight="1">
       <c r="A282" s="4"/>
       <c r="B282" s="4"/>
       <c r="C282" s="4"/>
@@ -8641,7 +8647,7 @@
       <c r="BD282" s="4"/>
       <c r="BE282" s="4"/>
     </row>
-    <row r="283" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:57" ht="15.95" customHeight="1">
       <c r="A283" s="4"/>
       <c r="B283" s="4"/>
       <c r="C283" s="4"/>
@@ -8665,7 +8671,7 @@
       <c r="BD283" s="4"/>
       <c r="BE283" s="4"/>
     </row>
-    <row r="284" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:57" ht="15.95" customHeight="1">
       <c r="A284" s="4"/>
       <c r="B284" s="4"/>
       <c r="C284" s="4"/>
@@ -8689,7 +8695,7 @@
       <c r="BD284" s="4"/>
       <c r="BE284" s="4"/>
     </row>
-    <row r="285" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:57" ht="15.95" customHeight="1">
       <c r="A285" s="4"/>
       <c r="B285" s="4"/>
       <c r="C285" s="4"/>
@@ -8713,7 +8719,7 @@
       <c r="BD285" s="4"/>
       <c r="BE285" s="4"/>
     </row>
-    <row r="286" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:57" ht="15.95" customHeight="1">
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
@@ -8737,7 +8743,7 @@
       <c r="BD286" s="4"/>
       <c r="BE286" s="4"/>
     </row>
-    <row r="287" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:57" ht="15.95" customHeight="1">
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
@@ -8761,7 +8767,7 @@
       <c r="BD287" s="4"/>
       <c r="BE287" s="4"/>
     </row>
-    <row r="288" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:57" ht="15.95" customHeight="1">
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
@@ -8785,7 +8791,7 @@
       <c r="BD288" s="4"/>
       <c r="BE288" s="4"/>
     </row>
-    <row r="289" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:57" ht="15.95" customHeight="1">
       <c r="A289" s="4"/>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
@@ -8809,7 +8815,7 @@
       <c r="BD289" s="4"/>
       <c r="BE289" s="4"/>
     </row>
-    <row r="290" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:57" ht="15.95" customHeight="1">
       <c r="A290" s="4"/>
       <c r="B290" s="4"/>
       <c r="C290" s="4"/>
@@ -8833,7 +8839,7 @@
       <c r="BD290" s="4"/>
       <c r="BE290" s="4"/>
     </row>
-    <row r="291" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:57" ht="15.95" customHeight="1">
       <c r="A291" s="4"/>
       <c r="B291" s="4"/>
       <c r="C291" s="4"/>
@@ -8857,7 +8863,7 @@
       <c r="BD291" s="4"/>
       <c r="BE291" s="4"/>
     </row>
-    <row r="292" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:57" ht="15.95" customHeight="1">
       <c r="A292" s="4"/>
       <c r="B292" s="4"/>
       <c r="C292" s="4"/>
@@ -8881,7 +8887,7 @@
       <c r="BD292" s="4"/>
       <c r="BE292" s="4"/>
     </row>
-    <row r="293" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:57" ht="15.95" customHeight="1">
       <c r="A293" s="4"/>
       <c r="B293" s="4"/>
       <c r="C293" s="4"/>
@@ -8905,7 +8911,7 @@
       <c r="BD293" s="4"/>
       <c r="BE293" s="4"/>
     </row>
-    <row r="294" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:57" ht="15.95" customHeight="1">
       <c r="A294" s="4"/>
       <c r="B294" s="4"/>
       <c r="C294" s="4"/>
@@ -8929,7 +8935,7 @@
       <c r="BD294" s="4"/>
       <c r="BE294" s="4"/>
     </row>
-    <row r="295" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:57" ht="15.95" customHeight="1">
       <c r="A295" s="4"/>
       <c r="B295" s="4"/>
       <c r="C295" s="4"/>
@@ -8953,7 +8959,7 @@
       <c r="BD295" s="4"/>
       <c r="BE295" s="4"/>
     </row>
-    <row r="296" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:57" ht="15.95" customHeight="1">
       <c r="A296" s="4"/>
       <c r="B296" s="4"/>
       <c r="C296" s="4"/>
@@ -8977,7 +8983,7 @@
       <c r="BD296" s="4"/>
       <c r="BE296" s="4"/>
     </row>
-    <row r="297" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:57" ht="15.95" customHeight="1">
       <c r="A297" s="4"/>
       <c r="B297" s="4"/>
       <c r="C297" s="4"/>
@@ -9001,7 +9007,7 @@
       <c r="BD297" s="4"/>
       <c r="BE297" s="4"/>
     </row>
-    <row r="298" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:57" ht="15.95" customHeight="1">
       <c r="A298" s="4"/>
       <c r="B298" s="4"/>
       <c r="C298" s="4"/>
@@ -9025,7 +9031,7 @@
       <c r="BD298" s="4"/>
       <c r="BE298" s="4"/>
     </row>
-    <row r="299" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:57" ht="15.95" customHeight="1">
       <c r="A299" s="4"/>
       <c r="B299" s="4"/>
       <c r="C299" s="4"/>
@@ -9049,7 +9055,7 @@
       <c r="BD299" s="4"/>
       <c r="BE299" s="4"/>
     </row>
-    <row r="300" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:57" ht="15.95" customHeight="1">
       <c r="A300" s="4"/>
       <c r="B300" s="4"/>
       <c r="C300" s="4"/>
@@ -9073,7 +9079,7 @@
       <c r="BD300" s="4"/>
       <c r="BE300" s="4"/>
     </row>
-    <row r="301" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:57" ht="15.95" customHeight="1">
       <c r="A301" s="4"/>
       <c r="B301" s="4"/>
       <c r="C301" s="4"/>
@@ -9097,7 +9103,7 @@
       <c r="BD301" s="4"/>
       <c r="BE301" s="4"/>
     </row>
-    <row r="302" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:57" ht="15.95" customHeight="1">
       <c r="A302" s="4"/>
       <c r="B302" s="4"/>
       <c r="C302" s="4"/>
@@ -9121,7 +9127,7 @@
       <c r="BD302" s="4"/>
       <c r="BE302" s="4"/>
     </row>
-    <row r="303" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:57" ht="15.95" customHeight="1">
       <c r="A303" s="4"/>
       <c r="B303" s="4"/>
       <c r="C303" s="4"/>
@@ -9145,7 +9151,7 @@
       <c r="BD303" s="4"/>
       <c r="BE303" s="4"/>
     </row>
-    <row r="304" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:57" ht="15.95" customHeight="1">
       <c r="A304" s="4"/>
       <c r="B304" s="4"/>
       <c r="C304" s="4"/>
@@ -9169,7 +9175,7 @@
       <c r="BD304" s="4"/>
       <c r="BE304" s="4"/>
     </row>
-    <row r="305" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:57" ht="15.95" customHeight="1">
       <c r="A305" s="4"/>
       <c r="B305" s="4"/>
       <c r="C305" s="4"/>
@@ -9193,7 +9199,7 @@
       <c r="BD305" s="4"/>
       <c r="BE305" s="4"/>
     </row>
-    <row r="306" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:57" ht="15.95" customHeight="1">
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
@@ -9217,7 +9223,7 @@
       <c r="BD306" s="4"/>
       <c r="BE306" s="4"/>
     </row>
-    <row r="307" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:57" ht="15.95" customHeight="1">
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
@@ -9241,7 +9247,7 @@
       <c r="BD307" s="4"/>
       <c r="BE307" s="4"/>
     </row>
-    <row r="308" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:57" ht="15.95" customHeight="1">
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
@@ -9265,7 +9271,7 @@
       <c r="BD308" s="4"/>
       <c r="BE308" s="4"/>
     </row>
-    <row r="309" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:57" ht="15.95" customHeight="1">
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
@@ -9289,7 +9295,7 @@
       <c r="BD309" s="4"/>
       <c r="BE309" s="4"/>
     </row>
-    <row r="310" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:57" ht="15.95" customHeight="1">
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
@@ -9313,7 +9319,7 @@
       <c r="BD310" s="4"/>
       <c r="BE310" s="4"/>
     </row>
-    <row r="311" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:57" ht="15.95" customHeight="1">
       <c r="A311" s="4"/>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
@@ -9337,7 +9343,7 @@
       <c r="BD311" s="4"/>
       <c r="BE311" s="4"/>
     </row>
-    <row r="312" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:57" ht="15.95" customHeight="1">
       <c r="A312" s="4"/>
       <c r="B312" s="4"/>
       <c r="C312" s="4"/>
@@ -9361,7 +9367,7 @@
       <c r="BD312" s="4"/>
       <c r="BE312" s="4"/>
     </row>
-    <row r="313" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:57" ht="15.95" customHeight="1">
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
@@ -9385,7 +9391,7 @@
       <c r="BD313" s="4"/>
       <c r="BE313" s="4"/>
     </row>
-    <row r="314" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:57" ht="15.95" customHeight="1">
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
@@ -9409,7 +9415,7 @@
       <c r="BD314" s="4"/>
       <c r="BE314" s="4"/>
     </row>
-    <row r="315" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:57" ht="15.95" customHeight="1">
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
@@ -9433,7 +9439,7 @@
       <c r="BD315" s="4"/>
       <c r="BE315" s="4"/>
     </row>
-    <row r="316" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:57" ht="15.95" customHeight="1">
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
@@ -9457,7 +9463,7 @@
       <c r="BD316" s="4"/>
       <c r="BE316" s="4"/>
     </row>
-    <row r="317" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:57" ht="15.95" customHeight="1">
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
@@ -9481,7 +9487,7 @@
       <c r="BD317" s="4"/>
       <c r="BE317" s="4"/>
     </row>
-    <row r="318" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:57" ht="15.95" customHeight="1">
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
@@ -9505,7 +9511,7 @@
       <c r="BD318" s="4"/>
       <c r="BE318" s="4"/>
     </row>
-    <row r="319" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:57" ht="15.95" customHeight="1">
       <c r="A319" s="4"/>
       <c r="B319" s="4"/>
       <c r="C319" s="4"/>
@@ -9529,7 +9535,7 @@
       <c r="BD319" s="4"/>
       <c r="BE319" s="4"/>
     </row>
-    <row r="320" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:57" ht="15.95" customHeight="1">
       <c r="A320" s="4"/>
       <c r="B320" s="4"/>
       <c r="C320" s="4"/>
@@ -9553,7 +9559,7 @@
       <c r="BD320" s="4"/>
       <c r="BE320" s="4"/>
     </row>
-    <row r="321" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:57" ht="15.95" customHeight="1">
       <c r="A321" s="4"/>
       <c r="B321" s="4"/>
       <c r="C321" s="4"/>
@@ -9577,7 +9583,7 @@
       <c r="BD321" s="4"/>
       <c r="BE321" s="4"/>
     </row>
-    <row r="322" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:57" ht="15.95" customHeight="1">
       <c r="A322" s="4"/>
       <c r="B322" s="4"/>
       <c r="C322" s="4"/>
@@ -9601,7 +9607,7 @@
       <c r="BD322" s="4"/>
       <c r="BE322" s="4"/>
     </row>
-    <row r="323" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:57" ht="15.95" customHeight="1">
       <c r="A323" s="4"/>
       <c r="B323" s="4"/>
       <c r="C323" s="4"/>
@@ -9625,7 +9631,7 @@
       <c r="BD323" s="4"/>
       <c r="BE323" s="4"/>
     </row>
-    <row r="324" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:57" ht="15.95" customHeight="1">
       <c r="A324" s="4"/>
       <c r="B324" s="4"/>
       <c r="C324" s="4"/>
@@ -9649,7 +9655,7 @@
       <c r="BD324" s="4"/>
       <c r="BE324" s="4"/>
     </row>
-    <row r="325" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:57" ht="15.95" customHeight="1">
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
@@ -9673,7 +9679,7 @@
       <c r="BD325" s="4"/>
       <c r="BE325" s="4"/>
     </row>
-    <row r="326" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:57" ht="15.95" customHeight="1">
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
@@ -9697,7 +9703,7 @@
       <c r="BD326" s="4"/>
       <c r="BE326" s="4"/>
     </row>
-    <row r="327" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:57" ht="15.95" customHeight="1">
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
@@ -9721,7 +9727,7 @@
       <c r="BD327" s="4"/>
       <c r="BE327" s="4"/>
     </row>
-    <row r="328" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:57" ht="15.95" customHeight="1">
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
@@ -9745,7 +9751,7 @@
       <c r="BD328" s="4"/>
       <c r="BE328" s="4"/>
     </row>
-    <row r="329" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:57" ht="15.95" customHeight="1">
       <c r="A329" s="4"/>
       <c r="B329" s="4"/>
       <c r="C329" s="4"/>
@@ -9769,7 +9775,7 @@
       <c r="BD329" s="4"/>
       <c r="BE329" s="4"/>
     </row>
-    <row r="330" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:57" ht="15.95" customHeight="1">
       <c r="A330" s="4"/>
       <c r="B330" s="4"/>
       <c r="C330" s="4"/>
@@ -9793,7 +9799,7 @@
       <c r="BD330" s="4"/>
       <c r="BE330" s="4"/>
     </row>
-    <row r="331" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:57" ht="15.95" customHeight="1">
       <c r="A331" s="4"/>
       <c r="B331" s="4"/>
       <c r="C331" s="4"/>
@@ -9817,7 +9823,7 @@
       <c r="BD331" s="4"/>
       <c r="BE331" s="4"/>
     </row>
-    <row r="332" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:57" ht="15.95" customHeight="1">
       <c r="A332" s="4"/>
       <c r="B332" s="4"/>
       <c r="C332" s="4"/>
@@ -9841,7 +9847,7 @@
       <c r="BD332" s="4"/>
       <c r="BE332" s="4"/>
     </row>
-    <row r="333" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:57" ht="15.95" customHeight="1">
       <c r="A333" s="4"/>
       <c r="B333" s="4"/>
       <c r="C333" s="4"/>
@@ -9865,7 +9871,7 @@
       <c r="BD333" s="4"/>
       <c r="BE333" s="4"/>
     </row>
-    <row r="334" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:57" ht="15.95" customHeight="1">
       <c r="A334" s="4"/>
       <c r="B334" s="4"/>
       <c r="C334" s="4"/>
@@ -9889,7 +9895,7 @@
       <c r="BD334" s="4"/>
       <c r="BE334" s="4"/>
     </row>
-    <row r="335" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:57" ht="15.95" customHeight="1">
       <c r="A335" s="4"/>
       <c r="B335" s="4"/>
       <c r="C335" s="4"/>
@@ -9913,7 +9919,7 @@
       <c r="BD335" s="4"/>
       <c r="BE335" s="4"/>
     </row>
-    <row r="336" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:57" ht="15.95" customHeight="1">
       <c r="A336" s="4"/>
       <c r="B336" s="4"/>
       <c r="C336" s="4"/>
@@ -9937,7 +9943,7 @@
       <c r="BD336" s="4"/>
       <c r="BE336" s="4"/>
     </row>
-    <row r="337" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:57" ht="15.95" customHeight="1">
       <c r="A337" s="4"/>
       <c r="B337" s="4"/>
       <c r="C337" s="4"/>
@@ -9961,7 +9967,7 @@
       <c r="BD337" s="4"/>
       <c r="BE337" s="4"/>
     </row>
-    <row r="338" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:57" ht="15.95" customHeight="1">
       <c r="A338" s="4"/>
       <c r="B338" s="4"/>
       <c r="C338" s="4"/>
@@ -9985,7 +9991,7 @@
       <c r="BD338" s="4"/>
       <c r="BE338" s="4"/>
     </row>
-    <row r="339" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:57" ht="15.95" customHeight="1">
       <c r="A339" s="4"/>
       <c r="B339" s="4"/>
       <c r="C339" s="4"/>
@@ -10009,7 +10015,7 @@
       <c r="BD339" s="4"/>
       <c r="BE339" s="4"/>
     </row>
-    <row r="340" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:57" ht="15.95" customHeight="1">
       <c r="A340" s="4"/>
       <c r="B340" s="4"/>
       <c r="C340" s="4"/>
@@ -10033,7 +10039,7 @@
       <c r="BD340" s="4"/>
       <c r="BE340" s="4"/>
     </row>
-    <row r="341" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:57" ht="15.95" customHeight="1">
       <c r="A341" s="4"/>
       <c r="B341" s="4"/>
       <c r="C341" s="4"/>
@@ -10057,7 +10063,7 @@
       <c r="BD341" s="4"/>
       <c r="BE341" s="4"/>
     </row>
-    <row r="342" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:57" ht="15.95" customHeight="1">
       <c r="A342" s="4"/>
       <c r="B342" s="4"/>
       <c r="C342" s="4"/>
@@ -10081,7 +10087,7 @@
       <c r="BD342" s="4"/>
       <c r="BE342" s="4"/>
     </row>
-    <row r="343" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:57" ht="15.95" customHeight="1">
       <c r="A343" s="4"/>
       <c r="B343" s="4"/>
       <c r="C343" s="4"/>
@@ -10105,7 +10111,7 @@
       <c r="BD343" s="4"/>
       <c r="BE343" s="4"/>
     </row>
-    <row r="344" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:57" ht="15.95" customHeight="1">
       <c r="A344" s="4"/>
       <c r="B344" s="4"/>
       <c r="C344" s="4"/>
@@ -10129,7 +10135,7 @@
       <c r="BD344" s="4"/>
       <c r="BE344" s="4"/>
     </row>
-    <row r="345" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:57" ht="15.95" customHeight="1">
       <c r="A345" s="4"/>
       <c r="B345" s="4"/>
       <c r="C345" s="4"/>
@@ -10153,7 +10159,7 @@
       <c r="BD345" s="4"/>
       <c r="BE345" s="4"/>
     </row>
-    <row r="346" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:57" ht="15.95" customHeight="1">
       <c r="A346" s="4"/>
       <c r="B346" s="4"/>
       <c r="C346" s="4"/>
@@ -10177,7 +10183,7 @@
       <c r="BD346" s="4"/>
       <c r="BE346" s="4"/>
     </row>
-    <row r="347" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:57" ht="15.95" customHeight="1">
       <c r="A347" s="4"/>
       <c r="B347" s="4"/>
       <c r="C347" s="4"/>
@@ -10201,7 +10207,7 @@
       <c r="BD347" s="4"/>
       <c r="BE347" s="4"/>
     </row>
-    <row r="348" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:57" ht="15.95" customHeight="1">
       <c r="A348" s="4"/>
       <c r="B348" s="4"/>
       <c r="C348" s="4"/>
@@ -10225,7 +10231,7 @@
       <c r="BD348" s="4"/>
       <c r="BE348" s="4"/>
     </row>
-    <row r="349" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:57" ht="15.95" customHeight="1">
       <c r="A349" s="4"/>
       <c r="B349" s="4"/>
       <c r="C349" s="4"/>
@@ -10249,7 +10255,7 @@
       <c r="BD349" s="4"/>
       <c r="BE349" s="4"/>
     </row>
-    <row r="350" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:57" ht="15.95" customHeight="1">
       <c r="A350" s="4"/>
       <c r="B350" s="4"/>
       <c r="C350" s="4"/>
@@ -10273,7 +10279,7 @@
       <c r="BD350" s="4"/>
       <c r="BE350" s="4"/>
     </row>
-    <row r="351" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:57" ht="15.95" customHeight="1">
       <c r="A351" s="4"/>
       <c r="B351" s="4"/>
       <c r="C351" s="4"/>
@@ -10297,7 +10303,7 @@
       <c r="BD351" s="4"/>
       <c r="BE351" s="4"/>
     </row>
-    <row r="352" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:57" ht="15.95" customHeight="1">
       <c r="A352" s="4"/>
       <c r="B352" s="4"/>
       <c r="C352" s="4"/>
@@ -10321,7 +10327,7 @@
       <c r="BD352" s="4"/>
       <c r="BE352" s="4"/>
     </row>
-    <row r="353" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:57" ht="15.95" customHeight="1">
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
@@ -10345,7 +10351,7 @@
       <c r="BD353" s="4"/>
       <c r="BE353" s="4"/>
     </row>
-    <row r="354" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:57" ht="15.95" customHeight="1">
       <c r="A354" s="4"/>
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
@@ -10369,7 +10375,7 @@
       <c r="BD354" s="4"/>
       <c r="BE354" s="4"/>
     </row>
-    <row r="355" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:57" ht="15.95" customHeight="1">
       <c r="A355" s="4"/>
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
@@ -10393,7 +10399,7 @@
       <c r="BD355" s="4"/>
       <c r="BE355" s="4"/>
     </row>
-    <row r="356" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:57" ht="15.95" customHeight="1">
       <c r="A356" s="4"/>
       <c r="B356" s="4"/>
       <c r="C356" s="4"/>
@@ -10417,7 +10423,7 @@
       <c r="BD356" s="4"/>
       <c r="BE356" s="4"/>
     </row>
-    <row r="357" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:57" ht="15.95" customHeight="1">
       <c r="A357" s="4"/>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
@@ -10441,7 +10447,7 @@
       <c r="BD357" s="4"/>
       <c r="BE357" s="4"/>
     </row>
-    <row r="358" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:57" ht="15.95" customHeight="1">
       <c r="A358" s="4"/>
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
@@ -10465,7 +10471,7 @@
       <c r="BD358" s="4"/>
       <c r="BE358" s="4"/>
     </row>
-    <row r="359" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:57" ht="15.95" customHeight="1">
       <c r="A359" s="4"/>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
@@ -10489,7 +10495,7 @@
       <c r="BD359" s="4"/>
       <c r="BE359" s="4"/>
     </row>
-    <row r="360" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:57" ht="15.95" customHeight="1">
       <c r="A360" s="4"/>
       <c r="B360" s="4"/>
       <c r="C360" s="4"/>
@@ -10513,7 +10519,7 @@
       <c r="BD360" s="4"/>
       <c r="BE360" s="4"/>
     </row>
-    <row r="361" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:57" ht="15.95" customHeight="1">
       <c r="A361" s="4"/>
       <c r="B361" s="4"/>
       <c r="C361" s="4"/>
@@ -10537,7 +10543,7 @@
       <c r="BD361" s="4"/>
       <c r="BE361" s="4"/>
     </row>
-    <row r="362" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:57" ht="15.95" customHeight="1">
       <c r="A362" s="4"/>
       <c r="B362" s="4"/>
       <c r="C362" s="4"/>
@@ -10561,7 +10567,7 @@
       <c r="BD362" s="4"/>
       <c r="BE362" s="4"/>
     </row>
-    <row r="363" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:57" ht="15.95" customHeight="1">
       <c r="A363" s="4"/>
       <c r="B363" s="4"/>
       <c r="C363" s="4"/>
@@ -10585,7 +10591,7 @@
       <c r="BD363" s="4"/>
       <c r="BE363" s="4"/>
     </row>
-    <row r="364" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:57" ht="15.95" customHeight="1">
       <c r="A364" s="4"/>
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
@@ -10609,7 +10615,7 @@
       <c r="BD364" s="4"/>
       <c r="BE364" s="4"/>
     </row>
-    <row r="365" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:57" ht="15.95" customHeight="1">
       <c r="A365" s="4"/>
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
@@ -10633,7 +10639,7 @@
       <c r="BD365" s="4"/>
       <c r="BE365" s="4"/>
     </row>
-    <row r="366" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:57" ht="15.95" customHeight="1">
       <c r="A366" s="4"/>
       <c r="B366" s="4"/>
       <c r="C366" s="4"/>
@@ -10657,7 +10663,7 @@
       <c r="BD366" s="4"/>
       <c r="BE366" s="4"/>
     </row>
-    <row r="367" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:57" ht="15.95" customHeight="1">
       <c r="A367" s="4"/>
       <c r="B367" s="4"/>
       <c r="C367" s="4"/>
@@ -10681,7 +10687,7 @@
       <c r="BD367" s="4"/>
       <c r="BE367" s="4"/>
     </row>
-    <row r="368" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:57" ht="15.95" customHeight="1">
       <c r="A368" s="4"/>
       <c r="B368" s="4"/>
       <c r="C368" s="4"/>
@@ -10705,7 +10711,7 @@
       <c r="BD368" s="4"/>
       <c r="BE368" s="4"/>
     </row>
-    <row r="369" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:57" ht="15.95" customHeight="1">
       <c r="A369" s="4"/>
       <c r="B369" s="4"/>
       <c r="C369" s="4"/>
@@ -10729,7 +10735,7 @@
       <c r="BD369" s="4"/>
       <c r="BE369" s="4"/>
     </row>
-    <row r="370" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:57" ht="15.95" customHeight="1">
       <c r="A370" s="4"/>
       <c r="B370" s="4"/>
       <c r="C370" s="4"/>
@@ -10753,7 +10759,7 @@
       <c r="BD370" s="4"/>
       <c r="BE370" s="4"/>
     </row>
-    <row r="371" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:57" ht="15.95" customHeight="1">
       <c r="A371" s="4"/>
       <c r="B371" s="4"/>
       <c r="C371" s="4"/>
@@ -10777,7 +10783,7 @@
       <c r="BD371" s="4"/>
       <c r="BE371" s="4"/>
     </row>
-    <row r="372" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:57" ht="15.95" customHeight="1">
       <c r="A372" s="4"/>
       <c r="B372" s="4"/>
       <c r="C372" s="4"/>
@@ -10801,7 +10807,7 @@
       <c r="BD372" s="4"/>
       <c r="BE372" s="4"/>
     </row>
-    <row r="373" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:57" ht="15.95" customHeight="1">
       <c r="A373" s="4"/>
       <c r="B373" s="4"/>
       <c r="C373" s="4"/>
@@ -10825,7 +10831,7 @@
       <c r="BD373" s="4"/>
       <c r="BE373" s="4"/>
     </row>
-    <row r="374" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:57" ht="15.95" customHeight="1">
       <c r="A374" s="4"/>
       <c r="B374" s="4"/>
       <c r="C374" s="4"/>
@@ -10849,7 +10855,7 @@
       <c r="BD374" s="4"/>
       <c r="BE374" s="4"/>
     </row>
-    <row r="375" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:57" ht="15.95" customHeight="1">
       <c r="A375" s="4"/>
       <c r="B375" s="4"/>
       <c r="C375" s="4"/>
@@ -10873,7 +10879,7 @@
       <c r="BD375" s="4"/>
       <c r="BE375" s="4"/>
     </row>
-    <row r="376" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:57" ht="15.95" customHeight="1">
       <c r="A376" s="4"/>
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
@@ -10897,7 +10903,7 @@
       <c r="BD376" s="4"/>
       <c r="BE376" s="4"/>
     </row>
-    <row r="377" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:57" ht="15.95" customHeight="1">
       <c r="A377" s="4"/>
       <c r="B377" s="4"/>
       <c r="C377" s="4"/>
@@ -10921,7 +10927,7 @@
       <c r="BD377" s="4"/>
       <c r="BE377" s="4"/>
     </row>
-    <row r="378" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:57" ht="15.95" customHeight="1">
       <c r="A378" s="4"/>
       <c r="B378" s="4"/>
       <c r="C378" s="4"/>
@@ -10945,7 +10951,7 @@
       <c r="BD378" s="4"/>
       <c r="BE378" s="4"/>
     </row>
-    <row r="379" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:57" ht="15.95" customHeight="1">
       <c r="A379" s="4"/>
       <c r="B379" s="4"/>
       <c r="C379" s="4"/>
@@ -10969,7 +10975,7 @@
       <c r="BD379" s="4"/>
       <c r="BE379" s="4"/>
     </row>
-    <row r="380" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:57" ht="15.95" customHeight="1">
       <c r="A380" s="4"/>
       <c r="B380" s="4"/>
       <c r="C380" s="4"/>
@@ -10993,7 +10999,7 @@
       <c r="BD380" s="4"/>
       <c r="BE380" s="4"/>
     </row>
-    <row r="381" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:57" ht="15.95" customHeight="1">
       <c r="A381" s="4"/>
       <c r="B381" s="4"/>
       <c r="C381" s="4"/>
@@ -11017,7 +11023,7 @@
       <c r="BD381" s="4"/>
       <c r="BE381" s="4"/>
     </row>
-    <row r="382" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:57" ht="15.95" customHeight="1">
       <c r="A382" s="4"/>
       <c r="B382" s="4"/>
       <c r="C382" s="4"/>
@@ -11041,7 +11047,7 @@
       <c r="BD382" s="4"/>
       <c r="BE382" s="4"/>
     </row>
-    <row r="383" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:57" ht="15.95" customHeight="1">
       <c r="A383" s="4"/>
       <c r="B383" s="4"/>
       <c r="C383" s="4"/>
@@ -11065,7 +11071,7 @@
       <c r="BD383" s="4"/>
       <c r="BE383" s="4"/>
     </row>
-    <row r="384" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:57" ht="15.95" customHeight="1">
       <c r="A384" s="4"/>
       <c r="B384" s="4"/>
       <c r="C384" s="4"/>
@@ -11089,7 +11095,7 @@
       <c r="BD384" s="4"/>
       <c r="BE384" s="4"/>
     </row>
-    <row r="385" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:57" ht="15.95" customHeight="1">
       <c r="A385" s="4"/>
       <c r="B385" s="4"/>
       <c r="C385" s="4"/>
@@ -11113,7 +11119,7 @@
       <c r="BD385" s="4"/>
       <c r="BE385" s="4"/>
     </row>
-    <row r="386" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:57" ht="15.95" customHeight="1">
       <c r="A386" s="4"/>
       <c r="B386" s="4"/>
       <c r="C386" s="4"/>
@@ -11137,7 +11143,7 @@
       <c r="BD386" s="4"/>
       <c r="BE386" s="4"/>
     </row>
-    <row r="387" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:57" ht="15.95" customHeight="1">
       <c r="A387" s="4"/>
       <c r="B387" s="4"/>
       <c r="C387" s="4"/>
@@ -11161,7 +11167,7 @@
       <c r="BD387" s="4"/>
       <c r="BE387" s="4"/>
     </row>
-    <row r="388" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:57" ht="15.95" customHeight="1">
       <c r="A388" s="4"/>
       <c r="B388" s="4"/>
       <c r="C388" s="4"/>
@@ -11185,7 +11191,7 @@
       <c r="BD388" s="4"/>
       <c r="BE388" s="4"/>
     </row>
-    <row r="389" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:57" ht="15.95" customHeight="1">
       <c r="A389" s="4"/>
       <c r="B389" s="4"/>
       <c r="C389" s="4"/>
@@ -11209,7 +11215,7 @@
       <c r="BD389" s="4"/>
       <c r="BE389" s="4"/>
     </row>
-    <row r="390" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:57" ht="15.95" customHeight="1">
       <c r="A390" s="4"/>
       <c r="B390" s="4"/>
       <c r="C390" s="4"/>
@@ -11233,7 +11239,7 @@
       <c r="BD390" s="4"/>
       <c r="BE390" s="4"/>
     </row>
-    <row r="391" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:57" ht="15.95" customHeight="1">
       <c r="A391" s="4"/>
       <c r="B391" s="4"/>
       <c r="C391" s="4"/>
@@ -11257,7 +11263,7 @@
       <c r="BD391" s="4"/>
       <c r="BE391" s="4"/>
     </row>
-    <row r="392" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:57" ht="15.95" customHeight="1">
       <c r="A392" s="4"/>
       <c r="B392" s="4"/>
       <c r="C392" s="4"/>
@@ -11281,7 +11287,7 @@
       <c r="BD392" s="4"/>
       <c r="BE392" s="4"/>
     </row>
-    <row r="393" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:57" ht="15.95" customHeight="1">
       <c r="A393" s="4"/>
       <c r="B393" s="4"/>
       <c r="C393" s="4"/>
@@ -11305,7 +11311,7 @@
       <c r="BD393" s="4"/>
       <c r="BE393" s="4"/>
     </row>
-    <row r="394" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:57" ht="15.95" customHeight="1">
       <c r="A394" s="4"/>
       <c r="B394" s="4"/>
       <c r="C394" s="4"/>
@@ -11329,7 +11335,7 @@
       <c r="BD394" s="4"/>
       <c r="BE394" s="4"/>
     </row>
-    <row r="395" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:57" ht="15.95" customHeight="1">
       <c r="A395" s="4"/>
       <c r="B395" s="4"/>
       <c r="C395" s="4"/>
@@ -11353,7 +11359,7 @@
       <c r="BD395" s="4"/>
       <c r="BE395" s="4"/>
     </row>
-    <row r="396" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:57" ht="15.95" customHeight="1">
       <c r="A396" s="4"/>
       <c r="B396" s="4"/>
       <c r="C396" s="4"/>
@@ -11377,7 +11383,7 @@
       <c r="BD396" s="4"/>
       <c r="BE396" s="4"/>
     </row>
-    <row r="397" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:57" ht="15.95" customHeight="1">
       <c r="A397" s="4"/>
       <c r="B397" s="4"/>
       <c r="C397" s="4"/>
@@ -11401,7 +11407,7 @@
       <c r="BD397" s="4"/>
       <c r="BE397" s="4"/>
     </row>
-    <row r="398" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:57" ht="15.95" customHeight="1">
       <c r="A398" s="4"/>
       <c r="B398" s="4"/>
       <c r="C398" s="4"/>
@@ -11425,7 +11431,7 @@
       <c r="BD398" s="4"/>
       <c r="BE398" s="4"/>
     </row>
-    <row r="399" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:57" ht="15.95" customHeight="1">
       <c r="A399" s="4"/>
       <c r="B399" s="4"/>
       <c r="C399" s="4"/>
@@ -11449,7 +11455,7 @@
       <c r="BD399" s="4"/>
       <c r="BE399" s="4"/>
     </row>
-    <row r="400" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:57" ht="15.95" customHeight="1">
       <c r="A400" s="4"/>
       <c r="B400" s="4"/>
       <c r="C400" s="4"/>
@@ -11473,7 +11479,7 @@
       <c r="BD400" s="4"/>
       <c r="BE400" s="4"/>
     </row>
-    <row r="401" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:57" ht="15.95" customHeight="1">
       <c r="A401" s="4"/>
       <c r="B401" s="4"/>
       <c r="C401" s="4"/>
@@ -11497,7 +11503,7 @@
       <c r="BD401" s="4"/>
       <c r="BE401" s="4"/>
     </row>
-    <row r="402" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:57" ht="15.95" customHeight="1">
       <c r="A402" s="4"/>
       <c r="B402" s="4"/>
       <c r="C402" s="4"/>
@@ -11521,7 +11527,7 @@
       <c r="BD402" s="4"/>
       <c r="BE402" s="4"/>
     </row>
-    <row r="403" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:57" ht="15.95" customHeight="1">
       <c r="A403" s="4"/>
       <c r="B403" s="4"/>
       <c r="C403" s="4"/>
@@ -11545,7 +11551,7 @@
       <c r="BD403" s="4"/>
       <c r="BE403" s="4"/>
     </row>
-    <row r="404" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:57" ht="15.95" customHeight="1">
       <c r="A404" s="4"/>
       <c r="B404" s="4"/>
       <c r="C404" s="4"/>
@@ -11569,7 +11575,7 @@
       <c r="BD404" s="4"/>
       <c r="BE404" s="4"/>
     </row>
-    <row r="405" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:57" ht="15.95" customHeight="1">
       <c r="A405" s="4"/>
       <c r="B405" s="4"/>
       <c r="C405" s="4"/>
@@ -11593,7 +11599,7 @@
       <c r="BD405" s="4"/>
       <c r="BE405" s="4"/>
     </row>
-    <row r="406" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:57" ht="15.95" customHeight="1">
       <c r="A406" s="4"/>
       <c r="B406" s="4"/>
       <c r="C406" s="4"/>
@@ -11617,7 +11623,7 @@
       <c r="BD406" s="4"/>
       <c r="BE406" s="4"/>
     </row>
-    <row r="407" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:57" ht="15.95" customHeight="1">
       <c r="A407" s="4"/>
       <c r="B407" s="4"/>
       <c r="C407" s="4"/>
@@ -11641,7 +11647,7 @@
       <c r="BD407" s="4"/>
       <c r="BE407" s="4"/>
     </row>
-    <row r="408" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:57" ht="15.95" customHeight="1">
       <c r="A408" s="4"/>
       <c r="B408" s="4"/>
       <c r="C408" s="4"/>
@@ -11665,7 +11671,7 @@
       <c r="BD408" s="4"/>
       <c r="BE408" s="4"/>
     </row>
-    <row r="409" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:57" ht="15.95" customHeight="1">
       <c r="A409" s="4"/>
       <c r="B409" s="4"/>
       <c r="C409" s="4"/>
@@ -11689,7 +11695,7 @@
       <c r="BD409" s="4"/>
       <c r="BE409" s="4"/>
     </row>
-    <row r="410" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:57" ht="15.95" customHeight="1">
       <c r="A410" s="4"/>
       <c r="B410" s="4"/>
       <c r="C410" s="4"/>
@@ -11713,7 +11719,7 @@
       <c r="BD410" s="4"/>
       <c r="BE410" s="4"/>
     </row>
-    <row r="411" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:57" ht="15.95" customHeight="1">
       <c r="A411" s="4"/>
       <c r="B411" s="4"/>
       <c r="C411" s="4"/>
@@ -11737,7 +11743,7 @@
       <c r="BD411" s="4"/>
       <c r="BE411" s="4"/>
     </row>
-    <row r="412" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:57" ht="15.95" customHeight="1">
       <c r="A412" s="4"/>
       <c r="B412" s="4"/>
       <c r="C412" s="4"/>
@@ -11761,7 +11767,7 @@
       <c r="BD412" s="4"/>
       <c r="BE412" s="4"/>
     </row>
-    <row r="413" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:57" ht="15.95" customHeight="1">
       <c r="A413" s="4"/>
       <c r="B413" s="4"/>
       <c r="C413" s="4"/>
@@ -11785,7 +11791,7 @@
       <c r="BD413" s="4"/>
       <c r="BE413" s="4"/>
     </row>
-    <row r="414" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:57" ht="15.95" customHeight="1">
       <c r="A414" s="4"/>
       <c r="B414" s="4"/>
       <c r="C414" s="4"/>
@@ -11809,7 +11815,7 @@
       <c r="BD414" s="4"/>
       <c r="BE414" s="4"/>
     </row>
-    <row r="415" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:57" ht="15.95" customHeight="1">
       <c r="A415" s="4"/>
       <c r="B415" s="4"/>
       <c r="C415" s="4"/>
@@ -11833,7 +11839,7 @@
       <c r="BD415" s="4"/>
       <c r="BE415" s="4"/>
     </row>
-    <row r="416" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:57" ht="15.95" customHeight="1">
       <c r="A416" s="4"/>
       <c r="B416" s="4"/>
       <c r="C416" s="4"/>
@@ -11857,7 +11863,7 @@
       <c r="BD416" s="4"/>
       <c r="BE416" s="4"/>
     </row>
-    <row r="417" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:57" ht="15.95" customHeight="1">
       <c r="A417" s="4"/>
       <c r="B417" s="4"/>
       <c r="C417" s="4"/>
@@ -11881,7 +11887,7 @@
       <c r="BD417" s="4"/>
       <c r="BE417" s="4"/>
     </row>
-    <row r="418" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:57" ht="15.95" customHeight="1">
       <c r="A418" s="4"/>
       <c r="B418" s="4"/>
       <c r="C418" s="4"/>
@@ -11905,7 +11911,7 @@
       <c r="BD418" s="4"/>
       <c r="BE418" s="4"/>
     </row>
-    <row r="419" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:57" ht="15.95" customHeight="1">
       <c r="A419" s="4"/>
       <c r="B419" s="4"/>
       <c r="C419" s="4"/>
@@ -11929,7 +11935,7 @@
       <c r="BD419" s="4"/>
       <c r="BE419" s="4"/>
     </row>
-    <row r="420" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:57" ht="15.95" customHeight="1">
       <c r="A420" s="4"/>
       <c r="B420" s="4"/>
       <c r="C420" s="4"/>
@@ -11953,7 +11959,7 @@
       <c r="BD420" s="4"/>
       <c r="BE420" s="4"/>
     </row>
-    <row r="421" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:57" ht="15.95" customHeight="1">
       <c r="A421" s="4"/>
       <c r="B421" s="4"/>
       <c r="C421" s="4"/>
@@ -11977,7 +11983,7 @@
       <c r="BD421" s="4"/>
       <c r="BE421" s="4"/>
     </row>
-    <row r="422" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:57" ht="15.95" customHeight="1">
       <c r="A422" s="4"/>
       <c r="B422" s="4"/>
       <c r="C422" s="4"/>
@@ -12001,7 +12007,7 @@
       <c r="BD422" s="4"/>
       <c r="BE422" s="4"/>
     </row>
-    <row r="423" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:57" ht="15.95" customHeight="1">
       <c r="A423" s="4"/>
       <c r="B423" s="4"/>
       <c r="C423" s="4"/>
@@ -12025,7 +12031,7 @@
       <c r="BD423" s="4"/>
       <c r="BE423" s="4"/>
     </row>
-    <row r="424" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:57" ht="15.95" customHeight="1">
       <c r="A424" s="4"/>
       <c r="B424" s="4"/>
       <c r="C424" s="4"/>
@@ -12049,7 +12055,7 @@
       <c r="BD424" s="4"/>
       <c r="BE424" s="4"/>
     </row>
-    <row r="425" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:57" ht="15.95" customHeight="1">
       <c r="A425" s="4"/>
       <c r="B425" s="4"/>
       <c r="C425" s="4"/>
@@ -12073,7 +12079,7 @@
       <c r="BD425" s="4"/>
       <c r="BE425" s="4"/>
     </row>
-    <row r="426" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:57" ht="15.95" customHeight="1">
       <c r="A426" s="4"/>
       <c r="B426" s="4"/>
       <c r="C426" s="4"/>
@@ -12097,7 +12103,7 @@
       <c r="BD426" s="4"/>
       <c r="BE426" s="4"/>
     </row>
-    <row r="427" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:57" ht="15.95" customHeight="1">
       <c r="A427" s="4"/>
       <c r="B427" s="4"/>
       <c r="C427" s="4"/>
@@ -12121,7 +12127,7 @@
       <c r="BD427" s="4"/>
       <c r="BE427" s="4"/>
     </row>
-    <row r="428" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:57" ht="15.95" customHeight="1">
       <c r="A428" s="4"/>
       <c r="B428" s="4"/>
       <c r="C428" s="4"/>
@@ -12145,7 +12151,7 @@
       <c r="BD428" s="4"/>
       <c r="BE428" s="4"/>
     </row>
-    <row r="429" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:57" ht="15.95" customHeight="1">
       <c r="A429" s="4"/>
       <c r="B429" s="4"/>
       <c r="C429" s="4"/>
@@ -12169,7 +12175,7 @@
       <c r="BD429" s="4"/>
       <c r="BE429" s="4"/>
     </row>
-    <row r="430" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:57" ht="15.95" customHeight="1">
       <c r="A430" s="4"/>
       <c r="B430" s="4"/>
       <c r="C430" s="4"/>
@@ -12193,7 +12199,7 @@
       <c r="BD430" s="4"/>
       <c r="BE430" s="4"/>
     </row>
-    <row r="431" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:57" ht="15.95" customHeight="1">
       <c r="A431" s="4"/>
       <c r="B431" s="4"/>
       <c r="C431" s="4"/>
@@ -12217,7 +12223,7 @@
       <c r="BD431" s="4"/>
       <c r="BE431" s="4"/>
     </row>
-    <row r="432" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:57" ht="15.95" customHeight="1">
       <c r="A432" s="4"/>
       <c r="B432" s="4"/>
       <c r="C432" s="4"/>
@@ -12241,7 +12247,7 @@
       <c r="BD432" s="4"/>
       <c r="BE432" s="4"/>
     </row>
-    <row r="433" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:57" ht="15.95" customHeight="1">
       <c r="A433" s="4"/>
       <c r="B433" s="4"/>
       <c r="C433" s="4"/>
@@ -12265,7 +12271,7 @@
       <c r="BD433" s="4"/>
       <c r="BE433" s="4"/>
     </row>
-    <row r="434" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:57" ht="15.95" customHeight="1">
       <c r="A434" s="4"/>
       <c r="B434" s="4"/>
       <c r="C434" s="4"/>
@@ -12289,7 +12295,7 @@
       <c r="BD434" s="4"/>
       <c r="BE434" s="4"/>
     </row>
-    <row r="435" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:57" ht="15.95" customHeight="1">
       <c r="A435" s="4"/>
       <c r="B435" s="4"/>
       <c r="C435" s="4"/>
@@ -12313,7 +12319,7 @@
       <c r="BD435" s="4"/>
       <c r="BE435" s="4"/>
     </row>
-    <row r="436" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:57" ht="15.95" customHeight="1">
       <c r="A436" s="4"/>
       <c r="B436" s="4"/>
       <c r="C436" s="4"/>
@@ -12337,7 +12343,7 @@
       <c r="BD436" s="4"/>
       <c r="BE436" s="4"/>
     </row>
-    <row r="437" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:57" ht="15.95" customHeight="1">
       <c r="A437" s="4"/>
       <c r="B437" s="4"/>
       <c r="C437" s="4"/>
@@ -12361,7 +12367,7 @@
       <c r="BD437" s="4"/>
       <c r="BE437" s="4"/>
     </row>
-    <row r="438" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:57" ht="15.95" customHeight="1">
       <c r="A438" s="4"/>
       <c r="B438" s="4"/>
       <c r="C438" s="4"/>
@@ -12385,7 +12391,7 @@
       <c r="BD438" s="4"/>
       <c r="BE438" s="4"/>
     </row>
-    <row r="439" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:57" ht="15.95" customHeight="1">
       <c r="A439" s="4"/>
       <c r="B439" s="4"/>
       <c r="C439" s="4"/>
@@ -12409,7 +12415,7 @@
       <c r="BD439" s="4"/>
       <c r="BE439" s="4"/>
     </row>
-    <row r="440" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:57" ht="15.95" customHeight="1">
       <c r="A440" s="4"/>
       <c r="B440" s="4"/>
       <c r="C440" s="4"/>
@@ -12433,7 +12439,7 @@
       <c r="BD440" s="4"/>
       <c r="BE440" s="4"/>
     </row>
-    <row r="441" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:57" ht="15.95" customHeight="1">
       <c r="A441" s="4"/>
       <c r="B441" s="4"/>
       <c r="C441" s="4"/>
@@ -12457,7 +12463,7 @@
       <c r="BD441" s="4"/>
       <c r="BE441" s="4"/>
     </row>
-    <row r="442" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:57" ht="15.95" customHeight="1">
       <c r="A442" s="4"/>
       <c r="B442" s="4"/>
       <c r="C442" s="4"/>
@@ -12481,7 +12487,7 @@
       <c r="BD442" s="4"/>
       <c r="BE442" s="4"/>
     </row>
-    <row r="443" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:57" ht="15.95" customHeight="1">
       <c r="A443" s="4"/>
       <c r="B443" s="4"/>
       <c r="C443" s="4"/>
@@ -12505,7 +12511,7 @@
       <c r="BD443" s="4"/>
       <c r="BE443" s="4"/>
     </row>
-    <row r="444" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:57" ht="15.95" customHeight="1">
       <c r="A444" s="4"/>
       <c r="B444" s="4"/>
       <c r="C444" s="4"/>
@@ -12529,7 +12535,7 @@
       <c r="BD444" s="4"/>
       <c r="BE444" s="4"/>
     </row>
-    <row r="445" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:57" ht="15.95" customHeight="1">
       <c r="A445" s="4"/>
       <c r="B445" s="4"/>
       <c r="C445" s="4"/>
@@ -12553,7 +12559,7 @@
       <c r="BD445" s="4"/>
       <c r="BE445" s="4"/>
     </row>
-    <row r="446" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:57" ht="15.95" customHeight="1">
       <c r="A446" s="4"/>
       <c r="B446" s="4"/>
       <c r="C446" s="4"/>
@@ -12577,7 +12583,7 @@
       <c r="BD446" s="4"/>
       <c r="BE446" s="4"/>
     </row>
-    <row r="447" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:57" ht="15.95" customHeight="1">
       <c r="A447" s="4"/>
       <c r="B447" s="4"/>
       <c r="C447" s="4"/>
@@ -12601,7 +12607,7 @@
       <c r="BD447" s="4"/>
       <c r="BE447" s="4"/>
     </row>
-    <row r="448" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:57" ht="15.95" customHeight="1">
       <c r="A448" s="4"/>
       <c r="B448" s="4"/>
       <c r="C448" s="4"/>
@@ -12625,7 +12631,7 @@
       <c r="BD448" s="4"/>
       <c r="BE448" s="4"/>
     </row>
-    <row r="449" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:57" ht="15.95" customHeight="1">
       <c r="A449" s="4"/>
       <c r="B449" s="4"/>
       <c r="C449" s="4"/>
@@ -12649,7 +12655,7 @@
       <c r="BD449" s="4"/>
       <c r="BE449" s="4"/>
     </row>
-    <row r="450" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:57" ht="15.95" customHeight="1">
       <c r="A450" s="4"/>
       <c r="B450" s="4"/>
       <c r="C450" s="4"/>
@@ -12673,7 +12679,7 @@
       <c r="BD450" s="4"/>
       <c r="BE450" s="4"/>
     </row>
-    <row r="451" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:57" ht="15.95" customHeight="1">
       <c r="A451" s="4"/>
       <c r="B451" s="4"/>
       <c r="C451" s="4"/>
@@ -12697,7 +12703,7 @@
       <c r="BD451" s="4"/>
       <c r="BE451" s="4"/>
     </row>
-    <row r="452" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:57" ht="15.95" customHeight="1">
       <c r="A452" s="4"/>
       <c r="B452" s="4"/>
       <c r="C452" s="4"/>
@@ -12721,7 +12727,7 @@
       <c r="BD452" s="4"/>
       <c r="BE452" s="4"/>
     </row>
-    <row r="453" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:57" ht="15.95" customHeight="1">
       <c r="A453" s="4"/>
       <c r="B453" s="4"/>
       <c r="C453" s="4"/>
@@ -12745,7 +12751,7 @@
       <c r="BD453" s="4"/>
       <c r="BE453" s="4"/>
     </row>
-    <row r="454" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:57" ht="15.95" customHeight="1">
       <c r="A454" s="4"/>
       <c r="B454" s="4"/>
       <c r="C454" s="4"/>
@@ -12769,7 +12775,7 @@
       <c r="BD454" s="4"/>
       <c r="BE454" s="4"/>
     </row>
-    <row r="455" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:57" ht="15.95" customHeight="1">
       <c r="A455" s="4"/>
       <c r="B455" s="4"/>
       <c r="C455" s="4"/>
@@ -12793,7 +12799,7 @@
       <c r="BD455" s="4"/>
       <c r="BE455" s="4"/>
     </row>
-    <row r="456" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:57" ht="15.95" customHeight="1">
       <c r="A456" s="4"/>
       <c r="B456" s="4"/>
       <c r="C456" s="4"/>
@@ -12817,7 +12823,7 @@
       <c r="BD456" s="4"/>
       <c r="BE456" s="4"/>
     </row>
-    <row r="457" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:57" ht="15.95" customHeight="1">
       <c r="A457" s="4"/>
       <c r="B457" s="4"/>
       <c r="C457" s="4"/>
@@ -12841,7 +12847,7 @@
       <c r="BD457" s="4"/>
       <c r="BE457" s="4"/>
     </row>
-    <row r="458" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:57" ht="15.95" customHeight="1">
       <c r="A458" s="4"/>
       <c r="B458" s="4"/>
       <c r="C458" s="4"/>
@@ -12865,7 +12871,7 @@
       <c r="BD458" s="4"/>
       <c r="BE458" s="4"/>
     </row>
-    <row r="459" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:57" ht="15.95" customHeight="1">
       <c r="A459" s="4"/>
       <c r="B459" s="4"/>
       <c r="C459" s="4"/>
@@ -12889,7 +12895,7 @@
       <c r="BD459" s="4"/>
       <c r="BE459" s="4"/>
     </row>
-    <row r="460" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:57" ht="15.95" customHeight="1">
       <c r="A460" s="4"/>
       <c r="B460" s="4"/>
       <c r="C460" s="4"/>
@@ -12913,7 +12919,7 @@
       <c r="BD460" s="4"/>
       <c r="BE460" s="4"/>
     </row>
-    <row r="461" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:57" ht="15.95" customHeight="1">
       <c r="A461" s="4"/>
       <c r="B461" s="4"/>
       <c r="C461" s="4"/>
@@ -12937,7 +12943,7 @@
       <c r="BD461" s="4"/>
       <c r="BE461" s="4"/>
     </row>
-    <row r="462" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:57" ht="15.95" customHeight="1">
       <c r="A462" s="4"/>
       <c r="B462" s="4"/>
       <c r="C462" s="4"/>
@@ -12961,7 +12967,7 @@
       <c r="BD462" s="4"/>
       <c r="BE462" s="4"/>
     </row>
-    <row r="463" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:57" ht="15.95" customHeight="1">
       <c r="A463" s="4"/>
       <c r="B463" s="4"/>
       <c r="C463" s="4"/>
@@ -12985,7 +12991,7 @@
       <c r="BD463" s="4"/>
       <c r="BE463" s="4"/>
     </row>
-    <row r="464" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:57" ht="15.95" customHeight="1">
       <c r="A464" s="4"/>
       <c r="B464" s="4"/>
       <c r="C464" s="4"/>
@@ -13009,7 +13015,7 @@
       <c r="BD464" s="4"/>
       <c r="BE464" s="4"/>
     </row>
-    <row r="465" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:57" ht="15.95" customHeight="1">
       <c r="A465" s="4"/>
       <c r="B465" s="4"/>
       <c r="C465" s="4"/>
@@ -13033,7 +13039,7 @@
       <c r="BD465" s="4"/>
       <c r="BE465" s="4"/>
     </row>
-    <row r="466" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:57" ht="15.95" customHeight="1">
       <c r="A466" s="4"/>
       <c r="B466" s="4"/>
       <c r="C466" s="4"/>
@@ -13057,7 +13063,7 @@
       <c r="BD466" s="4"/>
       <c r="BE466" s="4"/>
     </row>
-    <row r="467" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:57" ht="15.95" customHeight="1">
       <c r="A467" s="4"/>
       <c r="B467" s="4"/>
       <c r="C467" s="4"/>
@@ -13081,7 +13087,7 @@
       <c r="BD467" s="4"/>
       <c r="BE467" s="4"/>
     </row>
-    <row r="468" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:57" ht="15.95" customHeight="1">
       <c r="A468" s="4"/>
       <c r="B468" s="4"/>
       <c r="C468" s="4"/>
@@ -13105,7 +13111,7 @@
       <c r="BD468" s="4"/>
       <c r="BE468" s="4"/>
     </row>
-    <row r="469" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:57" ht="15.95" customHeight="1">
       <c r="A469" s="4"/>
       <c r="B469" s="4"/>
       <c r="C469" s="4"/>
@@ -13129,7 +13135,7 @@
       <c r="BD469" s="4"/>
       <c r="BE469" s="4"/>
     </row>
-    <row r="470" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:57" ht="15.95" customHeight="1">
       <c r="A470" s="4"/>
       <c r="B470" s="4"/>
       <c r="C470" s="4"/>
@@ -13153,7 +13159,7 @@
       <c r="BD470" s="4"/>
       <c r="BE470" s="4"/>
     </row>
-    <row r="471" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:57" ht="15.95" customHeight="1">
       <c r="A471" s="4"/>
       <c r="B471" s="4"/>
       <c r="C471" s="4"/>
@@ -13177,7 +13183,7 @@
       <c r="BD471" s="4"/>
       <c r="BE471" s="4"/>
     </row>
-    <row r="472" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:57" ht="15.95" customHeight="1">
       <c r="A472" s="4"/>
       <c r="B472" s="4"/>
       <c r="C472" s="4"/>
@@ -13201,7 +13207,7 @@
       <c r="BD472" s="4"/>
       <c r="BE472" s="4"/>
     </row>
-    <row r="473" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:57" ht="15.95" customHeight="1">
       <c r="A473" s="4"/>
       <c r="B473" s="4"/>
       <c r="C473" s="4"/>
@@ -13225,7 +13231,7 @@
       <c r="BD473" s="4"/>
       <c r="BE473" s="4"/>
     </row>
-    <row r="474" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:57" ht="15.95" customHeight="1">
       <c r="A474" s="4"/>
       <c r="B474" s="4"/>
       <c r="C474" s="4"/>
@@ -13249,7 +13255,7 @@
       <c r="BD474" s="4"/>
       <c r="BE474" s="4"/>
     </row>
-    <row r="475" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:57" ht="15.95" customHeight="1">
       <c r="A475" s="4"/>
       <c r="B475" s="4"/>
       <c r="C475" s="4"/>
@@ -13273,7 +13279,7 @@
       <c r="BD475" s="4"/>
       <c r="BE475" s="4"/>
     </row>
-    <row r="476" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:57" ht="15.95" customHeight="1">
       <c r="A476" s="4"/>
       <c r="B476" s="4"/>
       <c r="C476" s="4"/>
@@ -13297,7 +13303,7 @@
       <c r="BD476" s="4"/>
       <c r="BE476" s="4"/>
     </row>
-    <row r="477" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:57" ht="15.95" customHeight="1">
       <c r="A477" s="4"/>
       <c r="B477" s="4"/>
       <c r="C477" s="4"/>
@@ -13321,7 +13327,7 @@
       <c r="BD477" s="4"/>
       <c r="BE477" s="4"/>
     </row>
-    <row r="478" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:57" ht="15.95" customHeight="1">
       <c r="A478" s="4"/>
       <c r="B478" s="4"/>
       <c r="C478" s="4"/>
@@ -13345,7 +13351,7 @@
       <c r="BD478" s="4"/>
       <c r="BE478" s="4"/>
     </row>
-    <row r="479" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:57" ht="15.95" customHeight="1">
       <c r="A479" s="4"/>
       <c r="B479" s="4"/>
       <c r="C479" s="4"/>
@@ -13369,7 +13375,7 @@
       <c r="BD479" s="4"/>
       <c r="BE479" s="4"/>
     </row>
-    <row r="480" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:57" ht="15.95" customHeight="1">
       <c r="A480" s="4"/>
       <c r="B480" s="4"/>
       <c r="C480" s="4"/>
@@ -13393,7 +13399,7 @@
       <c r="BD480" s="4"/>
       <c r="BE480" s="4"/>
     </row>
-    <row r="481" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:57" ht="15.95" customHeight="1">
       <c r="A481" s="4"/>
       <c r="B481" s="4"/>
       <c r="C481" s="4"/>
@@ -13417,7 +13423,7 @@
       <c r="BD481" s="4"/>
       <c r="BE481" s="4"/>
     </row>
-    <row r="482" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:57" ht="15.95" customHeight="1">
       <c r="A482" s="4"/>
       <c r="B482" s="4"/>
       <c r="C482" s="4"/>
@@ -13441,7 +13447,7 @@
       <c r="BD482" s="4"/>
       <c r="BE482" s="4"/>
     </row>
-    <row r="483" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:57" ht="15.95" customHeight="1">
       <c r="A483" s="4"/>
       <c r="B483" s="4"/>
       <c r="C483" s="4"/>
@@ -13465,7 +13471,7 @@
       <c r="BD483" s="4"/>
       <c r="BE483" s="4"/>
     </row>
-    <row r="484" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:57" ht="15.95" customHeight="1">
       <c r="A484" s="4"/>
       <c r="B484" s="4"/>
       <c r="C484" s="4"/>
@@ -13489,7 +13495,7 @@
       <c r="BD484" s="4"/>
       <c r="BE484" s="4"/>
     </row>
-    <row r="485" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:57" ht="15.95" customHeight="1">
       <c r="A485" s="4"/>
       <c r="B485" s="4"/>
       <c r="C485" s="4"/>
@@ -13513,7 +13519,7 @@
       <c r="BD485" s="4"/>
       <c r="BE485" s="4"/>
     </row>
-    <row r="486" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:57" ht="15.95" customHeight="1">
       <c r="A486" s="4"/>
       <c r="B486" s="4"/>
       <c r="C486" s="4"/>
@@ -13537,7 +13543,7 @@
       <c r="BD486" s="4"/>
       <c r="BE486" s="4"/>
     </row>
-    <row r="487" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:57" ht="15.95" customHeight="1">
       <c r="A487" s="4"/>
       <c r="B487" s="4"/>
       <c r="C487" s="4"/>
@@ -13561,7 +13567,7 @@
       <c r="BD487" s="4"/>
       <c r="BE487" s="4"/>
     </row>
-    <row r="488" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:57" ht="15.95" customHeight="1">
       <c r="A488" s="4"/>
       <c r="B488" s="4"/>
       <c r="C488" s="4"/>
@@ -13585,7 +13591,7 @@
       <c r="BD488" s="4"/>
       <c r="BE488" s="4"/>
     </row>
-    <row r="489" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:57" ht="15.95" customHeight="1">
       <c r="A489" s="4"/>
       <c r="B489" s="4"/>
       <c r="C489" s="4"/>
@@ -13609,7 +13615,7 @@
       <c r="BD489" s="4"/>
       <c r="BE489" s="4"/>
     </row>
-    <row r="490" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:57" ht="15.95" customHeight="1">
       <c r="A490" s="4"/>
       <c r="B490" s="4"/>
       <c r="C490" s="4"/>
@@ -13633,7 +13639,7 @@
       <c r="BD490" s="4"/>
       <c r="BE490" s="4"/>
     </row>
-    <row r="491" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:57" ht="15.95" customHeight="1">
       <c r="A491" s="4"/>
       <c r="B491" s="4"/>
       <c r="C491" s="4"/>
@@ -13657,7 +13663,7 @@
       <c r="BD491" s="4"/>
       <c r="BE491" s="4"/>
     </row>
-    <row r="492" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:57" ht="15.95" customHeight="1">
       <c r="A492" s="4"/>
       <c r="B492" s="4"/>
       <c r="C492" s="4"/>
@@ -13681,7 +13687,7 @@
       <c r="BD492" s="4"/>
       <c r="BE492" s="4"/>
     </row>
-    <row r="493" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:57" ht="15.95" customHeight="1">
       <c r="A493" s="4"/>
       <c r="B493" s="4"/>
       <c r="C493" s="4"/>
@@ -13705,7 +13711,7 @@
       <c r="BD493" s="4"/>
       <c r="BE493" s="4"/>
     </row>
-    <row r="494" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:57" ht="15.95" customHeight="1">
       <c r="A494" s="4"/>
       <c r="B494" s="4"/>
       <c r="C494" s="4"/>
@@ -13729,7 +13735,7 @@
       <c r="BD494" s="4"/>
       <c r="BE494" s="4"/>
     </row>
-    <row r="495" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:57" ht="15.95" customHeight="1">
       <c r="A495" s="4"/>
       <c r="B495" s="4"/>
       <c r="C495" s="4"/>
@@ -13753,7 +13759,7 @@
       <c r="BD495" s="4"/>
       <c r="BE495" s="4"/>
     </row>
-    <row r="496" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:57" ht="15.95" customHeight="1">
       <c r="A496" s="4"/>
       <c r="B496" s="4"/>
       <c r="C496" s="4"/>
@@ -13777,7 +13783,7 @@
       <c r="BD496" s="4"/>
       <c r="BE496" s="4"/>
     </row>
-    <row r="497" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:57" ht="15.95" customHeight="1">
       <c r="A497" s="4"/>
       <c r="B497" s="4"/>
       <c r="C497" s="4"/>
@@ -13801,7 +13807,7 @@
       <c r="BD497" s="4"/>
       <c r="BE497" s="4"/>
     </row>
-    <row r="498" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:57" ht="15.95" customHeight="1">
       <c r="A498" s="4"/>
       <c r="B498" s="4"/>
       <c r="C498" s="4"/>
@@ -13825,7 +13831,7 @@
       <c r="BD498" s="4"/>
       <c r="BE498" s="4"/>
     </row>
-    <row r="499" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:57" ht="15.95" customHeight="1">
       <c r="A499" s="4"/>
       <c r="B499" s="4"/>
       <c r="C499" s="4"/>
@@ -13849,7 +13855,7 @@
       <c r="BD499" s="4"/>
       <c r="BE499" s="4"/>
     </row>
-    <row r="500" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:57" ht="15.95" customHeight="1">
       <c r="A500" s="4"/>
       <c r="B500" s="4"/>
       <c r="C500" s="4"/>
@@ -13873,7 +13879,7 @@
       <c r="BD500" s="4"/>
       <c r="BE500" s="4"/>
     </row>
-    <row r="501" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:57" ht="15.95" customHeight="1">
       <c r="A501" s="4"/>
       <c r="B501" s="4"/>
       <c r="C501" s="4"/>
@@ -13897,7 +13903,7 @@
       <c r="BD501" s="4"/>
       <c r="BE501" s="4"/>
     </row>
-    <row r="502" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:57" ht="15.95" customHeight="1">
       <c r="A502" s="4"/>
       <c r="B502" s="4"/>
       <c r="C502" s="4"/>
@@ -13921,7 +13927,7 @@
       <c r="BD502" s="4"/>
       <c r="BE502" s="4"/>
     </row>
-    <row r="503" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:57" ht="15.95" customHeight="1">
       <c r="A503" s="4"/>
       <c r="B503" s="4"/>
       <c r="C503" s="4"/>
@@ -13945,7 +13951,7 @@
       <c r="BD503" s="4"/>
       <c r="BE503" s="4"/>
     </row>
-    <row r="504" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:57" ht="15.95" customHeight="1">
       <c r="A504" s="4"/>
       <c r="B504" s="4"/>
       <c r="C504" s="4"/>
@@ -13969,7 +13975,7 @@
       <c r="BD504" s="4"/>
       <c r="BE504" s="4"/>
     </row>
-    <row r="505" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:57" ht="15.95" customHeight="1">
       <c r="A505" s="4"/>
       <c r="B505" s="4"/>
       <c r="C505" s="4"/>
@@ -13993,7 +13999,7 @@
       <c r="BD505" s="4"/>
       <c r="BE505" s="4"/>
     </row>
-    <row r="506" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:57" ht="15.95" customHeight="1">
       <c r="A506" s="4"/>
       <c r="B506" s="4"/>
       <c r="C506" s="4"/>
@@ -14017,7 +14023,7 @@
       <c r="BD506" s="4"/>
       <c r="BE506" s="4"/>
     </row>
-    <row r="507" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:57" ht="15.95" customHeight="1">
       <c r="A507" s="4"/>
       <c r="B507" s="4"/>
       <c r="C507" s="4"/>
@@ -14041,7 +14047,7 @@
       <c r="BD507" s="4"/>
       <c r="BE507" s="4"/>
     </row>
-    <row r="508" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:57" ht="15.95" customHeight="1">
       <c r="A508" s="4"/>
       <c r="B508" s="4"/>
       <c r="C508" s="4"/>
@@ -14065,7 +14071,7 @@
       <c r="BD508" s="4"/>
       <c r="BE508" s="4"/>
     </row>
-    <row r="509" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:57" ht="15.95" customHeight="1">
       <c r="A509" s="4"/>
       <c r="B509" s="4"/>
       <c r="C509" s="4"/>
@@ -14089,7 +14095,7 @@
       <c r="BD509" s="4"/>
       <c r="BE509" s="4"/>
     </row>
-    <row r="510" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:57" ht="15.95" customHeight="1">
       <c r="A510" s="4"/>
       <c r="B510" s="4"/>
       <c r="C510" s="4"/>
@@ -14113,7 +14119,7 @@
       <c r="BD510" s="4"/>
       <c r="BE510" s="4"/>
     </row>
-    <row r="511" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:57" ht="15.95" customHeight="1">
       <c r="A511" s="4"/>
       <c r="B511" s="4"/>
       <c r="C511" s="4"/>
@@ -14137,7 +14143,7 @@
       <c r="BD511" s="4"/>
       <c r="BE511" s="4"/>
     </row>
-    <row r="512" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:57" ht="15.95" customHeight="1">
       <c r="A512" s="4"/>
       <c r="B512" s="4"/>
       <c r="C512" s="4"/>
@@ -14161,7 +14167,7 @@
       <c r="BD512" s="4"/>
       <c r="BE512" s="4"/>
     </row>
-    <row r="513" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:57" ht="15.95" customHeight="1">
       <c r="A513" s="4"/>
       <c r="B513" s="4"/>
       <c r="C513" s="4"/>
@@ -14185,7 +14191,7 @@
       <c r="BD513" s="4"/>
       <c r="BE513" s="4"/>
     </row>
-    <row r="514" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:57" ht="15.95" customHeight="1">
       <c r="A514" s="4"/>
       <c r="B514" s="4"/>
       <c r="C514" s="4"/>
@@ -14209,7 +14215,7 @@
       <c r="BD514" s="4"/>
       <c r="BE514" s="4"/>
     </row>
-    <row r="515" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:57" ht="15.95" customHeight="1">
       <c r="A515" s="4"/>
       <c r="B515" s="4"/>
       <c r="C515" s="4"/>
@@ -14233,7 +14239,7 @@
       <c r="BD515" s="4"/>
       <c r="BE515" s="4"/>
     </row>
-    <row r="516" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:57" ht="15.95" customHeight="1">
       <c r="A516" s="4"/>
       <c r="B516" s="4"/>
       <c r="C516" s="4"/>
@@ -14257,7 +14263,7 @@
       <c r="BD516" s="4"/>
       <c r="BE516" s="4"/>
     </row>
-    <row r="517" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:57" ht="15.95" customHeight="1">
       <c r="A517" s="4"/>
       <c r="B517" s="4"/>
       <c r="C517" s="4"/>
@@ -14281,7 +14287,7 @@
       <c r="BD517" s="4"/>
       <c r="BE517" s="4"/>
     </row>
-    <row r="518" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:57" ht="15.95" customHeight="1">
       <c r="A518" s="4"/>
       <c r="B518" s="4"/>
       <c r="C518" s="4"/>
@@ -14305,7 +14311,7 @@
       <c r="BD518" s="4"/>
       <c r="BE518" s="4"/>
     </row>
-    <row r="519" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:57" ht="15.95" customHeight="1">
       <c r="A519" s="4"/>
       <c r="B519" s="4"/>
       <c r="C519" s="4"/>
@@ -14329,7 +14335,7 @@
       <c r="BD519" s="4"/>
       <c r="BE519" s="4"/>
     </row>
-    <row r="520" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:57" ht="15.95" customHeight="1">
       <c r="A520" s="4"/>
       <c r="B520" s="4"/>
       <c r="C520" s="4"/>
@@ -14353,7 +14359,7 @@
       <c r="BD520" s="4"/>
       <c r="BE520" s="4"/>
     </row>
-    <row r="521" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:57" ht="15.95" customHeight="1">
       <c r="A521" s="4"/>
       <c r="B521" s="4"/>
       <c r="C521" s="4"/>
@@ -14377,7 +14383,7 @@
       <c r="BD521" s="4"/>
       <c r="BE521" s="4"/>
     </row>
-    <row r="522" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:57" ht="15.95" customHeight="1">
       <c r="A522" s="4"/>
       <c r="B522" s="4"/>
       <c r="C522" s="4"/>
@@ -14401,7 +14407,7 @@
       <c r="BD522" s="4"/>
       <c r="BE522" s="4"/>
     </row>
-    <row r="523" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:57" ht="15.95" customHeight="1">
       <c r="A523" s="4"/>
       <c r="B523" s="4"/>
       <c r="C523" s="4"/>
@@ -14425,7 +14431,7 @@
       <c r="BD523" s="4"/>
       <c r="BE523" s="4"/>
     </row>
-    <row r="524" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:57" ht="15.95" customHeight="1">
       <c r="A524" s="4"/>
       <c r="B524" s="4"/>
       <c r="C524" s="4"/>
@@ -14449,7 +14455,7 @@
       <c r="BD524" s="4"/>
       <c r="BE524" s="4"/>
     </row>
-    <row r="525" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:57" ht="15.95" customHeight="1">
       <c r="A525" s="4"/>
       <c r="B525" s="4"/>
       <c r="C525" s="4"/>
@@ -14473,7 +14479,7 @@
       <c r="BD525" s="4"/>
       <c r="BE525" s="4"/>
     </row>
-    <row r="526" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:57" ht="15.95" customHeight="1">
       <c r="A526" s="4"/>
       <c r="B526" s="4"/>
       <c r="C526" s="4"/>
@@ -14497,7 +14503,7 @@
       <c r="BD526" s="4"/>
       <c r="BE526" s="4"/>
     </row>
-    <row r="527" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:57" ht="15.95" customHeight="1">
       <c r="A527" s="4"/>
       <c r="B527" s="4"/>
       <c r="C527" s="4"/>
@@ -14521,7 +14527,7 @@
       <c r="BD527" s="4"/>
       <c r="BE527" s="4"/>
     </row>
-    <row r="528" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:57" ht="15.95" customHeight="1">
       <c r="A528" s="4"/>
       <c r="B528" s="4"/>
       <c r="C528" s="4"/>
@@ -14545,7 +14551,7 @@
       <c r="BD528" s="4"/>
       <c r="BE528" s="4"/>
     </row>
-    <row r="529" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:57" ht="15.95" customHeight="1">
       <c r="A529" s="4"/>
       <c r="B529" s="4"/>
       <c r="C529" s="4"/>
@@ -14569,7 +14575,7 @@
       <c r="BD529" s="4"/>
       <c r="BE529" s="4"/>
     </row>
-    <row r="530" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:57" ht="15.95" customHeight="1">
       <c r="A530" s="4"/>
       <c r="B530" s="4"/>
       <c r="C530" s="4"/>
@@ -14593,7 +14599,7 @@
       <c r="BD530" s="4"/>
       <c r="BE530" s="4"/>
     </row>
-    <row r="531" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:57" ht="15.95" customHeight="1">
       <c r="A531" s="4"/>
       <c r="B531" s="4"/>
       <c r="C531" s="4"/>
@@ -14617,7 +14623,7 @@
       <c r="BD531" s="4"/>
       <c r="BE531" s="4"/>
     </row>
-    <row r="532" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:57" ht="15.95" customHeight="1">
       <c r="A532" s="4"/>
       <c r="B532" s="4"/>
       <c r="C532" s="4"/>
@@ -14641,7 +14647,7 @@
       <c r="BD532" s="4"/>
       <c r="BE532" s="4"/>
     </row>
-    <row r="533" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:57" ht="15.95" customHeight="1">
       <c r="A533" s="4"/>
       <c r="B533" s="4"/>
       <c r="C533" s="4"/>
@@ -14665,7 +14671,7 @@
       <c r="BD533" s="4"/>
       <c r="BE533" s="4"/>
     </row>
-    <row r="534" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:57" ht="15.95" customHeight="1">
       <c r="A534" s="4"/>
       <c r="B534" s="4"/>
       <c r="C534" s="4"/>
@@ -14689,7 +14695,7 @@
       <c r="BD534" s="4"/>
       <c r="BE534" s="4"/>
     </row>
-    <row r="535" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:57" ht="15.95" customHeight="1">
       <c r="A535" s="4"/>
       <c r="B535" s="4"/>
       <c r="C535" s="4"/>
@@ -14713,7 +14719,7 @@
       <c r="BD535" s="4"/>
       <c r="BE535" s="4"/>
     </row>
-    <row r="536" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:57" ht="15.95" customHeight="1">
       <c r="A536" s="4"/>
       <c r="B536" s="4"/>
       <c r="C536" s="4"/>
@@ -14737,7 +14743,7 @@
       <c r="BD536" s="4"/>
       <c r="BE536" s="4"/>
     </row>
-    <row r="537" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:57" ht="15.95" customHeight="1">
       <c r="A537" s="4"/>
       <c r="B537" s="4"/>
       <c r="C537" s="4"/>
@@ -14761,7 +14767,7 @@
       <c r="BD537" s="4"/>
       <c r="BE537" s="4"/>
     </row>
-    <row r="538" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:57" ht="15.95" customHeight="1">
       <c r="A538" s="4"/>
       <c r="B538" s="4"/>
       <c r="C538" s="4"/>
@@ -14785,7 +14791,7 @@
       <c r="BD538" s="4"/>
       <c r="BE538" s="4"/>
     </row>
-    <row r="539" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:57" ht="15.95" customHeight="1">
       <c r="A539" s="4"/>
       <c r="B539" s="4"/>
       <c r="C539" s="4"/>
@@ -14809,7 +14815,7 @@
       <c r="BD539" s="4"/>
       <c r="BE539" s="4"/>
     </row>
-    <row r="540" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:57" ht="15.95" customHeight="1">
       <c r="A540" s="4"/>
       <c r="B540" s="4"/>
       <c r="C540" s="4"/>
@@ -14833,7 +14839,7 @@
       <c r="BD540" s="4"/>
       <c r="BE540" s="4"/>
     </row>
-    <row r="541" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:57" ht="15.95" customHeight="1">
       <c r="A541" s="4"/>
       <c r="B541" s="4"/>
       <c r="C541" s="4"/>
@@ -14857,7 +14863,7 @@
       <c r="BD541" s="4"/>
       <c r="BE541" s="4"/>
     </row>
-    <row r="542" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:57" ht="15.95" customHeight="1">
       <c r="A542" s="4"/>
       <c r="B542" s="4"/>
       <c r="C542" s="4"/>
@@ -14881,7 +14887,7 @@
       <c r="BD542" s="4"/>
       <c r="BE542" s="4"/>
     </row>
-    <row r="543" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:57" ht="15.95" customHeight="1">
       <c r="A543" s="4"/>
       <c r="B543" s="4"/>
       <c r="C543" s="4"/>
@@ -14905,7 +14911,7 @@
       <c r="BD543" s="4"/>
       <c r="BE543" s="4"/>
     </row>
-    <row r="544" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:57" ht="15.95" customHeight="1">
       <c r="A544" s="4"/>
       <c r="B544" s="4"/>
       <c r="C544" s="4"/>
@@ -14929,7 +14935,7 @@
       <c r="BD544" s="4"/>
       <c r="BE544" s="4"/>
     </row>
-    <row r="545" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:57" ht="15.95" customHeight="1">
       <c r="A545" s="4"/>
       <c r="B545" s="4"/>
       <c r="C545" s="4"/>
@@ -14953,7 +14959,7 @@
       <c r="BD545" s="4"/>
       <c r="BE545" s="4"/>
     </row>
-    <row r="546" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:57" ht="15.95" customHeight="1">
       <c r="A546" s="4"/>
       <c r="B546" s="4"/>
       <c r="C546" s="4"/>
@@ -14977,7 +14983,7 @@
       <c r="BD546" s="4"/>
       <c r="BE546" s="4"/>
     </row>
-    <row r="547" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:57" ht="15.95" customHeight="1">
       <c r="A547" s="4"/>
       <c r="B547" s="4"/>
       <c r="C547" s="4"/>
@@ -15001,7 +15007,7 @@
       <c r="BD547" s="4"/>
       <c r="BE547" s="4"/>
     </row>
-    <row r="548" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:57" ht="15.95" customHeight="1">
       <c r="A548" s="4"/>
       <c r="B548" s="4"/>
       <c r="C548" s="4"/>
@@ -15025,7 +15031,7 @@
       <c r="BD548" s="4"/>
       <c r="BE548" s="4"/>
     </row>
-    <row r="549" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:57" ht="15.95" customHeight="1">
       <c r="A549" s="4"/>
       <c r="B549" s="4"/>
       <c r="C549" s="4"/>
@@ -15049,7 +15055,7 @@
       <c r="BD549" s="4"/>
       <c r="BE549" s="4"/>
     </row>
-    <row r="550" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:57" ht="15.95" customHeight="1">
       <c r="A550" s="4"/>
       <c r="B550" s="4"/>
       <c r="C550" s="4"/>
@@ -15073,7 +15079,7 @@
       <c r="BD550" s="4"/>
       <c r="BE550" s="4"/>
     </row>
-    <row r="551" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:57" ht="15.95" customHeight="1">
       <c r="A551" s="4"/>
       <c r="B551" s="4"/>
       <c r="C551" s="4"/>
@@ -15097,7 +15103,7 @@
       <c r="BD551" s="4"/>
       <c r="BE551" s="4"/>
     </row>
-    <row r="552" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:57" ht="15.95" customHeight="1">
       <c r="A552" s="4"/>
       <c r="B552" s="4"/>
       <c r="C552" s="4"/>
@@ -15121,7 +15127,7 @@
       <c r="BD552" s="4"/>
       <c r="BE552" s="4"/>
     </row>
-    <row r="553" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:57" ht="15.95" customHeight="1">
       <c r="A553" s="4"/>
       <c r="B553" s="4"/>
       <c r="C553" s="4"/>
@@ -15145,7 +15151,7 @@
       <c r="BD553" s="4"/>
       <c r="BE553" s="4"/>
     </row>
-    <row r="554" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:57" ht="15.95" customHeight="1">
       <c r="A554" s="4"/>
       <c r="B554" s="4"/>
       <c r="C554" s="4"/>
@@ -15169,7 +15175,7 @@
       <c r="BD554" s="4"/>
       <c r="BE554" s="4"/>
     </row>
-    <row r="555" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:57" ht="15.95" customHeight="1">
       <c r="A555" s="4"/>
       <c r="B555" s="4"/>
       <c r="C555" s="4"/>
@@ -15193,7 +15199,7 @@
       <c r="BD555" s="4"/>
       <c r="BE555" s="4"/>
     </row>
-    <row r="556" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:57" ht="15.95" customHeight="1">
       <c r="A556" s="4"/>
       <c r="B556" s="4"/>
       <c r="C556" s="4"/>
@@ -15217,7 +15223,7 @@
       <c r="BD556" s="4"/>
       <c r="BE556" s="4"/>
     </row>
-    <row r="557" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:57" ht="15.95" customHeight="1">
       <c r="A557" s="4"/>
       <c r="B557" s="4"/>
       <c r="C557" s="4"/>
@@ -15241,7 +15247,7 @@
       <c r="BD557" s="4"/>
       <c r="BE557" s="4"/>
     </row>
-    <row r="558" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:57" ht="15.95" customHeight="1">
       <c r="A558" s="4"/>
       <c r="B558" s="4"/>
       <c r="C558" s="4"/>
@@ -15265,7 +15271,7 @@
       <c r="BD558" s="4"/>
       <c r="BE558" s="4"/>
     </row>
-    <row r="559" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:57" ht="15.95" customHeight="1">
       <c r="A559" s="4"/>
       <c r="B559" s="4"/>
       <c r="C559" s="4"/>
@@ -15289,7 +15295,7 @@
       <c r="BD559" s="4"/>
       <c r="BE559" s="4"/>
     </row>
-    <row r="560" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:57" ht="15.95" customHeight="1">
       <c r="A560" s="4"/>
       <c r="B560" s="4"/>
       <c r="C560" s="4"/>
@@ -15313,7 +15319,7 @@
       <c r="BD560" s="4"/>
       <c r="BE560" s="4"/>
     </row>
-    <row r="561" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:57" ht="15.95" customHeight="1">
       <c r="A561" s="4"/>
       <c r="B561" s="4"/>
       <c r="C561" s="4"/>
@@ -15337,7 +15343,7 @@
       <c r="BD561" s="4"/>
       <c r="BE561" s="4"/>
     </row>
-    <row r="562" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:57" ht="15.95" customHeight="1">
       <c r="A562" s="4"/>
       <c r="B562" s="4"/>
       <c r="C562" s="4"/>
@@ -15361,7 +15367,7 @@
       <c r="BD562" s="4"/>
       <c r="BE562" s="4"/>
     </row>
-    <row r="563" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:57" ht="15.95" customHeight="1">
       <c r="A563" s="4"/>
       <c r="B563" s="4"/>
       <c r="C563" s="4"/>
@@ -15385,7 +15391,7 @@
       <c r="BD563" s="4"/>
       <c r="BE563" s="4"/>
     </row>
-    <row r="564" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:57" ht="15.95" customHeight="1">
       <c r="A564" s="4"/>
       <c r="B564" s="4"/>
       <c r="C564" s="4"/>
@@ -15409,7 +15415,7 @@
       <c r="BD564" s="4"/>
       <c r="BE564" s="4"/>
     </row>
-    <row r="565" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:57" ht="15.95" customHeight="1">
       <c r="A565" s="4"/>
       <c r="B565" s="4"/>
       <c r="C565" s="4"/>
@@ -15433,7 +15439,7 @@
       <c r="BD565" s="4"/>
       <c r="BE565" s="4"/>
     </row>
-    <row r="566" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:57" ht="15.95" customHeight="1">
       <c r="A566" s="4"/>
       <c r="B566" s="4"/>
       <c r="C566" s="4"/>
@@ -15457,7 +15463,7 @@
       <c r="BD566" s="4"/>
       <c r="BE566" s="4"/>
     </row>
-    <row r="567" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:57" ht="15.95" customHeight="1">
       <c r="A567" s="4"/>
       <c r="B567" s="4"/>
       <c r="C567" s="4"/>
@@ -15481,7 +15487,7 @@
       <c r="BD567" s="4"/>
       <c r="BE567" s="4"/>
     </row>
-    <row r="568" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:57" ht="15.95" customHeight="1">
       <c r="A568" s="4"/>
       <c r="B568" s="4"/>
       <c r="C568" s="4"/>
@@ -15505,7 +15511,7 @@
       <c r="BD568" s="4"/>
       <c r="BE568" s="4"/>
     </row>
-    <row r="569" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:57" ht="15.95" customHeight="1">
       <c r="A569" s="4"/>
       <c r="B569" s="4"/>
       <c r="C569" s="4"/>
@@ -15529,7 +15535,7 @@
       <c r="BD569" s="4"/>
       <c r="BE569" s="4"/>
     </row>
-    <row r="570" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:57" ht="15.95" customHeight="1">
       <c r="A570" s="4"/>
       <c r="B570" s="4"/>
       <c r="C570" s="4"/>
@@ -15553,7 +15559,7 @@
       <c r="BD570" s="4"/>
       <c r="BE570" s="4"/>
     </row>
-    <row r="571" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:57" ht="15.95" customHeight="1">
       <c r="A571" s="4"/>
       <c r="B571" s="4"/>
       <c r="C571" s="4"/>
@@ -15577,7 +15583,7 @@
       <c r="BD571" s="4"/>
       <c r="BE571" s="4"/>
     </row>
-    <row r="572" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:57" ht="15.95" customHeight="1">
       <c r="A572" s="4"/>
       <c r="B572" s="4"/>
       <c r="C572" s="4"/>
@@ -15601,7 +15607,7 @@
       <c r="BD572" s="4"/>
       <c r="BE572" s="4"/>
     </row>
-    <row r="573" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:57" ht="15.95" customHeight="1">
       <c r="A573" s="4"/>
       <c r="B573" s="4"/>
       <c r="C573" s="4"/>
@@ -15625,7 +15631,7 @@
       <c r="BD573" s="4"/>
       <c r="BE573" s="4"/>
     </row>
-    <row r="574" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:57" ht="15.95" customHeight="1">
       <c r="A574" s="4"/>
       <c r="B574" s="4"/>
       <c r="C574" s="4"/>
@@ -15649,7 +15655,7 @@
       <c r="BD574" s="4"/>
       <c r="BE574" s="4"/>
     </row>
-    <row r="575" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:57" ht="15.95" customHeight="1">
       <c r="A575" s="4"/>
       <c r="B575" s="4"/>
       <c r="C575" s="4"/>
@@ -15673,7 +15679,7 @@
       <c r="BD575" s="4"/>
       <c r="BE575" s="4"/>
     </row>
-    <row r="576" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:57" ht="15.95" customHeight="1">
       <c r="A576" s="4"/>
       <c r="B576" s="4"/>
       <c r="C576" s="4"/>
@@ -15697,7 +15703,7 @@
       <c r="BD576" s="4"/>
       <c r="BE576" s="4"/>
     </row>
-    <row r="577" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:57" ht="15.95" customHeight="1">
       <c r="A577" s="4"/>
       <c r="B577" s="4"/>
       <c r="C577" s="4"/>
@@ -15721,7 +15727,7 @@
       <c r="BD577" s="4"/>
       <c r="BE577" s="4"/>
     </row>
-    <row r="578" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:57" ht="15.95" customHeight="1">
       <c r="A578" s="4"/>
       <c r="B578" s="4"/>
       <c r="C578" s="4"/>
@@ -15745,7 +15751,7 @@
       <c r="BD578" s="4"/>
       <c r="BE578" s="4"/>
     </row>
-    <row r="579" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:57" ht="15.95" customHeight="1">
       <c r="A579" s="4"/>
       <c r="B579" s="4"/>
       <c r="C579" s="4"/>
@@ -15769,7 +15775,7 @@
       <c r="BD579" s="4"/>
       <c r="BE579" s="4"/>
     </row>
-    <row r="580" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:57" ht="15.95" customHeight="1">
       <c r="A580" s="4"/>
       <c r="B580" s="4"/>
       <c r="C580" s="4"/>
@@ -15793,7 +15799,7 @@
       <c r="BD580" s="4"/>
       <c r="BE580" s="4"/>
     </row>
-    <row r="581" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:57" ht="15.95" customHeight="1">
       <c r="A581" s="4"/>
       <c r="B581" s="4"/>
       <c r="C581" s="4"/>
@@ -15817,7 +15823,7 @@
       <c r="BD581" s="4"/>
       <c r="BE581" s="4"/>
     </row>
-    <row r="582" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:57" ht="15.95" customHeight="1">
       <c r="A582" s="4"/>
       <c r="B582" s="4"/>
       <c r="C582" s="4"/>
@@ -15841,7 +15847,7 @@
       <c r="BD582" s="4"/>
       <c r="BE582" s="4"/>
     </row>
-    <row r="583" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:57" ht="15.95" customHeight="1">
       <c r="A583" s="4"/>
       <c r="B583" s="4"/>
       <c r="C583" s="4"/>
@@ -15865,7 +15871,7 @@
       <c r="BD583" s="4"/>
       <c r="BE583" s="4"/>
     </row>
-    <row r="584" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:57" ht="15.95" customHeight="1">
       <c r="A584" s="4"/>
       <c r="B584" s="4"/>
       <c r="C584" s="4"/>
@@ -15889,7 +15895,7 @@
       <c r="BD584" s="4"/>
       <c r="BE584" s="4"/>
     </row>
-    <row r="585" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:57" ht="15.95" customHeight="1">
       <c r="A585" s="4"/>
       <c r="B585" s="4"/>
       <c r="C585" s="4"/>
@@ -15913,7 +15919,7 @@
       <c r="BD585" s="4"/>
       <c r="BE585" s="4"/>
     </row>
-    <row r="586" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:57" ht="15.95" customHeight="1">
       <c r="A586" s="4"/>
       <c r="B586" s="4"/>
       <c r="C586" s="4"/>
@@ -15937,7 +15943,7 @@
       <c r="BD586" s="4"/>
       <c r="BE586" s="4"/>
     </row>
-    <row r="587" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:57" ht="15.95" customHeight="1">
       <c r="A587" s="4"/>
       <c r="B587" s="4"/>
       <c r="C587" s="4"/>
@@ -15961,7 +15967,7 @@
       <c r="BD587" s="4"/>
       <c r="BE587" s="4"/>
     </row>
-    <row r="588" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:57" ht="15.95" customHeight="1">
       <c r="A588" s="4"/>
       <c r="B588" s="4"/>
       <c r="C588" s="4"/>
@@ -15985,7 +15991,7 @@
       <c r="BD588" s="4"/>
       <c r="BE588" s="4"/>
     </row>
-    <row r="589" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:57" ht="15.95" customHeight="1">
       <c r="A589" s="4"/>
       <c r="B589" s="4"/>
       <c r="C589" s="4"/>
@@ -16009,7 +16015,7 @@
       <c r="BD589" s="4"/>
       <c r="BE589" s="4"/>
     </row>
-    <row r="590" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:57" ht="15.95" customHeight="1">
       <c r="A590" s="4"/>
       <c r="B590" s="4"/>
       <c r="C590" s="4"/>
@@ -16033,7 +16039,7 @@
       <c r="BD590" s="4"/>
       <c r="BE590" s="4"/>
     </row>
-    <row r="591" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:57" ht="15.95" customHeight="1">
       <c r="A591" s="4"/>
       <c r="B591" s="4"/>
       <c r="C591" s="4"/>
@@ -16057,7 +16063,7 @@
       <c r="BD591" s="4"/>
       <c r="BE591" s="4"/>
     </row>
-    <row r="592" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:57" ht="15.95" customHeight="1">
       <c r="A592" s="4"/>
       <c r="B592" s="4"/>
       <c r="C592" s="4"/>
@@ -16081,7 +16087,7 @@
       <c r="BD592" s="4"/>
       <c r="BE592" s="4"/>
     </row>
-    <row r="593" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:57" ht="15.95" customHeight="1">
       <c r="A593" s="4"/>
       <c r="B593" s="4"/>
       <c r="C593" s="4"/>
@@ -16105,7 +16111,7 @@
       <c r="BD593" s="4"/>
       <c r="BE593" s="4"/>
     </row>
-    <row r="594" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:57" ht="15.95" customHeight="1">
       <c r="A594" s="4"/>
       <c r="B594" s="4"/>
       <c r="C594" s="4"/>
@@ -16129,7 +16135,7 @@
       <c r="BD594" s="4"/>
       <c r="BE594" s="4"/>
     </row>
-    <row r="595" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:57" ht="15.95" customHeight="1">
       <c r="A595" s="4"/>
       <c r="B595" s="4"/>
       <c r="C595" s="4"/>
@@ -16153,7 +16159,7 @@
       <c r="BD595" s="4"/>
       <c r="BE595" s="4"/>
     </row>
-    <row r="596" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:57" ht="15.95" customHeight="1">
       <c r="A596" s="4"/>
       <c r="B596" s="4"/>
       <c r="C596" s="4"/>
@@ -16177,7 +16183,7 @@
       <c r="BD596" s="4"/>
       <c r="BE596" s="4"/>
     </row>
-    <row r="597" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:57" ht="15.95" customHeight="1">
       <c r="A597" s="4"/>
       <c r="B597" s="4"/>
       <c r="C597" s="4"/>
@@ -16201,7 +16207,7 @@
       <c r="BD597" s="4"/>
       <c r="BE597" s="4"/>
     </row>
-    <row r="598" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:57" ht="15.95" customHeight="1">
       <c r="A598" s="4"/>
       <c r="B598" s="4"/>
       <c r="C598" s="4"/>
@@ -16225,7 +16231,7 @@
       <c r="BD598" s="4"/>
       <c r="BE598" s="4"/>
     </row>
-    <row r="599" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:57" ht="15.95" customHeight="1">
       <c r="A599" s="4"/>
       <c r="B599" s="4"/>
       <c r="C599" s="4"/>
@@ -16249,7 +16255,7 @@
       <c r="BD599" s="4"/>
       <c r="BE599" s="4"/>
     </row>
-    <row r="600" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:57" ht="15.95" customHeight="1">
       <c r="A600" s="4"/>
       <c r="B600" s="4"/>
       <c r="C600" s="4"/>
@@ -16273,7 +16279,7 @@
       <c r="BD600" s="4"/>
       <c r="BE600" s="4"/>
     </row>
-    <row r="601" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:57" ht="15.95" customHeight="1">
       <c r="A601" s="4"/>
       <c r="B601" s="4"/>
       <c r="C601" s="4"/>
@@ -16297,7 +16303,7 @@
       <c r="BD601" s="4"/>
       <c r="BE601" s="4"/>
     </row>
-    <row r="602" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:57" ht="15.95" customHeight="1">
       <c r="A602" s="4"/>
       <c r="B602" s="4"/>
       <c r="C602" s="4"/>
@@ -16321,7 +16327,7 @@
       <c r="BD602" s="4"/>
       <c r="BE602" s="4"/>
     </row>
-    <row r="603" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:57" ht="15.95" customHeight="1">
       <c r="A603" s="4"/>
       <c r="B603" s="4"/>
       <c r="C603" s="4"/>
@@ -16345,7 +16351,7 @@
       <c r="BD603" s="4"/>
       <c r="BE603" s="4"/>
     </row>
-    <row r="604" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:57" ht="15.95" customHeight="1">
       <c r="A604" s="4"/>
       <c r="B604" s="4"/>
       <c r="C604" s="4"/>
@@ -16369,7 +16375,7 @@
       <c r="BD604" s="4"/>
       <c r="BE604" s="4"/>
     </row>
-    <row r="605" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:57" ht="15.95" customHeight="1">
       <c r="A605" s="4"/>
       <c r="B605" s="4"/>
       <c r="C605" s="4"/>
@@ -16393,7 +16399,7 @@
       <c r="BD605" s="4"/>
       <c r="BE605" s="4"/>
     </row>
-    <row r="606" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:57" ht="15.95" customHeight="1">
       <c r="A606" s="4"/>
       <c r="B606" s="4"/>
       <c r="C606" s="4"/>
@@ -16417,7 +16423,7 @@
       <c r="BD606" s="4"/>
       <c r="BE606" s="4"/>
     </row>
-    <row r="607" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:57" ht="15.95" customHeight="1">
       <c r="A607" s="4"/>
       <c r="B607" s="4"/>
       <c r="C607" s="4"/>
@@ -16441,7 +16447,7 @@
       <c r="BD607" s="4"/>
       <c r="BE607" s="4"/>
     </row>
-    <row r="608" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:57" ht="15.95" customHeight="1">
       <c r="A608" s="4"/>
       <c r="B608" s="4"/>
       <c r="C608" s="4"/>
@@ -16465,7 +16471,7 @@
       <c r="BD608" s="4"/>
       <c r="BE608" s="4"/>
     </row>
-    <row r="609" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:57" ht="15.95" customHeight="1">
       <c r="A609" s="4"/>
       <c r="B609" s="4"/>
       <c r="C609" s="4"/>
@@ -16489,7 +16495,7 @@
       <c r="BD609" s="4"/>
       <c r="BE609" s="4"/>
     </row>
-    <row r="610" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:57" ht="15.95" customHeight="1">
       <c r="A610" s="4"/>
       <c r="B610" s="4"/>
       <c r="C610" s="4"/>
@@ -16513,7 +16519,7 @@
       <c r="BD610" s="4"/>
       <c r="BE610" s="4"/>
     </row>
-    <row r="611" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:57" ht="15.95" customHeight="1">
       <c r="A611" s="4"/>
       <c r="B611" s="4"/>
       <c r="C611" s="4"/>
@@ -16537,7 +16543,7 @@
       <c r="BD611" s="4"/>
       <c r="BE611" s="4"/>
     </row>
-    <row r="612" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:57" ht="15.95" customHeight="1">
       <c r="A612" s="4"/>
       <c r="B612" s="4"/>
       <c r="C612" s="4"/>
@@ -16561,7 +16567,7 @@
       <c r="BD612" s="4"/>
       <c r="BE612" s="4"/>
     </row>
-    <row r="613" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:57" ht="15.95" customHeight="1">
       <c r="A613" s="4"/>
       <c r="B613" s="4"/>
       <c r="C613" s="4"/>
@@ -16585,7 +16591,7 @@
       <c r="BD613" s="4"/>
       <c r="BE613" s="4"/>
     </row>
-    <row r="614" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:57" ht="15.95" customHeight="1">
       <c r="A614" s="4"/>
       <c r="B614" s="4"/>
       <c r="C614" s="4"/>
@@ -16609,7 +16615,7 @@
       <c r="BD614" s="4"/>
       <c r="BE614" s="4"/>
     </row>
-    <row r="615" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:57" ht="15.95" customHeight="1">
       <c r="A615" s="4"/>
       <c r="B615" s="4"/>
       <c r="C615" s="4"/>
@@ -16633,7 +16639,7 @@
       <c r="BD615" s="4"/>
       <c r="BE615" s="4"/>
     </row>
-    <row r="616" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:57" ht="15.95" customHeight="1">
       <c r="A616" s="4"/>
       <c r="B616" s="4"/>
       <c r="C616" s="4"/>
@@ -16657,7 +16663,7 @@
       <c r="BD616" s="4"/>
       <c r="BE616" s="4"/>
     </row>
-    <row r="617" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:57" ht="15.95" customHeight="1">
       <c r="A617" s="4"/>
       <c r="B617" s="4"/>
       <c r="C617" s="4"/>
@@ -16681,7 +16687,7 @@
       <c r="BD617" s="4"/>
       <c r="BE617" s="4"/>
     </row>
-    <row r="618" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:57" ht="15.95" customHeight="1">
       <c r="A618" s="4"/>
       <c r="B618" s="4"/>
       <c r="C618" s="4"/>
@@ -16705,7 +16711,7 @@
       <c r="BD618" s="4"/>
       <c r="BE618" s="4"/>
     </row>
-    <row r="619" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:57" ht="15.95" customHeight="1">
       <c r="A619" s="4"/>
       <c r="B619" s="4"/>
       <c r="C619" s="4"/>
@@ -16729,7 +16735,7 @@
       <c r="BD619" s="4"/>
       <c r="BE619" s="4"/>
     </row>
-    <row r="620" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:57" ht="15.95" customHeight="1">
       <c r="A620" s="4"/>
       <c r="B620" s="4"/>
       <c r="C620" s="4"/>
@@ -16753,7 +16759,7 @@
       <c r="BD620" s="4"/>
       <c r="BE620" s="4"/>
     </row>
-    <row r="621" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:57" ht="15.95" customHeight="1">
       <c r="A621" s="4"/>
       <c r="B621" s="4"/>
       <c r="C621" s="4"/>
@@ -16777,7 +16783,7 @@
       <c r="BD621" s="4"/>
       <c r="BE621" s="4"/>
     </row>
-    <row r="622" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:57" ht="15.95" customHeight="1">
       <c r="A622" s="4"/>
       <c r="B622" s="4"/>
       <c r="C622" s="4"/>
@@ -16801,7 +16807,7 @@
       <c r="BD622" s="4"/>
       <c r="BE622" s="4"/>
     </row>
-    <row r="623" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:57" ht="15.95" customHeight="1">
       <c r="A623" s="4"/>
       <c r="B623" s="4"/>
       <c r="C623" s="4"/>
@@ -16825,7 +16831,7 @@
       <c r="BD623" s="4"/>
       <c r="BE623" s="4"/>
     </row>
-    <row r="624" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:57" ht="15.95" customHeight="1">
       <c r="A624" s="4"/>
       <c r="B624" s="4"/>
       <c r="C624" s="4"/>
@@ -16849,7 +16855,7 @@
       <c r="BD624" s="4"/>
       <c r="BE624" s="4"/>
     </row>
-    <row r="625" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:57" ht="15.95" customHeight="1">
       <c r="A625" s="4"/>
       <c r="B625" s="4"/>
       <c r="C625" s="4"/>
@@ -16873,7 +16879,7 @@
       <c r="BD625" s="4"/>
       <c r="BE625" s="4"/>
     </row>
-    <row r="626" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:57" ht="15.95" customHeight="1">
       <c r="A626" s="4"/>
       <c r="B626" s="4"/>
       <c r="C626" s="4"/>
@@ -16897,7 +16903,7 @@
       <c r="BD626" s="4"/>
       <c r="BE626" s="4"/>
     </row>
-    <row r="627" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:57" ht="15.95" customHeight="1">
       <c r="A627" s="4"/>
       <c r="B627" s="4"/>
       <c r="C627" s="4"/>
@@ -16921,7 +16927,7 @@
       <c r="BD627" s="4"/>
       <c r="BE627" s="4"/>
     </row>
-    <row r="628" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:57" ht="15.95" customHeight="1">
       <c r="A628" s="4"/>
       <c r="B628" s="4"/>
       <c r="C628" s="4"/>
@@ -16945,7 +16951,7 @@
       <c r="BD628" s="4"/>
       <c r="BE628" s="4"/>
     </row>
-    <row r="629" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:57" ht="15.95" customHeight="1">
       <c r="A629" s="4"/>
       <c r="B629" s="4"/>
       <c r="C629" s="4"/>
@@ -16969,7 +16975,7 @@
       <c r="BD629" s="4"/>
       <c r="BE629" s="4"/>
     </row>
-    <row r="630" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:57" ht="15.95" customHeight="1">
       <c r="A630" s="4"/>
       <c r="B630" s="4"/>
       <c r="C630" s="4"/>
@@ -16993,7 +16999,7 @@
       <c r="BD630" s="4"/>
       <c r="BE630" s="4"/>
     </row>
-    <row r="631" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:57" ht="15.95" customHeight="1">
       <c r="A631" s="4"/>
       <c r="B631" s="4"/>
       <c r="C631" s="4"/>
@@ -17017,7 +17023,7 @@
       <c r="BD631" s="4"/>
       <c r="BE631" s="4"/>
     </row>
-    <row r="632" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:57" ht="15.95" customHeight="1">
       <c r="A632" s="4"/>
       <c r="B632" s="4"/>
       <c r="C632" s="4"/>
@@ -17041,7 +17047,7 @@
       <c r="BD632" s="4"/>
       <c r="BE632" s="4"/>
     </row>
-    <row r="633" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:57" ht="15.95" customHeight="1">
       <c r="A633" s="4"/>
       <c r="B633" s="4"/>
       <c r="C633" s="4"/>
@@ -17065,7 +17071,7 @@
       <c r="BD633" s="4"/>
       <c r="BE633" s="4"/>
     </row>
-    <row r="634" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:57" ht="15.95" customHeight="1">
       <c r="A634" s="4"/>
       <c r="B634" s="4"/>
       <c r="C634" s="4"/>
@@ -17089,7 +17095,7 @@
       <c r="BD634" s="4"/>
       <c r="BE634" s="4"/>
     </row>
-    <row r="635" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:57" ht="15.95" customHeight="1">
       <c r="A635" s="4"/>
       <c r="B635" s="4"/>
       <c r="C635" s="4"/>
@@ -17113,7 +17119,7 @@
       <c r="BD635" s="4"/>
       <c r="BE635" s="4"/>
     </row>
-    <row r="636" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:57" ht="15.95" customHeight="1">
       <c r="A636" s="4"/>
       <c r="B636" s="4"/>
       <c r="C636" s="4"/>
@@ -17137,7 +17143,7 @@
       <c r="BD636" s="4"/>
       <c r="BE636" s="4"/>
     </row>
-    <row r="637" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:57" ht="15.95" customHeight="1">
       <c r="A637" s="4"/>
       <c r="B637" s="4"/>
       <c r="C637" s="4"/>
@@ -17161,7 +17167,7 @@
       <c r="BD637" s="4"/>
       <c r="BE637" s="4"/>
     </row>
-    <row r="638" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:57" ht="15.95" customHeight="1">
       <c r="A638" s="4"/>
       <c r="B638" s="4"/>
       <c r="C638" s="4"/>
@@ -17185,7 +17191,7 @@
       <c r="BD638" s="4"/>
       <c r="BE638" s="4"/>
     </row>
-    <row r="639" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:57" ht="15.95" customHeight="1">
       <c r="A639" s="4"/>
       <c r="B639" s="4"/>
       <c r="C639" s="4"/>
@@ -17209,7 +17215,7 @@
       <c r="BD639" s="4"/>
       <c r="BE639" s="4"/>
     </row>
-    <row r="640" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:57" ht="15.95" customHeight="1">
       <c r="A640" s="4"/>
       <c r="B640" s="4"/>
       <c r="C640" s="4"/>
@@ -17233,7 +17239,7 @@
       <c r="BD640" s="4"/>
       <c r="BE640" s="4"/>
     </row>
-    <row r="641" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:57" ht="15.95" customHeight="1">
       <c r="A641" s="4"/>
       <c r="B641" s="4"/>
       <c r="C641" s="4"/>
@@ -17257,7 +17263,7 @@
       <c r="BD641" s="4"/>
       <c r="BE641" s="4"/>
     </row>
-    <row r="642" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:57" ht="15.95" customHeight="1">
       <c r="A642" s="4"/>
       <c r="B642" s="4"/>
       <c r="C642" s="4"/>
@@ -17281,7 +17287,7 @@
       <c r="BD642" s="4"/>
       <c r="BE642" s="4"/>
     </row>
-    <row r="643" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:57" ht="15.95" customHeight="1">
       <c r="A643" s="4"/>
       <c r="B643" s="4"/>
       <c r="C643" s="4"/>
@@ -17305,7 +17311,7 @@
       <c r="BD643" s="4"/>
       <c r="BE643" s="4"/>
     </row>
-    <row r="644" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:57" ht="15.95" customHeight="1">
       <c r="A644" s="4"/>
       <c r="B644" s="4"/>
       <c r="C644" s="4"/>
@@ -17329,7 +17335,7 @@
       <c r="BD644" s="4"/>
       <c r="BE644" s="4"/>
     </row>
-    <row r="645" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:57" ht="15.95" customHeight="1">
       <c r="A645" s="4"/>
       <c r="B645" s="4"/>
       <c r="C645" s="4"/>
@@ -17353,7 +17359,7 @@
       <c r="BD645" s="4"/>
       <c r="BE645" s="4"/>
     </row>
-    <row r="646" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:57" ht="15.95" customHeight="1">
       <c r="A646" s="4"/>
       <c r="B646" s="4"/>
       <c r="C646" s="4"/>
@@ -17377,7 +17383,7 @@
       <c r="BD646" s="4"/>
       <c r="BE646" s="4"/>
     </row>
-    <row r="647" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:57" ht="15.95" customHeight="1">
       <c r="A647" s="4"/>
       <c r="B647" s="4"/>
       <c r="C647" s="4"/>
@@ -17401,7 +17407,7 @@
       <c r="BD647" s="4"/>
       <c r="BE647" s="4"/>
     </row>
-    <row r="648" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:57" ht="15.95" customHeight="1">
       <c r="A648" s="4"/>
       <c r="B648" s="4"/>
       <c r="C648" s="4"/>
@@ -17425,7 +17431,7 @@
       <c r="BD648" s="4"/>
       <c r="BE648" s="4"/>
     </row>
-    <row r="649" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:57" ht="15.95" customHeight="1">
       <c r="A649" s="4"/>
       <c r="B649" s="4"/>
       <c r="C649" s="4"/>
@@ -17449,7 +17455,7 @@
       <c r="BD649" s="4"/>
       <c r="BE649" s="4"/>
     </row>
-    <row r="650" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:57" ht="15.95" customHeight="1">
       <c r="A650" s="4"/>
       <c r="B650" s="4"/>
       <c r="C650" s="4"/>
@@ -17473,7 +17479,7 @@
       <c r="BD650" s="4"/>
       <c r="BE650" s="4"/>
     </row>
-    <row r="651" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:57" ht="15.95" customHeight="1">
       <c r="A651" s="4"/>
       <c r="B651" s="4"/>
       <c r="C651" s="4"/>
@@ -17497,7 +17503,7 @@
       <c r="BD651" s="4"/>
       <c r="BE651" s="4"/>
     </row>
-    <row r="652" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:57" ht="15.95" customHeight="1">
       <c r="A652" s="4"/>
       <c r="B652" s="4"/>
       <c r="C652" s="4"/>
@@ -17521,7 +17527,7 @@
       <c r="BD652" s="4"/>
       <c r="BE652" s="4"/>
     </row>
-    <row r="653" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:57" ht="15.95" customHeight="1">
       <c r="A653" s="4"/>
       <c r="B653" s="4"/>
       <c r="C653" s="4"/>
@@ -17545,7 +17551,7 @@
       <c r="BD653" s="4"/>
       <c r="BE653" s="4"/>
     </row>
-    <row r="654" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:57" ht="15.95" customHeight="1">
       <c r="A654" s="4"/>
       <c r="B654" s="4"/>
       <c r="C654" s="4"/>
@@ -17569,7 +17575,7 @@
       <c r="BD654" s="4"/>
       <c r="BE654" s="4"/>
     </row>
-    <row r="655" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:57" ht="15.95" customHeight="1">
       <c r="A655" s="4"/>
       <c r="B655" s="4"/>
       <c r="C655" s="4"/>
@@ -17593,7 +17599,7 @@
       <c r="BD655" s="4"/>
       <c r="BE655" s="4"/>
     </row>
-    <row r="656" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:57" ht="15.95" customHeight="1">
       <c r="A656" s="4"/>
       <c r="B656" s="4"/>
       <c r="C656" s="4"/>
@@ -17617,7 +17623,7 @@
       <c r="BD656" s="4"/>
       <c r="BE656" s="4"/>
     </row>
-    <row r="657" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:57" ht="15.95" customHeight="1">
       <c r="A657" s="4"/>
       <c r="B657" s="4"/>
       <c r="C657" s="4"/>
@@ -17641,7 +17647,7 @@
       <c r="BD657" s="4"/>
       <c r="BE657" s="4"/>
     </row>
-    <row r="658" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:57" ht="15.95" customHeight="1">
       <c r="A658" s="4"/>
       <c r="B658" s="4"/>
       <c r="C658" s="4"/>
@@ -17665,7 +17671,7 @@
       <c r="BD658" s="4"/>
       <c r="BE658" s="4"/>
     </row>
-    <row r="659" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:57" ht="15.95" customHeight="1">
       <c r="A659" s="4"/>
       <c r="B659" s="4"/>
       <c r="C659" s="4"/>
@@ -17689,7 +17695,7 @@
       <c r="BD659" s="4"/>
       <c r="BE659" s="4"/>
     </row>
-    <row r="660" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:57" ht="15.95" customHeight="1">
       <c r="A660" s="4"/>
       <c r="B660" s="4"/>
       <c r="C660" s="4"/>
@@ -17713,7 +17719,7 @@
       <c r="BD660" s="4"/>
       <c r="BE660" s="4"/>
     </row>
-    <row r="661" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:57" ht="15.95" customHeight="1">
       <c r="A661" s="4"/>
       <c r="B661" s="4"/>
       <c r="C661" s="4"/>
@@ -17737,7 +17743,7 @@
       <c r="BD661" s="4"/>
       <c r="BE661" s="4"/>
     </row>
-    <row r="662" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:57" ht="15.95" customHeight="1">
       <c r="A662" s="4"/>
       <c r="B662" s="4"/>
       <c r="C662" s="4"/>
@@ -17761,7 +17767,7 @@
       <c r="BD662" s="4"/>
       <c r="BE662" s="4"/>
     </row>
-    <row r="663" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:57" ht="15.95" customHeight="1">
       <c r="A663" s="4"/>
       <c r="B663" s="4"/>
       <c r="C663" s="4"/>
@@ -17785,7 +17791,7 @@
       <c r="BD663" s="4"/>
       <c r="BE663" s="4"/>
     </row>
-    <row r="664" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:57" ht="15.95" customHeight="1">
       <c r="A664" s="4"/>
       <c r="B664" s="4"/>
       <c r="C664" s="4"/>
@@ -17809,7 +17815,7 @@
       <c r="BD664" s="4"/>
       <c r="BE664" s="4"/>
     </row>
-    <row r="665" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:57" ht="15.95" customHeight="1">
       <c r="A665" s="4"/>
       <c r="B665" s="4"/>
       <c r="C665" s="4"/>
@@ -17833,7 +17839,7 @@
       <c r="BD665" s="4"/>
       <c r="BE665" s="4"/>
     </row>
-    <row r="666" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:57" ht="15.95" customHeight="1">
       <c r="A666" s="4"/>
       <c r="B666" s="4"/>
       <c r="C666" s="4"/>
@@ -17857,7 +17863,7 @@
       <c r="BD666" s="4"/>
       <c r="BE666" s="4"/>
     </row>
-    <row r="667" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:57" ht="15.95" customHeight="1">
       <c r="A667" s="4"/>
       <c r="B667" s="4"/>
       <c r="C667" s="4"/>
@@ -17881,7 +17887,7 @@
       <c r="BD667" s="4"/>
       <c r="BE667" s="4"/>
     </row>
-    <row r="668" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:57" ht="15.95" customHeight="1">
       <c r="A668" s="4"/>
       <c r="B668" s="4"/>
       <c r="C668" s="4"/>
@@ -17905,7 +17911,7 @@
       <c r="BD668" s="4"/>
       <c r="BE668" s="4"/>
     </row>
-    <row r="669" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:57" ht="15.95" customHeight="1">
       <c r="A669" s="4"/>
       <c r="B669" s="4"/>
       <c r="C669" s="4"/>
@@ -17929,7 +17935,7 @@
       <c r="BD669" s="4"/>
       <c r="BE669" s="4"/>
     </row>
-    <row r="670" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:57" ht="15.95" customHeight="1">
       <c r="A670" s="4"/>
       <c r="B670" s="4"/>
       <c r="C670" s="4"/>
@@ -17953,7 +17959,7 @@
       <c r="BD670" s="4"/>
       <c r="BE670" s="4"/>
     </row>
-    <row r="671" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:57" ht="15.95" customHeight="1">
       <c r="A671" s="4"/>
       <c r="B671" s="4"/>
       <c r="C671" s="4"/>
@@ -17977,7 +17983,7 @@
       <c r="BD671" s="4"/>
       <c r="BE671" s="4"/>
     </row>
-    <row r="672" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:57" ht="15.95" customHeight="1">
       <c r="A672" s="4"/>
       <c r="B672" s="4"/>
       <c r="C672" s="4"/>
@@ -18001,7 +18007,7 @@
       <c r="BD672" s="4"/>
       <c r="BE672" s="4"/>
     </row>
-    <row r="673" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:57" ht="15.95" customHeight="1">
       <c r="A673" s="4"/>
       <c r="B673" s="4"/>
       <c r="C673" s="4"/>
@@ -18025,7 +18031,7 @@
       <c r="BD673" s="4"/>
       <c r="BE673" s="4"/>
     </row>
-    <row r="674" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:57" ht="15.95" customHeight="1">
       <c r="A674" s="4"/>
       <c r="B674" s="4"/>
       <c r="C674" s="4"/>
@@ -18049,7 +18055,7 @@
       <c r="BD674" s="4"/>
       <c r="BE674" s="4"/>
     </row>
-    <row r="675" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:57" ht="15.95" customHeight="1">
       <c r="A675" s="4"/>
       <c r="B675" s="4"/>
       <c r="C675" s="4"/>
@@ -18073,7 +18079,7 @@
       <c r="BD675" s="4"/>
       <c r="BE675" s="4"/>
     </row>
-    <row r="676" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:57" ht="15.95" customHeight="1">
       <c r="A676" s="4"/>
       <c r="B676" s="4"/>
       <c r="C676" s="4"/>
@@ -18097,7 +18103,7 @@
       <c r="BD676" s="4"/>
       <c r="BE676" s="4"/>
     </row>
-    <row r="677" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:57" ht="15.95" customHeight="1">
       <c r="A677" s="4"/>
       <c r="B677" s="4"/>
       <c r="C677" s="4"/>
@@ -18121,7 +18127,7 @@
       <c r="BD677" s="4"/>
       <c r="BE677" s="4"/>
     </row>
-    <row r="678" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:57" ht="15.95" customHeight="1">
       <c r="A678" s="4"/>
       <c r="B678" s="4"/>
       <c r="C678" s="4"/>
@@ -18145,7 +18151,7 @@
       <c r="BD678" s="4"/>
       <c r="BE678" s="4"/>
     </row>
-    <row r="679" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:57" ht="15.95" customHeight="1">
       <c r="A679" s="4"/>
       <c r="B679" s="4"/>
       <c r="C679" s="4"/>
@@ -18169,7 +18175,7 @@
       <c r="BD679" s="4"/>
       <c r="BE679" s="4"/>
     </row>
-    <row r="680" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:57" ht="15.95" customHeight="1">
       <c r="A680" s="4"/>
       <c r="B680" s="4"/>
       <c r="C680" s="4"/>
@@ -18193,7 +18199,7 @@
       <c r="BD680" s="4"/>
       <c r="BE680" s="4"/>
     </row>
-    <row r="681" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:57" ht="15.95" customHeight="1">
       <c r="A681" s="4"/>
       <c r="B681" s="4"/>
       <c r="C681" s="4"/>
@@ -18217,7 +18223,7 @@
       <c r="BD681" s="4"/>
       <c r="BE681" s="4"/>
     </row>
-    <row r="682" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:57" ht="15.95" customHeight="1">
       <c r="A682" s="4"/>
       <c r="B682" s="4"/>
       <c r="C682" s="4"/>
@@ -18241,7 +18247,7 @@
       <c r="BD682" s="4"/>
       <c r="BE682" s="4"/>
     </row>
-    <row r="683" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:57" ht="15.95" customHeight="1">
       <c r="A683" s="4"/>
       <c r="B683" s="4"/>
       <c r="C683" s="4"/>
@@ -18265,7 +18271,7 @@
       <c r="BD683" s="4"/>
       <c r="BE683" s="4"/>
     </row>
-    <row r="684" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:57" ht="15.95" customHeight="1">
       <c r="A684" s="4"/>
       <c r="B684" s="4"/>
       <c r="C684" s="4"/>
@@ -18289,7 +18295,7 @@
       <c r="BD684" s="4"/>
       <c r="BE684" s="4"/>
     </row>
-    <row r="685" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:57" ht="15.95" customHeight="1">
       <c r="A685" s="4"/>
       <c r="B685" s="4"/>
       <c r="C685" s="4"/>
@@ -18313,7 +18319,7 @@
       <c r="BD685" s="4"/>
       <c r="BE685" s="4"/>
     </row>
-    <row r="686" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:57" ht="15.95" customHeight="1">
       <c r="A686" s="4"/>
       <c r="B686" s="4"/>
       <c r="C686" s="4"/>
@@ -18337,7 +18343,7 @@
       <c r="BD686" s="4"/>
       <c r="BE686" s="4"/>
     </row>
-    <row r="687" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:57" ht="15.95" customHeight="1">
       <c r="A687" s="4"/>
       <c r="B687" s="4"/>
       <c r="C687" s="4"/>
@@ -18361,7 +18367,7 @@
       <c r="BD687" s="4"/>
       <c r="BE687" s="4"/>
     </row>
-    <row r="688" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:57" ht="15.95" customHeight="1">
       <c r="A688" s="4"/>
       <c r="B688" s="4"/>
       <c r="C688" s="4"/>
@@ -18385,7 +18391,7 @@
       <c r="BD688" s="4"/>
       <c r="BE688" s="4"/>
     </row>
-    <row r="689" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:57" ht="15.95" customHeight="1">
       <c r="A689" s="4"/>
       <c r="B689" s="4"/>
       <c r="C689" s="4"/>
@@ -18409,7 +18415,7 @@
       <c r="BD689" s="4"/>
       <c r="BE689" s="4"/>
     </row>
-    <row r="690" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:57" ht="15.95" customHeight="1">
       <c r="A690" s="4"/>
       <c r="B690" s="4"/>
       <c r="C690" s="4"/>
@@ -18433,7 +18439,7 @@
       <c r="BD690" s="4"/>
       <c r="BE690" s="4"/>
     </row>
-    <row r="691" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:57" ht="15.95" customHeight="1">
       <c r="A691" s="4"/>
       <c r="B691" s="4"/>
       <c r="C691" s="4"/>
@@ -18457,7 +18463,7 @@
       <c r="BD691" s="4"/>
       <c r="BE691" s="4"/>
     </row>
-    <row r="692" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:57" ht="15.95" customHeight="1">
       <c r="A692" s="4"/>
       <c r="B692" s="4"/>
       <c r="C692" s="4"/>
@@ -18481,7 +18487,7 @@
       <c r="BD692" s="4"/>
       <c r="BE692" s="4"/>
     </row>
-    <row r="693" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:57" ht="15.95" customHeight="1">
       <c r="A693" s="4"/>
       <c r="B693" s="4"/>
       <c r="C693" s="4"/>
@@ -18505,7 +18511,7 @@
       <c r="BD693" s="4"/>
       <c r="BE693" s="4"/>
     </row>
-    <row r="694" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:57" ht="15.95" customHeight="1">
       <c r="A694" s="4"/>
       <c r="B694" s="4"/>
       <c r="C694" s="4"/>
@@ -18529,7 +18535,7 @@
       <c r="BD694" s="4"/>
       <c r="BE694" s="4"/>
     </row>
-    <row r="695" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:57" ht="15.95" customHeight="1">
       <c r="A695" s="4"/>
       <c r="B695" s="4"/>
       <c r="C695" s="4"/>
@@ -18553,7 +18559,7 @@
       <c r="BD695" s="4"/>
       <c r="BE695" s="4"/>
     </row>
-    <row r="696" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:57" ht="15.95" customHeight="1">
       <c r="A696" s="4"/>
       <c r="B696" s="4"/>
       <c r="C696" s="4"/>
@@ -18577,7 +18583,7 @@
       <c r="BD696" s="4"/>
       <c r="BE696" s="4"/>
     </row>
-    <row r="697" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:57" ht="15.95" customHeight="1">
       <c r="A697" s="4"/>
       <c r="B697" s="4"/>
       <c r="C697" s="4"/>
@@ -18601,7 +18607,7 @@
       <c r="BD697" s="4"/>
       <c r="BE697" s="4"/>
     </row>
-    <row r="698" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:57" ht="15.95" customHeight="1">
       <c r="A698" s="4"/>
       <c r="B698" s="4"/>
       <c r="C698" s="4"/>
@@ -18625,7 +18631,7 @@
       <c r="BD698" s="4"/>
       <c r="BE698" s="4"/>
     </row>
-    <row r="699" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:57" ht="15.95" customHeight="1">
       <c r="A699" s="4"/>
       <c r="B699" s="4"/>
       <c r="C699" s="4"/>
@@ -18649,7 +18655,7 @@
       <c r="BD699" s="4"/>
       <c r="BE699" s="4"/>
     </row>
-    <row r="700" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:57" ht="15.95" customHeight="1">
       <c r="A700" s="4"/>
       <c r="B700" s="4"/>
       <c r="C700" s="4"/>
@@ -18673,7 +18679,7 @@
       <c r="BD700" s="4"/>
       <c r="BE700" s="4"/>
     </row>
-    <row r="701" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:57" ht="15.95" customHeight="1">
       <c r="A701" s="4"/>
       <c r="B701" s="4"/>
       <c r="C701" s="4"/>
@@ -18697,7 +18703,7 @@
       <c r="BD701" s="4"/>
       <c r="BE701" s="4"/>
     </row>
-    <row r="702" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:57" ht="15.95" customHeight="1">
       <c r="A702" s="4"/>
       <c r="B702" s="4"/>
       <c r="C702" s="4"/>
@@ -18721,7 +18727,7 @@
       <c r="BD702" s="4"/>
       <c r="BE702" s="4"/>
     </row>
-    <row r="703" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:57" ht="15.95" customHeight="1">
       <c r="A703" s="4"/>
       <c r="B703" s="4"/>
       <c r="C703" s="4"/>
@@ -18745,7 +18751,7 @@
       <c r="BD703" s="4"/>
       <c r="BE703" s="4"/>
     </row>
-    <row r="704" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:57" ht="15.95" customHeight="1">
       <c r="A704" s="4"/>
       <c r="B704" s="4"/>
       <c r="C704" s="4"/>
@@ -18769,7 +18775,7 @@
       <c r="BD704" s="4"/>
       <c r="BE704" s="4"/>
     </row>
-    <row r="705" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:57" ht="15.95" customHeight="1">
       <c r="A705" s="4"/>
       <c r="B705" s="4"/>
       <c r="C705" s="4"/>
@@ -18793,7 +18799,7 @@
       <c r="BD705" s="4"/>
       <c r="BE705" s="4"/>
     </row>
-    <row r="706" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:57" ht="15.95" customHeight="1">
       <c r="A706" s="4"/>
       <c r="B706" s="4"/>
       <c r="C706" s="4"/>
@@ -18817,7 +18823,7 @@
       <c r="BD706" s="4"/>
       <c r="BE706" s="4"/>
     </row>
-    <row r="707" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:57" ht="15.95" customHeight="1">
       <c r="A707" s="4"/>
       <c r="B707" s="4"/>
       <c r="C707" s="4"/>
@@ -18841,7 +18847,7 @@
       <c r="BD707" s="4"/>
       <c r="BE707" s="4"/>
     </row>
-    <row r="708" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:57" ht="15.95" customHeight="1">
       <c r="A708" s="4"/>
       <c r="B708" s="4"/>
       <c r="C708" s="4"/>
@@ -18865,7 +18871,7 @@
       <c r="BD708" s="4"/>
       <c r="BE708" s="4"/>
     </row>
-    <row r="709" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:57" ht="15.95" customHeight="1">
       <c r="A709" s="4"/>
       <c r="B709" s="4"/>
       <c r="C709" s="4"/>
@@ -18889,7 +18895,7 @@
       <c r="BD709" s="4"/>
       <c r="BE709" s="4"/>
     </row>
-    <row r="710" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:57" ht="15.95" customHeight="1">
       <c r="A710" s="4"/>
       <c r="B710" s="4"/>
       <c r="C710" s="4"/>
@@ -18913,7 +18919,7 @@
       <c r="BD710" s="4"/>
       <c r="BE710" s="4"/>
     </row>
-    <row r="711" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:57" ht="15.95" customHeight="1">
       <c r="A711" s="4"/>
       <c r="B711" s="4"/>
       <c r="C711" s="4"/>
@@ -18937,7 +18943,7 @@
       <c r="BD711" s="4"/>
       <c r="BE711" s="4"/>
     </row>
-    <row r="712" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:57" ht="15.95" customHeight="1">
       <c r="A712" s="4"/>
       <c r="B712" s="4"/>
       <c r="C712" s="4"/>
@@ -18961,7 +18967,7 @@
       <c r="BD712" s="4"/>
       <c r="BE712" s="4"/>
     </row>
-    <row r="713" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:57" ht="15.95" customHeight="1">
       <c r="A713" s="4"/>
       <c r="B713" s="4"/>
       <c r="C713" s="4"/>
@@ -18985,7 +18991,7 @@
       <c r="BD713" s="4"/>
       <c r="BE713" s="4"/>
     </row>
-    <row r="714" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:57" ht="15.95" customHeight="1">
       <c r="A714" s="4"/>
       <c r="B714" s="4"/>
       <c r="C714" s="4"/>
@@ -19009,7 +19015,7 @@
       <c r="BD714" s="4"/>
       <c r="BE714" s="4"/>
     </row>
-    <row r="715" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:57" ht="15.95" customHeight="1">
       <c r="A715" s="4"/>
       <c r="B715" s="4"/>
       <c r="C715" s="4"/>
@@ -19033,7 +19039,7 @@
       <c r="BD715" s="4"/>
       <c r="BE715" s="4"/>
     </row>
-    <row r="716" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:57" ht="15.95" customHeight="1">
       <c r="A716" s="4"/>
       <c r="B716" s="4"/>
       <c r="C716" s="4"/>
@@ -19057,7 +19063,7 @@
       <c r="BD716" s="4"/>
       <c r="BE716" s="4"/>
     </row>
-    <row r="717" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:57" ht="15.95" customHeight="1">
       <c r="A717" s="4"/>
       <c r="B717" s="4"/>
       <c r="C717" s="4"/>
@@ -19081,7 +19087,7 @@
       <c r="BD717" s="4"/>
       <c r="BE717" s="4"/>
     </row>
-    <row r="718" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:57" ht="15.95" customHeight="1">
       <c r="A718" s="4"/>
       <c r="B718" s="4"/>
       <c r="C718" s="4"/>
@@ -19105,7 +19111,7 @@
       <c r="BD718" s="4"/>
       <c r="BE718" s="4"/>
     </row>
-    <row r="719" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:57" ht="15.95" customHeight="1">
       <c r="A719" s="4"/>
       <c r="B719" s="4"/>
       <c r="C719" s="4"/>
@@ -19129,7 +19135,7 @@
       <c r="BD719" s="4"/>
       <c r="BE719" s="4"/>
     </row>
-    <row r="720" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:57" ht="15.95" customHeight="1">
       <c r="A720" s="4"/>
       <c r="B720" s="4"/>
       <c r="C720" s="4"/>
@@ -19153,7 +19159,7 @@
       <c r="BD720" s="4"/>
       <c r="BE720" s="4"/>
     </row>
-    <row r="721" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:57" ht="15.95" customHeight="1">
       <c r="A721" s="4"/>
       <c r="B721" s="4"/>
       <c r="C721" s="4"/>
@@ -19177,7 +19183,7 @@
       <c r="BD721" s="4"/>
       <c r="BE721" s="4"/>
     </row>
-    <row r="722" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:57" ht="15.95" customHeight="1">
       <c r="A722" s="4"/>
       <c r="B722" s="4"/>
       <c r="C722" s="4"/>
@@ -19201,7 +19207,7 @@
       <c r="BD722" s="4"/>
       <c r="BE722" s="4"/>
     </row>
-    <row r="723" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:57" ht="15.95" customHeight="1">
       <c r="A723" s="4"/>
       <c r="B723" s="4"/>
       <c r="C723" s="4"/>
@@ -19225,7 +19231,7 @@
       <c r="BD723" s="4"/>
       <c r="BE723" s="4"/>
     </row>
-    <row r="724" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:57" ht="15.95" customHeight="1">
       <c r="A724" s="4"/>
       <c r="B724" s="4"/>
       <c r="C724" s="4"/>
@@ -19249,7 +19255,7 @@
       <c r="BD724" s="4"/>
       <c r="BE724" s="4"/>
     </row>
-    <row r="725" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:57" ht="15.95" customHeight="1">
       <c r="A725" s="4"/>
       <c r="B725" s="4"/>
       <c r="C725" s="4"/>
@@ -19273,7 +19279,7 @@
       <c r="BD725" s="4"/>
       <c r="BE725" s="4"/>
     </row>
-    <row r="726" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:57" ht="15.95" customHeight="1">
       <c r="A726" s="4"/>
       <c r="B726" s="4"/>
       <c r="C726" s="4"/>
@@ -19297,7 +19303,7 @@
       <c r="BD726" s="4"/>
       <c r="BE726" s="4"/>
     </row>
-    <row r="727" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:57" ht="15.95" customHeight="1">
       <c r="A727" s="4"/>
       <c r="B727" s="4"/>
       <c r="C727" s="4"/>
@@ -19321,7 +19327,7 @@
       <c r="BD727" s="4"/>
       <c r="BE727" s="4"/>
     </row>
-    <row r="728" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:57" ht="15.95" customHeight="1">
       <c r="A728" s="4"/>
       <c r="B728" s="4"/>
       <c r="C728" s="4"/>
@@ -19345,7 +19351,7 @@
       <c r="BD728" s="4"/>
       <c r="BE728" s="4"/>
     </row>
-    <row r="729" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:57" ht="15.95" customHeight="1">
       <c r="A729" s="4"/>
       <c r="B729" s="4"/>
       <c r="C729" s="4"/>
@@ -19369,7 +19375,7 @@
       <c r="BD729" s="4"/>
       <c r="BE729" s="4"/>
     </row>
-    <row r="730" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:57" ht="15.95" customHeight="1">
       <c r="A730" s="4"/>
       <c r="B730" s="4"/>
       <c r="C730" s="4"/>
@@ -19393,7 +19399,7 @@
       <c r="BD730" s="4"/>
       <c r="BE730" s="4"/>
     </row>
-    <row r="731" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:57" ht="15.95" customHeight="1">
       <c r="A731" s="4"/>
       <c r="B731" s="4"/>
       <c r="C731" s="4"/>
@@ -19417,7 +19423,7 @@
       <c r="BD731" s="4"/>
       <c r="BE731" s="4"/>
     </row>
-    <row r="732" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:57" ht="15.95" customHeight="1">
       <c r="A732" s="4"/>
       <c r="B732" s="4"/>
       <c r="C732" s="4"/>
@@ -19441,7 +19447,7 @@
       <c r="BD732" s="4"/>
       <c r="BE732" s="4"/>
     </row>
-    <row r="733" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:57" ht="15.95" customHeight="1">
       <c r="A733" s="4"/>
       <c r="B733" s="4"/>
       <c r="C733" s="4"/>
@@ -19465,7 +19471,7 @@
       <c r="BD733" s="4"/>
       <c r="BE733" s="4"/>
     </row>
-    <row r="734" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:57" ht="15.95" customHeight="1">
       <c r="A734" s="4"/>
       <c r="B734" s="4"/>
       <c r="C734" s="4"/>
@@ -19489,7 +19495,7 @@
       <c r="BD734" s="4"/>
       <c r="BE734" s="4"/>
     </row>
-    <row r="735" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:57" ht="15.95" customHeight="1">
       <c r="A735" s="4"/>
       <c r="B735" s="4"/>
       <c r="C735" s="4"/>
@@ -19513,7 +19519,7 @@
       <c r="BD735" s="4"/>
       <c r="BE735" s="4"/>
     </row>
-    <row r="736" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:57" ht="15.95" customHeight="1">
       <c r="A736" s="4"/>
       <c r="B736" s="4"/>
       <c r="C736" s="4"/>
@@ -19537,7 +19543,7 @@
       <c r="BD736" s="4"/>
       <c r="BE736" s="4"/>
     </row>
-    <row r="737" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:57" ht="15.95" customHeight="1">
       <c r="A737" s="4"/>
       <c r="B737" s="4"/>
       <c r="C737" s="4"/>
@@ -19561,7 +19567,7 @@
       <c r="BD737" s="4"/>
       <c r="BE737" s="4"/>
     </row>
-    <row r="738" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:57" ht="15.95" customHeight="1">
       <c r="A738" s="4"/>
       <c r="B738" s="4"/>
       <c r="C738" s="4"/>
@@ -19585,7 +19591,7 @@
       <c r="BD738" s="4"/>
       <c r="BE738" s="4"/>
     </row>
-    <row r="739" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:57" ht="15.95" customHeight="1">
       <c r="A739" s="4"/>
       <c r="B739" s="4"/>
       <c r="C739" s="4"/>
@@ -19609,7 +19615,7 @@
       <c r="BD739" s="4"/>
       <c r="BE739" s="4"/>
     </row>
-    <row r="740" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:57" ht="15.95" customHeight="1">
       <c r="A740" s="4"/>
       <c r="B740" s="4"/>
       <c r="C740" s="4"/>
@@ -19633,7 +19639,7 @@
       <c r="BD740" s="4"/>
       <c r="BE740" s="4"/>
     </row>
-    <row r="741" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:57" ht="15.95" customHeight="1">
       <c r="A741" s="4"/>
       <c r="B741" s="4"/>
       <c r="C741" s="4"/>
@@ -19657,7 +19663,7 @@
       <c r="BD741" s="4"/>
       <c r="BE741" s="4"/>
     </row>
-    <row r="742" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:57" ht="15.95" customHeight="1">
       <c r="A742" s="4"/>
       <c r="B742" s="4"/>
       <c r="C742" s="4"/>
@@ -19681,7 +19687,7 @@
       <c r="BD742" s="4"/>
       <c r="BE742" s="4"/>
     </row>
-    <row r="743" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:57" ht="15.95" customHeight="1">
       <c r="A743" s="4"/>
       <c r="B743" s="4"/>
       <c r="C743" s="4"/>
@@ -19705,7 +19711,7 @@
       <c r="BD743" s="4"/>
       <c r="BE743" s="4"/>
     </row>
-    <row r="744" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:57" ht="15.95" customHeight="1">
       <c r="A744" s="4"/>
       <c r="B744" s="4"/>
       <c r="C744" s="4"/>
@@ -19729,7 +19735,7 @@
       <c r="BD744" s="4"/>
       <c r="BE744" s="4"/>
     </row>
-    <row r="745" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:57" ht="15.95" customHeight="1">
       <c r="A745" s="4"/>
       <c r="B745" s="4"/>
       <c r="C745" s="4"/>
@@ -19753,7 +19759,7 @@
       <c r="BD745" s="4"/>
       <c r="BE745" s="4"/>
     </row>
-    <row r="746" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:57" ht="15.95" customHeight="1">
       <c r="A746" s="4"/>
       <c r="B746" s="4"/>
       <c r="C746" s="4"/>
@@ -19777,7 +19783,7 @@
       <c r="BD746" s="4"/>
       <c r="BE746" s="4"/>
     </row>
-    <row r="747" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:57" ht="15.95" customHeight="1">
       <c r="A747" s="4"/>
       <c r="B747" s="4"/>
       <c r="C747" s="4"/>
@@ -19801,7 +19807,7 @@
       <c r="BD747" s="4"/>
       <c r="BE747" s="4"/>
     </row>
-    <row r="748" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:57" ht="15.95" customHeight="1">
       <c r="A748" s="4"/>
       <c r="B748" s="4"/>
       <c r="C748" s="4"/>
@@ -19825,7 +19831,7 @@
       <c r="BD748" s="4"/>
       <c r="BE748" s="4"/>
     </row>
-    <row r="749" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:57" ht="15.95" customHeight="1">
       <c r="A749" s="4"/>
       <c r="B749" s="4"/>
       <c r="C749" s="4"/>
@@ -19849,7 +19855,7 @@
       <c r="BD749" s="4"/>
       <c r="BE749" s="4"/>
     </row>
-    <row r="750" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:57" ht="15.95" customHeight="1">
       <c r="A750" s="4"/>
       <c r="B750" s="4"/>
       <c r="C750" s="4"/>
@@ -19873,7 +19879,7 @@
       <c r="BD750" s="4"/>
       <c r="BE750" s="4"/>
     </row>
-    <row r="751" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:57" ht="15.95" customHeight="1">
       <c r="A751" s="4"/>
       <c r="B751" s="4"/>
       <c r="C751" s="4"/>
@@ -19897,7 +19903,7 @@
       <c r="BD751" s="4"/>
       <c r="BE751" s="4"/>
     </row>
-    <row r="752" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:57" ht="15.95" customHeight="1">
       <c r="A752" s="4"/>
       <c r="B752" s="4"/>
       <c r="C752" s="4"/>
@@ -19921,7 +19927,7 @@
       <c r="BD752" s="4"/>
       <c r="BE752" s="4"/>
     </row>
-    <row r="753" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:57" ht="15.95" customHeight="1">
       <c r="A753" s="4"/>
       <c r="B753" s="4"/>
       <c r="C753" s="4"/>
@@ -19945,7 +19951,7 @@
       <c r="BD753" s="4"/>
       <c r="BE753" s="4"/>
     </row>
-    <row r="754" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:57" ht="15.95" customHeight="1">
       <c r="A754" s="4"/>
       <c r="B754" s="4"/>
       <c r="C754" s="4"/>
@@ -19969,7 +19975,7 @@
       <c r="BD754" s="4"/>
       <c r="BE754" s="4"/>
     </row>
-    <row r="755" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:57" ht="15.95" customHeight="1">
       <c r="A755" s="4"/>
       <c r="B755" s="4"/>
       <c r="C755" s="4"/>
@@ -19993,7 +19999,7 @@
       <c r="BD755" s="4"/>
       <c r="BE755" s="4"/>
     </row>
-    <row r="756" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:57" ht="15.95" customHeight="1">
       <c r="A756" s="4"/>
       <c r="B756" s="4"/>
       <c r="C756" s="4"/>
@@ -20017,7 +20023,7 @@
       <c r="BD756" s="4"/>
       <c r="BE756" s="4"/>
     </row>
-    <row r="757" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:57" ht="15.95" customHeight="1">
       <c r="A757" s="4"/>
       <c r="B757" s="4"/>
       <c r="C757" s="4"/>
@@ -20041,7 +20047,7 @@
       <c r="BD757" s="4"/>
       <c r="BE757" s="4"/>
     </row>
-    <row r="758" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:57" ht="15.95" customHeight="1">
       <c r="A758" s="4"/>
       <c r="B758" s="4"/>
       <c r="C758" s="4"/>
@@ -20065,7 +20071,7 @@
       <c r="BD758" s="4"/>
       <c r="BE758" s="4"/>
     </row>
-    <row r="759" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:57" ht="15.95" customHeight="1">
       <c r="A759" s="4"/>
       <c r="B759" s="4"/>
       <c r="C759" s="4"/>
@@ -20089,7 +20095,7 @@
       <c r="BD759" s="4"/>
       <c r="BE759" s="4"/>
     </row>
-    <row r="760" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:57" ht="15.95" customHeight="1">
       <c r="A760" s="4"/>
       <c r="B760" s="4"/>
       <c r="C760" s="4"/>
@@ -20113,7 +20119,7 @@
       <c r="BD760" s="4"/>
       <c r="BE760" s="4"/>
     </row>
-    <row r="761" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:57" ht="15.95" customHeight="1">
       <c r="A761" s="4"/>
       <c r="B761" s="4"/>
       <c r="C761" s="4"/>
@@ -20137,7 +20143,7 @@
       <c r="BD761" s="4"/>
       <c r="BE761" s="4"/>
     </row>
-    <row r="762" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:57" ht="15.95" customHeight="1">
       <c r="A762" s="4"/>
       <c r="B762" s="4"/>
       <c r="C762" s="4"/>
@@ -20161,7 +20167,7 @@
       <c r="BD762" s="4"/>
       <c r="BE762" s="4"/>
     </row>
-    <row r="763" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:57" ht="15.95" customHeight="1">
       <c r="A763" s="4"/>
       <c r="B763" s="4"/>
       <c r="C763" s="4"/>
@@ -20185,7 +20191,7 @@
       <c r="BD763" s="4"/>
       <c r="BE763" s="4"/>
     </row>
-    <row r="764" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:57" ht="15.95" customHeight="1">
       <c r="A764" s="4"/>
       <c r="B764" s="4"/>
       <c r="C764" s="4"/>
@@ -20209,7 +20215,7 @@
       <c r="BD764" s="4"/>
       <c r="BE764" s="4"/>
     </row>
-    <row r="765" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:57" ht="15.95" customHeight="1">
       <c r="A765" s="4"/>
       <c r="B765" s="4"/>
       <c r="C765" s="4"/>
@@ -20233,7 +20239,7 @@
       <c r="BD765" s="4"/>
       <c r="BE765" s="4"/>
     </row>
-    <row r="766" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:57" ht="15.95" customHeight="1">
       <c r="A766" s="4"/>
       <c r="B766" s="4"/>
       <c r="C766" s="4"/>
@@ -20257,7 +20263,7 @@
       <c r="BD766" s="4"/>
       <c r="BE766" s="4"/>
     </row>
-    <row r="767" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:57" ht="15.95" customHeight="1">
       <c r="A767" s="4"/>
       <c r="B767" s="4"/>
       <c r="C767" s="4"/>
@@ -20281,7 +20287,7 @@
       <c r="BD767" s="4"/>
       <c r="BE767" s="4"/>
     </row>
-    <row r="768" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:57" ht="15.95" customHeight="1">
       <c r="A768" s="4"/>
       <c r="B768" s="4"/>
       <c r="C768" s="4"/>
@@ -20305,7 +20311,7 @@
       <c r="BD768" s="4"/>
       <c r="BE768" s="4"/>
     </row>
-    <row r="769" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:57" ht="15.95" customHeight="1">
       <c r="A769" s="4"/>
       <c r="B769" s="4"/>
       <c r="C769" s="4"/>
@@ -20329,7 +20335,7 @@
       <c r="BD769" s="4"/>
       <c r="BE769" s="4"/>
     </row>
-    <row r="770" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:57" ht="15.95" customHeight="1">
       <c r="A770" s="4"/>
       <c r="B770" s="4"/>
       <c r="C770" s="4"/>
@@ -20353,7 +20359,7 @@
       <c r="BD770" s="4"/>
       <c r="BE770" s="4"/>
     </row>
-    <row r="771" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:57" ht="15.95" customHeight="1">
       <c r="A771" s="4"/>
       <c r="B771" s="4"/>
       <c r="C771" s="4"/>
@@ -20377,7 +20383,7 @@
       <c r="BD771" s="4"/>
       <c r="BE771" s="4"/>
     </row>
-    <row r="772" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:57" ht="15.95" customHeight="1">
       <c r="A772" s="4"/>
       <c r="B772" s="4"/>
       <c r="C772" s="4"/>
@@ -20401,7 +20407,7 @@
       <c r="BD772" s="4"/>
       <c r="BE772" s="4"/>
     </row>
-    <row r="773" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:57" ht="15.95" customHeight="1">
       <c r="A773" s="4"/>
       <c r="B773" s="4"/>
       <c r="C773" s="4"/>
@@ -20425,7 +20431,7 @@
       <c r="BD773" s="4"/>
       <c r="BE773" s="4"/>
     </row>
-    <row r="774" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:57" ht="15.95" customHeight="1">
       <c r="A774" s="4"/>
       <c r="B774" s="4"/>
       <c r="C774" s="4"/>
@@ -20449,7 +20455,7 @@
       <c r="BD774" s="4"/>
       <c r="BE774" s="4"/>
     </row>
-    <row r="775" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:57" ht="15.95" customHeight="1">
       <c r="A775" s="4"/>
       <c r="B775" s="4"/>
       <c r="C775" s="4"/>
@@ -20473,7 +20479,7 @@
       <c r="BD775" s="4"/>
       <c r="BE775" s="4"/>
     </row>
-    <row r="776" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:57" ht="15.95" customHeight="1">
       <c r="A776" s="4"/>
       <c r="B776" s="4"/>
       <c r="C776" s="4"/>
@@ -20497,7 +20503,7 @@
       <c r="BD776" s="4"/>
       <c r="BE776" s="4"/>
     </row>
-    <row r="777" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:57" ht="15.95" customHeight="1">
       <c r="A777" s="4"/>
       <c r="B777" s="4"/>
       <c r="C777" s="4"/>
@@ -20521,7 +20527,7 @@
       <c r="BD777" s="4"/>
       <c r="BE777" s="4"/>
     </row>
-    <row r="778" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:57" ht="15.95" customHeight="1">
       <c r="A778" s="4"/>
       <c r="B778" s="4"/>
       <c r="C778" s="4"/>
@@ -20545,7 +20551,7 @@
       <c r="BD778" s="4"/>
       <c r="BE778" s="4"/>
     </row>
-    <row r="779" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:57" ht="15.95" customHeight="1">
       <c r="A779" s="4"/>
       <c r="B779" s="4"/>
       <c r="C779" s="4"/>
@@ -20569,7 +20575,7 @@
       <c r="BD779" s="4"/>
       <c r="BE779" s="4"/>
     </row>
-    <row r="780" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:57" ht="15.95" customHeight="1">
       <c r="A780" s="4"/>
       <c r="B780" s="4"/>
       <c r="C780" s="4"/>
@@ -20593,7 +20599,7 @@
       <c r="BD780" s="4"/>
       <c r="BE780" s="4"/>
     </row>
-    <row r="781" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:57" ht="15.95" customHeight="1">
       <c r="A781" s="4"/>
       <c r="B781" s="4"/>
       <c r="C781" s="4"/>
@@ -20617,7 +20623,7 @@
       <c r="BD781" s="4"/>
       <c r="BE781" s="4"/>
     </row>
-    <row r="782" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:57" ht="15.95" customHeight="1">
       <c r="A782" s="4"/>
       <c r="B782" s="4"/>
       <c r="C782" s="4"/>
@@ -20641,7 +20647,7 @@
       <c r="BD782" s="4"/>
       <c r="BE782" s="4"/>
     </row>
-    <row r="783" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:57" ht="15.95" customHeight="1">
       <c r="A783" s="4"/>
       <c r="B783" s="4"/>
       <c r="C783" s="4"/>
@@ -20665,7 +20671,7 @@
       <c r="BD783" s="4"/>
       <c r="BE783" s="4"/>
     </row>
-    <row r="784" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:57" ht="15.95" customHeight="1">
       <c r="A784" s="4"/>
       <c r="B784" s="4"/>
       <c r="C784" s="4"/>
@@ -20689,7 +20695,7 @@
       <c r="BD784" s="4"/>
       <c r="BE784" s="4"/>
     </row>
-    <row r="785" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:57" ht="15.95" customHeight="1">
       <c r="A785" s="4"/>
       <c r="B785" s="4"/>
       <c r="C785" s="4"/>
@@ -20713,7 +20719,7 @@
       <c r="BD785" s="4"/>
       <c r="BE785" s="4"/>
     </row>
-    <row r="786" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:57" ht="15.95" customHeight="1">
       <c r="A786" s="4"/>
       <c r="B786" s="4"/>
       <c r="C786" s="4"/>
@@ -20737,7 +20743,7 @@
       <c r="BD786" s="4"/>
       <c r="BE786" s="4"/>
     </row>
-    <row r="787" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:57" ht="15.95" customHeight="1">
       <c r="A787" s="4"/>
       <c r="B787" s="4"/>
       <c r="C787" s="4"/>
@@ -20761,7 +20767,7 @@
       <c r="BD787" s="4"/>
       <c r="BE787" s="4"/>
     </row>
-    <row r="788" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:57" ht="15.95" customHeight="1">
       <c r="A788" s="4"/>
       <c r="B788" s="4"/>
       <c r="C788" s="4"/>
@@ -20785,7 +20791,7 @@
       <c r="BD788" s="4"/>
       <c r="BE788" s="4"/>
     </row>
-    <row r="789" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:57" ht="15.95" customHeight="1">
       <c r="A789" s="4"/>
       <c r="B789" s="4"/>
       <c r="C789" s="4"/>
@@ -20809,7 +20815,7 @@
       <c r="BD789" s="4"/>
       <c r="BE789" s="4"/>
     </row>
-    <row r="790" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:57" ht="15.95" customHeight="1">
       <c r="A790" s="4"/>
       <c r="B790" s="4"/>
       <c r="C790" s="4"/>
@@ -20833,7 +20839,7 @@
       <c r="BD790" s="4"/>
       <c r="BE790" s="4"/>
     </row>
-    <row r="791" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:57" ht="15.95" customHeight="1">
       <c r="A791" s="4"/>
       <c r="B791" s="4"/>
       <c r="C791" s="4"/>
@@ -20857,7 +20863,7 @@
       <c r="BD791" s="4"/>
       <c r="BE791" s="4"/>
     </row>
-    <row r="792" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:57" ht="15.95" customHeight="1">
       <c r="A792" s="4"/>
       <c r="B792" s="4"/>
       <c r="C792" s="4"/>
@@ -20881,7 +20887,7 @@
       <c r="BD792" s="4"/>
       <c r="BE792" s="4"/>
     </row>
-    <row r="793" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:57" ht="15.95" customHeight="1">
       <c r="A793" s="4"/>
       <c r="B793" s="4"/>
       <c r="C793" s="4"/>
@@ -20905,7 +20911,7 @@
       <c r="BD793" s="4"/>
       <c r="BE793" s="4"/>
     </row>
-    <row r="794" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:57" ht="15.95" customHeight="1">
       <c r="A794" s="4"/>
       <c r="B794" s="4"/>
       <c r="C794" s="4"/>
@@ -20929,7 +20935,7 @@
       <c r="BD794" s="4"/>
       <c r="BE794" s="4"/>
     </row>
-    <row r="795" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:57" ht="15.95" customHeight="1">
       <c r="A795" s="4"/>
       <c r="B795" s="4"/>
       <c r="C795" s="4"/>
@@ -20953,7 +20959,7 @@
       <c r="BD795" s="4"/>
       <c r="BE795" s="4"/>
     </row>
-    <row r="796" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:57" ht="15.95" customHeight="1">
       <c r="A796" s="4"/>
       <c r="B796" s="4"/>
       <c r="C796" s="4"/>
@@ -20977,7 +20983,7 @@
       <c r="BD796" s="4"/>
       <c r="BE796" s="4"/>
     </row>
-    <row r="797" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:57" ht="15.95" customHeight="1">
       <c r="A797" s="4"/>
       <c r="B797" s="4"/>
       <c r="C797" s="4"/>
@@ -21001,7 +21007,7 @@
       <c r="BD797" s="4"/>
       <c r="BE797" s="4"/>
     </row>
-    <row r="798" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:57" ht="15.95" customHeight="1">
       <c r="A798" s="4"/>
       <c r="B798" s="4"/>
       <c r="C798" s="4"/>
@@ -21025,7 +21031,7 @@
       <c r="BD798" s="4"/>
       <c r="BE798" s="4"/>
     </row>
-    <row r="799" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:57" ht="15.95" customHeight="1">
       <c r="A799" s="4"/>
       <c r="B799" s="4"/>
       <c r="C799" s="4"/>
@@ -21049,7 +21055,7 @@
       <c r="BD799" s="4"/>
       <c r="BE799" s="4"/>
     </row>
-    <row r="800" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:57" ht="15.95" customHeight="1">
       <c r="A800" s="4"/>
       <c r="B800" s="4"/>
       <c r="C800" s="4"/>
@@ -21073,7 +21079,7 @@
       <c r="BD800" s="4"/>
       <c r="BE800" s="4"/>
     </row>
-    <row r="801" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:57" ht="15.95" customHeight="1">
       <c r="A801" s="4"/>
       <c r="B801" s="4"/>
       <c r="C801" s="4"/>
@@ -21097,7 +21103,7 @@
       <c r="BD801" s="4"/>
       <c r="BE801" s="4"/>
     </row>
-    <row r="802" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="802" spans="1:57" ht="15.95" customHeight="1">
       <c r="A802" s="4"/>
       <c r="B802" s="4"/>
       <c r="C802" s="4"/>
@@ -21121,7 +21127,7 @@
       <c r="BD802" s="4"/>
       <c r="BE802" s="4"/>
     </row>
-    <row r="803" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:57" ht="15.95" customHeight="1">
       <c r="A803" s="4"/>
       <c r="B803" s="4"/>
       <c r="C803" s="4"/>
@@ -21145,7 +21151,7 @@
       <c r="BD803" s="4"/>
       <c r="BE803" s="4"/>
     </row>
-    <row r="804" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="804" spans="1:57" ht="15.95" customHeight="1">
       <c r="A804" s="4"/>
       <c r="B804" s="4"/>
       <c r="C804" s="4"/>
@@ -21169,7 +21175,7 @@
       <c r="BD804" s="4"/>
       <c r="BE804" s="4"/>
     </row>
-    <row r="805" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:57" ht="15.95" customHeight="1">
       <c r="A805" s="4"/>
       <c r="B805" s="4"/>
       <c r="C805" s="4"/>
@@ -21193,7 +21199,7 @@
       <c r="BD805" s="4"/>
       <c r="BE805" s="4"/>
     </row>
-    <row r="806" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:57" ht="15.95" customHeight="1">
       <c r="A806" s="4"/>
       <c r="B806" s="4"/>
       <c r="C806" s="4"/>
@@ -21217,7 +21223,7 @@
       <c r="BD806" s="4"/>
       <c r="BE806" s="4"/>
     </row>
-    <row r="807" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:57" ht="15.95" customHeight="1">
       <c r="A807" s="4"/>
       <c r="B807" s="4"/>
       <c r="C807" s="4"/>
@@ -21241,7 +21247,7 @@
       <c r="BD807" s="4"/>
       <c r="BE807" s="4"/>
     </row>
-    <row r="808" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:57" ht="15.95" customHeight="1">
       <c r="A808" s="4"/>
       <c r="B808" s="4"/>
       <c r="C808" s="4"/>
@@ -21265,7 +21271,7 @@
       <c r="BD808" s="4"/>
       <c r="BE808" s="4"/>
     </row>
-    <row r="809" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:57" ht="15.95" customHeight="1">
       <c r="A809" s="4"/>
       <c r="B809" s="4"/>
       <c r="C809" s="4"/>
@@ -21289,7 +21295,7 @@
       <c r="BD809" s="4"/>
       <c r="BE809" s="4"/>
     </row>
-    <row r="810" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:57" ht="15.95" customHeight="1">
       <c r="A810" s="4"/>
       <c r="B810" s="4"/>
       <c r="C810" s="4"/>
@@ -21313,7 +21319,7 @@
       <c r="BD810" s="4"/>
       <c r="BE810" s="4"/>
     </row>
-    <row r="811" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:57" ht="15.95" customHeight="1">
       <c r="A811" s="4"/>
       <c r="B811" s="4"/>
       <c r="C811" s="4"/>
@@ -21337,7 +21343,7 @@
       <c r="BD811" s="4"/>
       <c r="BE811" s="4"/>
     </row>
-    <row r="812" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:57" ht="15.95" customHeight="1">
       <c r="A812" s="4"/>
       <c r="B812" s="4"/>
       <c r="C812" s="4"/>
@@ -21361,7 +21367,7 @@
       <c r="BD812" s="4"/>
       <c r="BE812" s="4"/>
     </row>
-    <row r="813" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:57" ht="15.95" customHeight="1">
       <c r="A813" s="4"/>
       <c r="B813" s="4"/>
       <c r="C813" s="4"/>
@@ -21385,7 +21391,7 @@
       <c r="BD813" s="4"/>
       <c r="BE813" s="4"/>
     </row>
-    <row r="814" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="814" spans="1:57" ht="15.95" customHeight="1">
       <c r="A814" s="4"/>
       <c r="B814" s="4"/>
       <c r="C814" s="4"/>
@@ -21409,7 +21415,7 @@
       <c r="BD814" s="4"/>
       <c r="BE814" s="4"/>
     </row>
-    <row r="815" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:57" ht="15.95" customHeight="1">
       <c r="A815" s="4"/>
       <c r="B815" s="4"/>
       <c r="C815" s="4"/>
@@ -21433,7 +21439,7 @@
       <c r="BD815" s="4"/>
       <c r="BE815" s="4"/>
     </row>
-    <row r="816" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:57" ht="15.95" customHeight="1">
       <c r="A816" s="4"/>
       <c r="B816" s="4"/>
       <c r="C816" s="4"/>
@@ -21457,7 +21463,7 @@
       <c r="BD816" s="4"/>
       <c r="BE816" s="4"/>
     </row>
-    <row r="817" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:57" ht="15.95" customHeight="1">
       <c r="A817" s="4"/>
       <c r="B817" s="4"/>
       <c r="C817" s="4"/>
@@ -21481,7 +21487,7 @@
       <c r="BD817" s="4"/>
       <c r="BE817" s="4"/>
     </row>
-    <row r="818" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:57" ht="15.95" customHeight="1">
       <c r="A818" s="4"/>
       <c r="B818" s="4"/>
       <c r="C818" s="4"/>
@@ -21505,7 +21511,7 @@
       <c r="BD818" s="4"/>
       <c r="BE818" s="4"/>
     </row>
-    <row r="819" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:57" ht="15.95" customHeight="1">
       <c r="A819" s="4"/>
       <c r="B819" s="4"/>
       <c r="C819" s="4"/>
@@ -21529,7 +21535,7 @@
       <c r="BD819" s="4"/>
       <c r="BE819" s="4"/>
     </row>
-    <row r="820" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:57" ht="15.95" customHeight="1">
       <c r="A820" s="4"/>
       <c r="B820" s="4"/>
       <c r="C820" s="4"/>
@@ -21553,7 +21559,7 @@
       <c r="BD820" s="4"/>
       <c r="BE820" s="4"/>
     </row>
-    <row r="821" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:57" ht="15.95" customHeight="1">
       <c r="A821" s="4"/>
       <c r="B821" s="4"/>
       <c r="C821" s="4"/>
@@ -21577,7 +21583,7 @@
       <c r="BD821" s="4"/>
       <c r="BE821" s="4"/>
     </row>
-    <row r="822" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:57" ht="15.95" customHeight="1">
       <c r="A822" s="4"/>
       <c r="B822" s="4"/>
       <c r="C822" s="4"/>
@@ -21601,7 +21607,7 @@
       <c r="BD822" s="4"/>
       <c r="BE822" s="4"/>
     </row>
-    <row r="823" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:57" ht="15.95" customHeight="1">
       <c r="A823" s="4"/>
       <c r="B823" s="4"/>
       <c r="C823" s="4"/>
@@ -21625,7 +21631,7 @@
       <c r="BD823" s="4"/>
       <c r="BE823" s="4"/>
     </row>
-    <row r="824" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:57" ht="15.95" customHeight="1">
       <c r="A824" s="4"/>
       <c r="B824" s="4"/>
       <c r="C824" s="4"/>
@@ -21649,7 +21655,7 @@
       <c r="BD824" s="4"/>
       <c r="BE824" s="4"/>
     </row>
-    <row r="825" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:57" ht="15.95" customHeight="1">
       <c r="A825" s="4"/>
       <c r="B825" s="4"/>
       <c r="C825" s="4"/>
@@ -21673,7 +21679,7 @@
       <c r="BD825" s="4"/>
       <c r="BE825" s="4"/>
     </row>
-    <row r="826" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:57" ht="15.95" customHeight="1">
       <c r="A826" s="4"/>
       <c r="B826" s="4"/>
       <c r="C826" s="4"/>
@@ -21697,7 +21703,7 @@
       <c r="BD826" s="4"/>
       <c r="BE826" s="4"/>
     </row>
-    <row r="827" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:57" ht="15.95" customHeight="1">
       <c r="A827" s="4"/>
       <c r="B827" s="4"/>
       <c r="C827" s="4"/>
@@ -21721,7 +21727,7 @@
       <c r="BD827" s="4"/>
       <c r="BE827" s="4"/>
     </row>
-    <row r="828" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:57" ht="15.95" customHeight="1">
       <c r="A828" s="4"/>
       <c r="B828" s="4"/>
       <c r="C828" s="4"/>
@@ -21745,7 +21751,7 @@
       <c r="BD828" s="4"/>
       <c r="BE828" s="4"/>
     </row>
-    <row r="829" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:57" ht="15.95" customHeight="1">
       <c r="A829" s="4"/>
       <c r="B829" s="4"/>
       <c r="C829" s="4"/>
@@ -21769,7 +21775,7 @@
       <c r="BD829" s="4"/>
       <c r="BE829" s="4"/>
     </row>
-    <row r="830" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:57" ht="15.95" customHeight="1">
       <c r="A830" s="4"/>
       <c r="B830" s="4"/>
       <c r="C830" s="4"/>
@@ -21793,7 +21799,7 @@
       <c r="BD830" s="4"/>
       <c r="BE830" s="4"/>
     </row>
-    <row r="831" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:57" ht="15.95" customHeight="1">
       <c r="A831" s="4"/>
       <c r="B831" s="4"/>
       <c r="C831" s="4"/>
@@ -21817,7 +21823,7 @@
       <c r="BD831" s="4"/>
       <c r="BE831" s="4"/>
     </row>
-    <row r="832" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="832" spans="1:57" ht="15.95" customHeight="1">
       <c r="A832" s="4"/>
       <c r="B832" s="4"/>
       <c r="C832" s="4"/>
@@ -21841,7 +21847,7 @@
       <c r="BD832" s="4"/>
       <c r="BE832" s="4"/>
     </row>
-    <row r="833" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:57" ht="15.95" customHeight="1">
       <c r="A833" s="4"/>
       <c r="B833" s="4"/>
       <c r="C833" s="4"/>
@@ -21865,7 +21871,7 @@
       <c r="BD833" s="4"/>
       <c r="BE833" s="4"/>
     </row>
-    <row r="834" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:57" ht="15.95" customHeight="1">
       <c r="A834" s="4"/>
       <c r="B834" s="4"/>
       <c r="C834" s="4"/>
@@ -21889,7 +21895,7 @@
       <c r="BD834" s="4"/>
       <c r="BE834" s="4"/>
     </row>
-    <row r="835" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:57" ht="15.95" customHeight="1">
       <c r="A835" s="4"/>
       <c r="B835" s="4"/>
       <c r="C835" s="4"/>
@@ -21913,7 +21919,7 @@
       <c r="BD835" s="4"/>
       <c r="BE835" s="4"/>
     </row>
-    <row r="836" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="836" spans="1:57" ht="15.95" customHeight="1">
       <c r="A836" s="4"/>
       <c r="B836" s="4"/>
       <c r="C836" s="4"/>
@@ -21937,7 +21943,7 @@
       <c r="BD836" s="4"/>
       <c r="BE836" s="4"/>
     </row>
-    <row r="837" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:57" ht="15.95" customHeight="1">
       <c r="A837" s="4"/>
       <c r="B837" s="4"/>
       <c r="C837" s="4"/>
@@ -21961,7 +21967,7 @@
       <c r="BD837" s="4"/>
       <c r="BE837" s="4"/>
     </row>
-    <row r="838" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:57" ht="15.95" customHeight="1">
       <c r="A838" s="4"/>
       <c r="B838" s="4"/>
       <c r="C838" s="4"/>
@@ -21985,7 +21991,7 @@
       <c r="BD838" s="4"/>
       <c r="BE838" s="4"/>
     </row>
-    <row r="839" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:57" ht="15.95" customHeight="1">
       <c r="A839" s="4"/>
       <c r="B839" s="4"/>
       <c r="C839" s="4"/>
@@ -22009,7 +22015,7 @@
       <c r="BD839" s="4"/>
       <c r="BE839" s="4"/>
     </row>
-    <row r="840" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:57" ht="15.95" customHeight="1">
       <c r="A840" s="4"/>
       <c r="B840" s="4"/>
       <c r="C840" s="4"/>
@@ -22033,7 +22039,7 @@
       <c r="BD840" s="4"/>
       <c r="BE840" s="4"/>
     </row>
-    <row r="841" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:57" ht="15.95" customHeight="1">
       <c r="A841" s="4"/>
       <c r="B841" s="4"/>
       <c r="C841" s="4"/>
@@ -22057,7 +22063,7 @@
       <c r="BD841" s="4"/>
       <c r="BE841" s="4"/>
     </row>
-    <row r="842" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:57" ht="15.95" customHeight="1">
       <c r="A842" s="4"/>
       <c r="B842" s="4"/>
       <c r="C842" s="4"/>
@@ -22081,7 +22087,7 @@
       <c r="BD842" s="4"/>
       <c r="BE842" s="4"/>
     </row>
-    <row r="843" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="843" spans="1:57" ht="15.95" customHeight="1">
       <c r="A843" s="4"/>
       <c r="B843" s="4"/>
       <c r="C843" s="4"/>
@@ -22105,7 +22111,7 @@
       <c r="BD843" s="4"/>
       <c r="BE843" s="4"/>
     </row>
-    <row r="844" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="844" spans="1:57" ht="15.95" customHeight="1">
       <c r="A844" s="4"/>
       <c r="B844" s="4"/>
       <c r="C844" s="4"/>
@@ -22129,7 +22135,7 @@
       <c r="BD844" s="4"/>
       <c r="BE844" s="4"/>
     </row>
-    <row r="845" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="845" spans="1:57" ht="15.95" customHeight="1">
       <c r="A845" s="4"/>
       <c r="B845" s="4"/>
       <c r="C845" s="4"/>
@@ -22153,7 +22159,7 @@
       <c r="BD845" s="4"/>
       <c r="BE845" s="4"/>
     </row>
-    <row r="846" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="846" spans="1:57" ht="15.95" customHeight="1">
       <c r="A846" s="4"/>
       <c r="B846" s="4"/>
       <c r="C846" s="4"/>
@@ -22177,7 +22183,7 @@
       <c r="BD846" s="4"/>
       <c r="BE846" s="4"/>
     </row>
-    <row r="847" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="847" spans="1:57" ht="15.95" customHeight="1">
       <c r="A847" s="4"/>
       <c r="B847" s="4"/>
       <c r="C847" s="4"/>
@@ -22201,7 +22207,7 @@
       <c r="BD847" s="4"/>
       <c r="BE847" s="4"/>
     </row>
-    <row r="848" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:57" ht="15.95" customHeight="1">
       <c r="A848" s="4"/>
       <c r="B848" s="4"/>
       <c r="C848" s="4"/>
@@ -22225,7 +22231,7 @@
       <c r="BD848" s="4"/>
       <c r="BE848" s="4"/>
     </row>
-    <row r="849" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="849" spans="1:57" ht="15.95" customHeight="1">
       <c r="A849" s="4"/>
       <c r="B849" s="4"/>
       <c r="C849" s="4"/>
@@ -22249,7 +22255,7 @@
       <c r="BD849" s="4"/>
       <c r="BE849" s="4"/>
     </row>
-    <row r="850" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="850" spans="1:57" ht="15.95" customHeight="1">
       <c r="A850" s="4"/>
       <c r="B850" s="4"/>
       <c r="C850" s="4"/>
@@ -22273,7 +22279,7 @@
       <c r="BD850" s="4"/>
       <c r="BE850" s="4"/>
     </row>
-    <row r="851" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="851" spans="1:57" ht="15.95" customHeight="1">
       <c r="A851" s="4"/>
       <c r="B851" s="4"/>
       <c r="C851" s="4"/>
@@ -22297,7 +22303,7 @@
       <c r="BD851" s="4"/>
       <c r="BE851" s="4"/>
     </row>
-    <row r="852" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="852" spans="1:57" ht="15.95" customHeight="1">
       <c r="A852" s="4"/>
       <c r="B852" s="4"/>
       <c r="C852" s="4"/>
@@ -22321,7 +22327,7 @@
       <c r="BD852" s="4"/>
       <c r="BE852" s="4"/>
     </row>
-    <row r="853" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="853" spans="1:57" ht="15.95" customHeight="1">
       <c r="A853" s="4"/>
       <c r="B853" s="4"/>
       <c r="C853" s="4"/>
@@ -22345,7 +22351,7 @@
       <c r="BD853" s="4"/>
       <c r="BE853" s="4"/>
     </row>
-    <row r="854" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="854" spans="1:57" ht="15.95" customHeight="1">
       <c r="A854" s="4"/>
       <c r="B854" s="4"/>
       <c r="C854" s="4"/>
@@ -22369,7 +22375,7 @@
       <c r="BD854" s="4"/>
       <c r="BE854" s="4"/>
     </row>
-    <row r="855" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="855" spans="1:57" ht="15.95" customHeight="1">
       <c r="A855" s="4"/>
       <c r="B855" s="4"/>
       <c r="C855" s="4"/>
@@ -22393,7 +22399,7 @@
       <c r="BD855" s="4"/>
       <c r="BE855" s="4"/>
     </row>
-    <row r="856" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="856" spans="1:57" ht="15.95" customHeight="1">
       <c r="A856" s="4"/>
       <c r="B856" s="4"/>
       <c r="C856" s="4"/>
@@ -22417,7 +22423,7 @@
       <c r="BD856" s="4"/>
       <c r="BE856" s="4"/>
     </row>
-    <row r="857" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="857" spans="1:57" ht="15.95" customHeight="1">
       <c r="A857" s="4"/>
       <c r="B857" s="4"/>
       <c r="C857" s="4"/>
@@ -22441,7 +22447,7 @@
       <c r="BD857" s="4"/>
       <c r="BE857" s="4"/>
     </row>
-    <row r="858" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="858" spans="1:57" ht="15.95" customHeight="1">
       <c r="A858" s="4"/>
       <c r="B858" s="4"/>
       <c r="C858" s="4"/>
@@ -22465,7 +22471,7 @@
       <c r="BD858" s="4"/>
       <c r="BE858" s="4"/>
     </row>
-    <row r="859" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="859" spans="1:57" ht="15.95" customHeight="1">
       <c r="A859" s="4"/>
       <c r="B859" s="4"/>
       <c r="C859" s="4"/>
@@ -22489,7 +22495,7 @@
       <c r="BD859" s="4"/>
       <c r="BE859" s="4"/>
     </row>
-    <row r="860" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="860" spans="1:57" ht="15.95" customHeight="1">
       <c r="A860" s="4"/>
       <c r="B860" s="4"/>
       <c r="C860" s="4"/>
@@ -22513,7 +22519,7 @@
       <c r="BD860" s="4"/>
       <c r="BE860" s="4"/>
     </row>
-    <row r="861" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="861" spans="1:57" ht="15.95" customHeight="1">
       <c r="A861" s="4"/>
       <c r="B861" s="4"/>
       <c r="C861" s="4"/>
@@ -22537,7 +22543,7 @@
       <c r="BD861" s="4"/>
       <c r="BE861" s="4"/>
     </row>
-    <row r="862" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="862" spans="1:57" ht="15.95" customHeight="1">
       <c r="A862" s="4"/>
       <c r="B862" s="4"/>
       <c r="C862" s="4"/>
@@ -22561,7 +22567,7 @@
       <c r="BD862" s="4"/>
       <c r="BE862" s="4"/>
     </row>
-    <row r="863" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="863" spans="1:57" ht="15.95" customHeight="1">
       <c r="A863" s="4"/>
       <c r="B863" s="4"/>
       <c r="C863" s="4"/>
@@ -22585,7 +22591,7 @@
       <c r="BD863" s="4"/>
       <c r="BE863" s="4"/>
     </row>
-    <row r="864" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="864" spans="1:57" ht="15.95" customHeight="1">
       <c r="A864" s="4"/>
       <c r="B864" s="4"/>
       <c r="C864" s="4"/>
@@ -22609,7 +22615,7 @@
       <c r="BD864" s="4"/>
       <c r="BE864" s="4"/>
     </row>
-    <row r="865" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="865" spans="1:57" ht="15.95" customHeight="1">
       <c r="A865" s="4"/>
       <c r="B865" s="4"/>
       <c r="C865" s="4"/>
@@ -22633,7 +22639,7 @@
       <c r="BD865" s="4"/>
       <c r="BE865" s="4"/>
     </row>
-    <row r="866" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="866" spans="1:57" ht="15.95" customHeight="1">
       <c r="A866" s="4"/>
       <c r="B866" s="4"/>
       <c r="C866" s="4"/>
@@ -22657,7 +22663,7 @@
       <c r="BD866" s="4"/>
       <c r="BE866" s="4"/>
     </row>
-    <row r="867" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="867" spans="1:57" ht="15.95" customHeight="1">
       <c r="A867" s="4"/>
       <c r="B867" s="4"/>
       <c r="C867" s="4"/>
@@ -22681,7 +22687,7 @@
       <c r="BD867" s="4"/>
       <c r="BE867" s="4"/>
     </row>
-    <row r="868" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="868" spans="1:57" ht="15.95" customHeight="1">
       <c r="A868" s="4"/>
       <c r="B868" s="4"/>
       <c r="C868" s="4"/>
@@ -22705,7 +22711,7 @@
       <c r="BD868" s="4"/>
       <c r="BE868" s="4"/>
     </row>
-    <row r="869" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="869" spans="1:57" ht="15.95" customHeight="1">
       <c r="A869" s="4"/>
       <c r="B869" s="4"/>
       <c r="C869" s="4"/>
@@ -22729,7 +22735,7 @@
       <c r="BD869" s="4"/>
       <c r="BE869" s="4"/>
     </row>
-    <row r="870" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="870" spans="1:57" ht="15.95" customHeight="1">
       <c r="A870" s="4"/>
       <c r="B870" s="4"/>
       <c r="C870" s="4"/>
@@ -22753,7 +22759,7 @@
       <c r="BD870" s="4"/>
       <c r="BE870" s="4"/>
     </row>
-    <row r="871" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="871" spans="1:57" ht="15.95" customHeight="1">
       <c r="A871" s="4"/>
       <c r="B871" s="4"/>
       <c r="C871" s="4"/>
@@ -22777,7 +22783,7 @@
       <c r="BD871" s="4"/>
       <c r="BE871" s="4"/>
     </row>
-    <row r="872" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="872" spans="1:57" ht="15.95" customHeight="1">
       <c r="A872" s="4"/>
       <c r="B872" s="4"/>
       <c r="C872" s="4"/>
@@ -22801,7 +22807,7 @@
       <c r="BD872" s="4"/>
       <c r="BE872" s="4"/>
     </row>
-    <row r="873" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="873" spans="1:57" ht="15.95" customHeight="1">
       <c r="A873" s="4"/>
       <c r="B873" s="4"/>
       <c r="C873" s="4"/>
@@ -22825,7 +22831,7 @@
       <c r="BD873" s="4"/>
       <c r="BE873" s="4"/>
     </row>
-    <row r="874" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="874" spans="1:57" ht="15.95" customHeight="1">
       <c r="A874" s="4"/>
       <c r="B874" s="4"/>
       <c r="C874" s="4"/>
@@ -22849,7 +22855,7 @@
       <c r="BD874" s="4"/>
       <c r="BE874" s="4"/>
     </row>
-    <row r="875" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="875" spans="1:57" ht="15.95" customHeight="1">
       <c r="A875" s="4"/>
       <c r="B875" s="4"/>
       <c r="C875" s="4"/>
@@ -22873,7 +22879,7 @@
       <c r="BD875" s="4"/>
       <c r="BE875" s="4"/>
     </row>
-    <row r="876" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="876" spans="1:57" ht="15.95" customHeight="1">
       <c r="A876" s="4"/>
       <c r="B876" s="4"/>
       <c r="C876" s="4"/>
@@ -22897,7 +22903,7 @@
       <c r="BD876" s="4"/>
       <c r="BE876" s="4"/>
     </row>
-    <row r="877" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="877" spans="1:57" ht="15.95" customHeight="1">
       <c r="A877" s="4"/>
       <c r="B877" s="4"/>
       <c r="C877" s="4"/>
@@ -22921,7 +22927,7 @@
       <c r="BD877" s="4"/>
       <c r="BE877" s="4"/>
     </row>
-    <row r="878" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="878" spans="1:57" ht="15.95" customHeight="1">
       <c r="A878" s="4"/>
       <c r="B878" s="4"/>
       <c r="C878" s="4"/>
@@ -22945,7 +22951,7 @@
       <c r="BD878" s="4"/>
       <c r="BE878" s="4"/>
     </row>
-    <row r="879" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="879" spans="1:57" ht="15.95" customHeight="1">
       <c r="A879" s="4"/>
       <c r="B879" s="4"/>
       <c r="C879" s="4"/>
@@ -22969,7 +22975,7 @@
       <c r="BD879" s="4"/>
       <c r="BE879" s="4"/>
     </row>
-    <row r="880" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="880" spans="1:57" ht="15.95" customHeight="1">
       <c r="A880" s="4"/>
       <c r="B880" s="4"/>
       <c r="C880" s="4"/>
@@ -22993,7 +22999,7 @@
       <c r="BD880" s="4"/>
       <c r="BE880" s="4"/>
     </row>
-    <row r="881" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="881" spans="1:57" ht="15.95" customHeight="1">
       <c r="A881" s="4"/>
       <c r="B881" s="4"/>
       <c r="C881" s="4"/>
@@ -23017,7 +23023,7 @@
       <c r="BD881" s="4"/>
       <c r="BE881" s="4"/>
     </row>
-    <row r="882" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="882" spans="1:57" ht="15.95" customHeight="1">
       <c r="A882" s="4"/>
       <c r="B882" s="4"/>
       <c r="C882" s="4"/>
@@ -23041,7 +23047,7 @@
       <c r="BD882" s="4"/>
       <c r="BE882" s="4"/>
     </row>
-    <row r="883" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="883" spans="1:57" ht="15.95" customHeight="1">
       <c r="A883" s="4"/>
       <c r="B883" s="4"/>
       <c r="C883" s="4"/>
@@ -23065,7 +23071,7 @@
       <c r="BD883" s="4"/>
       <c r="BE883" s="4"/>
     </row>
-    <row r="884" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="884" spans="1:57" ht="15.95" customHeight="1">
       <c r="A884" s="4"/>
       <c r="B884" s="4"/>
       <c r="C884" s="4"/>
@@ -23089,7 +23095,7 @@
       <c r="BD884" s="4"/>
       <c r="BE884" s="4"/>
     </row>
-    <row r="885" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="885" spans="1:57" ht="15.95" customHeight="1">
       <c r="A885" s="4"/>
       <c r="B885" s="4"/>
       <c r="C885" s="4"/>
@@ -23113,7 +23119,7 @@
       <c r="BD885" s="4"/>
       <c r="BE885" s="4"/>
     </row>
-    <row r="886" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:57" ht="15.95" customHeight="1">
       <c r="A886" s="4"/>
       <c r="B886" s="4"/>
       <c r="C886" s="4"/>
@@ -23137,7 +23143,7 @@
       <c r="BD886" s="4"/>
       <c r="BE886" s="4"/>
     </row>
-    <row r="887" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:57" ht="15.95" customHeight="1">
       <c r="A887" s="4"/>
       <c r="B887" s="4"/>
       <c r="C887" s="4"/>
@@ -23161,7 +23167,7 @@
       <c r="BD887" s="4"/>
       <c r="BE887" s="4"/>
     </row>
-    <row r="888" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:57" ht="15.95" customHeight="1">
       <c r="A888" s="4"/>
       <c r="B888" s="4"/>
       <c r="C888" s="4"/>
@@ -23185,7 +23191,7 @@
       <c r="BD888" s="4"/>
       <c r="BE888" s="4"/>
     </row>
-    <row r="889" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:57" ht="15.95" customHeight="1">
       <c r="A889" s="4"/>
       <c r="B889" s="4"/>
       <c r="C889" s="4"/>
@@ -23209,7 +23215,7 @@
       <c r="BD889" s="4"/>
       <c r="BE889" s="4"/>
     </row>
-    <row r="890" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:57" ht="15.95" customHeight="1">
       <c r="A890" s="4"/>
       <c r="B890" s="4"/>
       <c r="C890" s="4"/>
@@ -23233,7 +23239,7 @@
       <c r="BD890" s="4"/>
       <c r="BE890" s="4"/>
     </row>
-    <row r="891" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:57" ht="15.95" customHeight="1">
       <c r="A891" s="4"/>
       <c r="B891" s="4"/>
       <c r="C891" s="4"/>
@@ -23257,7 +23263,7 @@
       <c r="BD891" s="4"/>
       <c r="BE891" s="4"/>
     </row>
-    <row r="892" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:57" ht="15.95" customHeight="1">
       <c r="A892" s="4"/>
       <c r="B892" s="4"/>
       <c r="C892" s="4"/>
@@ -23281,7 +23287,7 @@
       <c r="BD892" s="4"/>
       <c r="BE892" s="4"/>
     </row>
-    <row r="893" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:57" ht="15.95" customHeight="1">
       <c r="A893" s="4"/>
       <c r="B893" s="4"/>
       <c r="C893" s="4"/>
@@ -23305,7 +23311,7 @@
       <c r="BD893" s="4"/>
       <c r="BE893" s="4"/>
     </row>
-    <row r="894" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:57" ht="15.95" customHeight="1">
       <c r="A894" s="4"/>
       <c r="B894" s="4"/>
       <c r="C894" s="4"/>
@@ -23329,7 +23335,7 @@
       <c r="BD894" s="4"/>
       <c r="BE894" s="4"/>
     </row>
-    <row r="895" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:57" ht="15.95" customHeight="1">
       <c r="A895" s="4"/>
       <c r="B895" s="4"/>
       <c r="C895" s="4"/>
@@ -23353,7 +23359,7 @@
       <c r="BD895" s="4"/>
       <c r="BE895" s="4"/>
     </row>
-    <row r="896" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="896" spans="1:57" ht="15.95" customHeight="1">
       <c r="A896" s="4"/>
       <c r="B896" s="4"/>
       <c r="C896" s="4"/>
@@ -23377,7 +23383,7 @@
       <c r="BD896" s="4"/>
       <c r="BE896" s="4"/>
     </row>
-    <row r="897" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="897" spans="1:57" ht="15.95" customHeight="1">
       <c r="A897" s="4"/>
       <c r="B897" s="4"/>
       <c r="C897" s="4"/>
@@ -23401,7 +23407,7 @@
       <c r="BD897" s="4"/>
       <c r="BE897" s="4"/>
     </row>
-    <row r="898" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:57" ht="15.95" customHeight="1">
       <c r="A898" s="4"/>
       <c r="B898" s="4"/>
       <c r="C898" s="4"/>
@@ -23425,7 +23431,7 @@
       <c r="BD898" s="4"/>
       <c r="BE898" s="4"/>
     </row>
-    <row r="899" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="899" spans="1:57" ht="15.95" customHeight="1">
       <c r="A899" s="4"/>
       <c r="B899" s="4"/>
       <c r="C899" s="4"/>
@@ -23449,7 +23455,7 @@
       <c r="BD899" s="4"/>
       <c r="BE899" s="4"/>
     </row>
-    <row r="900" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="900" spans="1:57" ht="15.95" customHeight="1">
       <c r="A900" s="4"/>
       <c r="B900" s="4"/>
       <c r="C900" s="4"/>
@@ -23473,7 +23479,7 @@
       <c r="BD900" s="4"/>
       <c r="BE900" s="4"/>
     </row>
-    <row r="901" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="901" spans="1:57" ht="15.95" customHeight="1">
       <c r="A901" s="4"/>
       <c r="B901" s="4"/>
       <c r="C901" s="4"/>
@@ -23497,7 +23503,7 @@
       <c r="BD901" s="4"/>
       <c r="BE901" s="4"/>
     </row>
-    <row r="902" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="902" spans="1:57" ht="15.95" customHeight="1">
       <c r="A902" s="4"/>
       <c r="B902" s="4"/>
       <c r="C902" s="4"/>
@@ -23521,7 +23527,7 @@
       <c r="BD902" s="4"/>
       <c r="BE902" s="4"/>
     </row>
-    <row r="903" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="903" spans="1:57" ht="15.95" customHeight="1">
       <c r="A903" s="4"/>
       <c r="B903" s="4"/>
       <c r="C903" s="4"/>
@@ -23545,7 +23551,7 @@
       <c r="BD903" s="4"/>
       <c r="BE903" s="4"/>
     </row>
-    <row r="904" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="904" spans="1:57" ht="15.95" customHeight="1">
       <c r="A904" s="4"/>
       <c r="B904" s="4"/>
       <c r="C904" s="4"/>
@@ -23569,7 +23575,7 @@
       <c r="BD904" s="4"/>
       <c r="BE904" s="4"/>
     </row>
-    <row r="905" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="905" spans="1:57" ht="15.95" customHeight="1">
       <c r="A905" s="4"/>
       <c r="B905" s="4"/>
       <c r="C905" s="4"/>
@@ -23593,7 +23599,7 @@
       <c r="BD905" s="4"/>
       <c r="BE905" s="4"/>
     </row>
-    <row r="906" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="906" spans="1:57" ht="15.95" customHeight="1">
       <c r="A906" s="4"/>
       <c r="B906" s="4"/>
       <c r="C906" s="4"/>
@@ -23617,7 +23623,7 @@
       <c r="BD906" s="4"/>
       <c r="BE906" s="4"/>
     </row>
-    <row r="907" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="907" spans="1:57" ht="15.95" customHeight="1">
       <c r="A907" s="4"/>
       <c r="B907" s="4"/>
       <c r="C907" s="4"/>
@@ -23641,7 +23647,7 @@
       <c r="BD907" s="4"/>
       <c r="BE907" s="4"/>
     </row>
-    <row r="908" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="908" spans="1:57" ht="15.95" customHeight="1">
       <c r="A908" s="4"/>
       <c r="B908" s="4"/>
       <c r="C908" s="4"/>
@@ -23665,7 +23671,7 @@
       <c r="BD908" s="4"/>
       <c r="BE908" s="4"/>
     </row>
-    <row r="909" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="909" spans="1:57" ht="15.95" customHeight="1">
       <c r="A909" s="4"/>
       <c r="B909" s="4"/>
       <c r="C909" s="4"/>
@@ -23689,7 +23695,7 @@
       <c r="BD909" s="4"/>
       <c r="BE909" s="4"/>
     </row>
-    <row r="910" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="910" spans="1:57" ht="15.95" customHeight="1">
       <c r="A910" s="4"/>
       <c r="B910" s="4"/>
       <c r="C910" s="4"/>
@@ -23713,7 +23719,7 @@
       <c r="BD910" s="4"/>
       <c r="BE910" s="4"/>
     </row>
-    <row r="911" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="911" spans="1:57" ht="15.95" customHeight="1">
       <c r="A911" s="4"/>
       <c r="B911" s="4"/>
       <c r="C911" s="4"/>
@@ -23737,7 +23743,7 @@
       <c r="BD911" s="4"/>
       <c r="BE911" s="4"/>
     </row>
-    <row r="912" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="912" spans="1:57" ht="15.95" customHeight="1">
       <c r="A912" s="4"/>
       <c r="B912" s="4"/>
       <c r="C912" s="4"/>
@@ -23761,7 +23767,7 @@
       <c r="BD912" s="4"/>
       <c r="BE912" s="4"/>
     </row>
-    <row r="913" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="913" spans="1:57" ht="15.95" customHeight="1">
       <c r="A913" s="4"/>
       <c r="B913" s="4"/>
       <c r="C913" s="4"/>
@@ -23785,7 +23791,7 @@
       <c r="BD913" s="4"/>
       <c r="BE913" s="4"/>
     </row>
-    <row r="914" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="914" spans="1:57" ht="15.95" customHeight="1">
       <c r="A914" s="4"/>
       <c r="B914" s="4"/>
       <c r="C914" s="4"/>
@@ -23809,7 +23815,7 @@
       <c r="BD914" s="4"/>
       <c r="BE914" s="4"/>
     </row>
-    <row r="915" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="915" spans="1:57" ht="15.95" customHeight="1">
       <c r="A915" s="4"/>
       <c r="B915" s="4"/>
       <c r="C915" s="4"/>
@@ -23833,7 +23839,7 @@
       <c r="BD915" s="4"/>
       <c r="BE915" s="4"/>
     </row>
-    <row r="916" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="916" spans="1:57" ht="15.95" customHeight="1">
       <c r="A916" s="4"/>
       <c r="B916" s="4"/>
       <c r="C916" s="4"/>
@@ -23857,7 +23863,7 @@
       <c r="BD916" s="4"/>
       <c r="BE916" s="4"/>
     </row>
-    <row r="917" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="917" spans="1:57" ht="15.95" customHeight="1">
       <c r="A917" s="4"/>
       <c r="B917" s="4"/>
       <c r="C917" s="4"/>
@@ -23881,7 +23887,7 @@
       <c r="BD917" s="4"/>
       <c r="BE917" s="4"/>
     </row>
-    <row r="918" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="918" spans="1:57" ht="15.95" customHeight="1">
       <c r="A918" s="4"/>
       <c r="B918" s="4"/>
       <c r="C918" s="4"/>
@@ -23905,7 +23911,7 @@
       <c r="BD918" s="4"/>
       <c r="BE918" s="4"/>
     </row>
-    <row r="919" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="919" spans="1:57" ht="15.95" customHeight="1">
       <c r="A919" s="4"/>
       <c r="B919" s="4"/>
       <c r="C919" s="4"/>
@@ -23929,7 +23935,7 @@
       <c r="BD919" s="4"/>
       <c r="BE919" s="4"/>
     </row>
-    <row r="920" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="920" spans="1:57" ht="15.95" customHeight="1">
       <c r="A920" s="4"/>
       <c r="B920" s="4"/>
       <c r="C920" s="4"/>
@@ -23953,7 +23959,7 @@
       <c r="BD920" s="4"/>
       <c r="BE920" s="4"/>
     </row>
-    <row r="921" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="921" spans="1:57" ht="15.95" customHeight="1">
       <c r="A921" s="4"/>
       <c r="B921" s="4"/>
       <c r="C921" s="4"/>
@@ -23977,7 +23983,7 @@
       <c r="BD921" s="4"/>
       <c r="BE921" s="4"/>
     </row>
-    <row r="922" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="922" spans="1:57" ht="15.95" customHeight="1">
       <c r="A922" s="4"/>
       <c r="B922" s="4"/>
       <c r="C922" s="4"/>
@@ -24001,7 +24007,7 @@
       <c r="BD922" s="4"/>
       <c r="BE922" s="4"/>
     </row>
-    <row r="923" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="923" spans="1:57" ht="15.95" customHeight="1">
       <c r="A923" s="4"/>
       <c r="B923" s="4"/>
       <c r="C923" s="4"/>
@@ -24025,7 +24031,7 @@
       <c r="BD923" s="4"/>
       <c r="BE923" s="4"/>
     </row>
-    <row r="924" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="924" spans="1:57" ht="15.95" customHeight="1">
       <c r="A924" s="4"/>
       <c r="B924" s="4"/>
       <c r="C924" s="4"/>
@@ -24049,7 +24055,7 @@
       <c r="BD924" s="4"/>
       <c r="BE924" s="4"/>
     </row>
-    <row r="925" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="925" spans="1:57" ht="15.95" customHeight="1">
       <c r="A925" s="4"/>
       <c r="B925" s="4"/>
       <c r="C925" s="4"/>
@@ -24073,7 +24079,7 @@
       <c r="BD925" s="4"/>
       <c r="BE925" s="4"/>
     </row>
-    <row r="926" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="926" spans="1:57" ht="15.95" customHeight="1">
       <c r="A926" s="4"/>
       <c r="B926" s="4"/>
       <c r="C926" s="4"/>
@@ -24097,7 +24103,7 @@
       <c r="BD926" s="4"/>
       <c r="BE926" s="4"/>
     </row>
-    <row r="927" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="927" spans="1:57" ht="15.95" customHeight="1">
       <c r="A927" s="4"/>
       <c r="B927" s="4"/>
       <c r="C927" s="4"/>
@@ -24121,7 +24127,7 @@
       <c r="BD927" s="4"/>
       <c r="BE927" s="4"/>
     </row>
-    <row r="928" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="928" spans="1:57" ht="15.95" customHeight="1">
       <c r="A928" s="4"/>
       <c r="B928" s="4"/>
       <c r="C928" s="4"/>
@@ -24145,7 +24151,7 @@
       <c r="BD928" s="4"/>
       <c r="BE928" s="4"/>
     </row>
-    <row r="929" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="929" spans="1:57" ht="15.95" customHeight="1">
       <c r="A929" s="4"/>
       <c r="B929" s="4"/>
       <c r="C929" s="4"/>
@@ -24169,7 +24175,7 @@
       <c r="BD929" s="4"/>
       <c r="BE929" s="4"/>
     </row>
-    <row r="930" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="930" spans="1:57" ht="15.95" customHeight="1">
       <c r="A930" s="4"/>
       <c r="B930" s="4"/>
       <c r="C930" s="4"/>
@@ -24193,7 +24199,7 @@
       <c r="BD930" s="4"/>
       <c r="BE930" s="4"/>
     </row>
-    <row r="931" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="931" spans="1:57" ht="15.95" customHeight="1">
       <c r="A931" s="4"/>
       <c r="B931" s="4"/>
       <c r="C931" s="4"/>
@@ -24217,7 +24223,7 @@
       <c r="BD931" s="4"/>
       <c r="BE931" s="4"/>
     </row>
-    <row r="932" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="932" spans="1:57" ht="15.95" customHeight="1">
       <c r="A932" s="4"/>
       <c r="B932" s="4"/>
       <c r="C932" s="4"/>
@@ -24241,7 +24247,7 @@
       <c r="BD932" s="4"/>
       <c r="BE932" s="4"/>
     </row>
-    <row r="933" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="933" spans="1:57" ht="15.95" customHeight="1">
       <c r="A933" s="4"/>
       <c r="B933" s="4"/>
       <c r="C933" s="4"/>
@@ -24265,7 +24271,7 @@
       <c r="BD933" s="4"/>
       <c r="BE933" s="4"/>
     </row>
-    <row r="934" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="934" spans="1:57" ht="15.95" customHeight="1">
       <c r="A934" s="4"/>
       <c r="B934" s="4"/>
       <c r="C934" s="4"/>
@@ -24289,7 +24295,7 @@
       <c r="BD934" s="4"/>
       <c r="BE934" s="4"/>
     </row>
-    <row r="935" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="935" spans="1:57" ht="15.95" customHeight="1">
       <c r="A935" s="4"/>
       <c r="B935" s="4"/>
       <c r="C935" s="4"/>
@@ -24313,7 +24319,7 @@
       <c r="BD935" s="4"/>
       <c r="BE935" s="4"/>
     </row>
-    <row r="936" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="936" spans="1:57" ht="15.95" customHeight="1">
       <c r="A936" s="4"/>
       <c r="B936" s="4"/>
       <c r="C936" s="4"/>
@@ -24337,7 +24343,7 @@
       <c r="BD936" s="4"/>
       <c r="BE936" s="4"/>
     </row>
-    <row r="937" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="937" spans="1:57" ht="15.95" customHeight="1">
       <c r="A937" s="4"/>
       <c r="B937" s="4"/>
       <c r="C937" s="4"/>
@@ -24361,7 +24367,7 @@
       <c r="BD937" s="4"/>
       <c r="BE937" s="4"/>
     </row>
-    <row r="938" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="938" spans="1:57" ht="15.95" customHeight="1">
       <c r="A938" s="4"/>
       <c r="B938" s="4"/>
       <c r="C938" s="4"/>
@@ -24385,7 +24391,7 @@
       <c r="BD938" s="4"/>
       <c r="BE938" s="4"/>
     </row>
-    <row r="939" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="939" spans="1:57" ht="15.95" customHeight="1">
       <c r="A939" s="4"/>
       <c r="B939" s="4"/>
       <c r="C939" s="4"/>
@@ -24409,7 +24415,7 @@
       <c r="BD939" s="4"/>
       <c r="BE939" s="4"/>
     </row>
-    <row r="940" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="940" spans="1:57" ht="15.95" customHeight="1">
       <c r="A940" s="4"/>
       <c r="B940" s="4"/>
       <c r="C940" s="4"/>
@@ -24433,7 +24439,7 @@
       <c r="BD940" s="4"/>
       <c r="BE940" s="4"/>
     </row>
-    <row r="941" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="941" spans="1:57" ht="15.95" customHeight="1">
       <c r="A941" s="4"/>
       <c r="B941" s="4"/>
       <c r="C941" s="4"/>
@@ -24457,7 +24463,7 @@
       <c r="BD941" s="4"/>
       <c r="BE941" s="4"/>
     </row>
-    <row r="942" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="942" spans="1:57" ht="15.95" customHeight="1">
       <c r="A942" s="4"/>
       <c r="B942" s="4"/>
       <c r="C942" s="4"/>
@@ -24481,7 +24487,7 @@
       <c r="BD942" s="4"/>
       <c r="BE942" s="4"/>
     </row>
-    <row r="943" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="943" spans="1:57" ht="15.95" customHeight="1">
       <c r="A943" s="4"/>
       <c r="B943" s="4"/>
       <c r="C943" s="4"/>
@@ -24505,7 +24511,7 @@
       <c r="BD943" s="4"/>
       <c r="BE943" s="4"/>
     </row>
-    <row r="944" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="944" spans="1:57" ht="15.95" customHeight="1">
       <c r="A944" s="4"/>
       <c r="B944" s="4"/>
       <c r="C944" s="4"/>
@@ -24529,7 +24535,7 @@
       <c r="BD944" s="4"/>
       <c r="BE944" s="4"/>
     </row>
-    <row r="945" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="945" spans="1:57" ht="15.95" customHeight="1">
       <c r="A945" s="4"/>
       <c r="B945" s="4"/>
       <c r="C945" s="4"/>
@@ -24553,7 +24559,7 @@
       <c r="BD945" s="4"/>
       <c r="BE945" s="4"/>
     </row>
-    <row r="946" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="946" spans="1:57" ht="15.95" customHeight="1">
       <c r="A946" s="4"/>
       <c r="B946" s="4"/>
       <c r="C946" s="4"/>
@@ -24577,7 +24583,7 @@
       <c r="BD946" s="4"/>
       <c r="BE946" s="4"/>
     </row>
-    <row r="947" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="947" spans="1:57" ht="15.95" customHeight="1">
       <c r="A947" s="4"/>
       <c r="B947" s="4"/>
       <c r="C947" s="4"/>
@@ -24601,7 +24607,7 @@
       <c r="BD947" s="4"/>
       <c r="BE947" s="4"/>
     </row>
-    <row r="948" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="948" spans="1:57" ht="15.95" customHeight="1">
       <c r="A948" s="4"/>
       <c r="B948" s="4"/>
       <c r="C948" s="4"/>
@@ -24625,7 +24631,7 @@
       <c r="BD948" s="4"/>
       <c r="BE948" s="4"/>
     </row>
-    <row r="949" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="949" spans="1:57" ht="15.95" customHeight="1">
       <c r="A949" s="4"/>
       <c r="B949" s="4"/>
       <c r="C949" s="4"/>
@@ -24649,7 +24655,7 @@
       <c r="BD949" s="4"/>
       <c r="BE949" s="4"/>
     </row>
-    <row r="950" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="950" spans="1:57" ht="15.95" customHeight="1">
       <c r="A950" s="4"/>
       <c r="B950" s="4"/>
       <c r="C950" s="4"/>
@@ -24673,7 +24679,7 @@
       <c r="BD950" s="4"/>
       <c r="BE950" s="4"/>
     </row>
-    <row r="951" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="951" spans="1:57" ht="15.95" customHeight="1">
       <c r="A951" s="4"/>
       <c r="B951" s="4"/>
       <c r="C951" s="4"/>
@@ -24697,7 +24703,7 @@
       <c r="BD951" s="4"/>
       <c r="BE951" s="4"/>
     </row>
-    <row r="952" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="952" spans="1:57" ht="15.95" customHeight="1">
       <c r="A952" s="4"/>
       <c r="B952" s="4"/>
       <c r="C952" s="4"/>
@@ -24721,7 +24727,7 @@
       <c r="BD952" s="4"/>
       <c r="BE952" s="4"/>
     </row>
-    <row r="953" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="953" spans="1:57" ht="15.95" customHeight="1">
       <c r="A953" s="4"/>
       <c r="B953" s="4"/>
       <c r="C953" s="4"/>
@@ -24745,7 +24751,7 @@
       <c r="BD953" s="4"/>
       <c r="BE953" s="4"/>
     </row>
-    <row r="954" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="954" spans="1:57" ht="15.95" customHeight="1">
       <c r="A954" s="4"/>
       <c r="B954" s="4"/>
       <c r="C954" s="4"/>
@@ -24769,7 +24775,7 @@
       <c r="BD954" s="4"/>
       <c r="BE954" s="4"/>
     </row>
-    <row r="955" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="955" spans="1:57" ht="15.95" customHeight="1">
       <c r="A955" s="4"/>
       <c r="B955" s="4"/>
       <c r="C955" s="4"/>
@@ -24793,7 +24799,7 @@
       <c r="BD955" s="4"/>
       <c r="BE955" s="4"/>
     </row>
-    <row r="956" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="956" spans="1:57" ht="15.95" customHeight="1">
       <c r="A956" s="4"/>
       <c r="B956" s="4"/>
       <c r="C956" s="4"/>
@@ -24817,7 +24823,7 @@
       <c r="BD956" s="4"/>
       <c r="BE956" s="4"/>
     </row>
-    <row r="957" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="957" spans="1:57" ht="15.95" customHeight="1">
       <c r="A957" s="4"/>
       <c r="B957" s="4"/>
       <c r="C957" s="4"/>
@@ -24841,7 +24847,7 @@
       <c r="BD957" s="4"/>
       <c r="BE957" s="4"/>
     </row>
-    <row r="958" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="958" spans="1:57" ht="15.95" customHeight="1">
       <c r="A958" s="4"/>
       <c r="B958" s="4"/>
       <c r="C958" s="4"/>
@@ -24865,7 +24871,7 @@
       <c r="BD958" s="4"/>
       <c r="BE958" s="4"/>
     </row>
-    <row r="959" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="959" spans="1:57" ht="15.95" customHeight="1">
       <c r="A959" s="4"/>
       <c r="B959" s="4"/>
       <c r="C959" s="4"/>
@@ -24889,7 +24895,7 @@
       <c r="BD959" s="4"/>
       <c r="BE959" s="4"/>
     </row>
-    <row r="960" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="960" spans="1:57" ht="15.95" customHeight="1">
       <c r="A960" s="4"/>
       <c r="B960" s="4"/>
       <c r="C960" s="4"/>
@@ -24913,7 +24919,7 @@
       <c r="BD960" s="4"/>
       <c r="BE960" s="4"/>
     </row>
-    <row r="961" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="961" spans="1:57" ht="15.95" customHeight="1">
       <c r="A961" s="4"/>
       <c r="B961" s="4"/>
       <c r="C961" s="4"/>
@@ -24937,7 +24943,7 @@
       <c r="BD961" s="4"/>
       <c r="BE961" s="4"/>
     </row>
-    <row r="962" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="962" spans="1:57" ht="15.95" customHeight="1">
       <c r="A962" s="4"/>
       <c r="B962" s="4"/>
       <c r="C962" s="4"/>
@@ -24961,7 +24967,7 @@
       <c r="BD962" s="4"/>
       <c r="BE962" s="4"/>
     </row>
-    <row r="963" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="963" spans="1:57" ht="15.95" customHeight="1">
       <c r="A963" s="4"/>
       <c r="B963" s="4"/>
       <c r="C963" s="4"/>
@@ -24985,7 +24991,7 @@
       <c r="BD963" s="4"/>
       <c r="BE963" s="4"/>
     </row>
-    <row r="964" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="964" spans="1:57" ht="15.95" customHeight="1">
       <c r="A964" s="4"/>
       <c r="B964" s="4"/>
       <c r="C964" s="4"/>
@@ -25009,7 +25015,7 @@
       <c r="BD964" s="4"/>
       <c r="BE964" s="4"/>
     </row>
-    <row r="965" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="965" spans="1:57" ht="15.95" customHeight="1">
       <c r="A965" s="4"/>
       <c r="B965" s="4"/>
       <c r="C965" s="4"/>
@@ -25033,7 +25039,7 @@
       <c r="BD965" s="4"/>
       <c r="BE965" s="4"/>
     </row>
-    <row r="966" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="966" spans="1:57" ht="15.95" customHeight="1">
       <c r="A966" s="4"/>
       <c r="B966" s="4"/>
       <c r="C966" s="4"/>
@@ -25057,7 +25063,7 @@
       <c r="BD966" s="4"/>
       <c r="BE966" s="4"/>
     </row>
-    <row r="967" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="967" spans="1:57" ht="15.95" customHeight="1">
       <c r="A967" s="4"/>
       <c r="B967" s="4"/>
       <c r="C967" s="4"/>
@@ -25081,7 +25087,7 @@
       <c r="BD967" s="4"/>
       <c r="BE967" s="4"/>
     </row>
-    <row r="968" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="968" spans="1:57" ht="15.95" customHeight="1">
       <c r="A968" s="4"/>
       <c r="B968" s="4"/>
       <c r="C968" s="4"/>
@@ -25105,7 +25111,7 @@
       <c r="BD968" s="4"/>
       <c r="BE968" s="4"/>
     </row>
-    <row r="969" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="969" spans="1:57" ht="15.95" customHeight="1">
       <c r="A969" s="4"/>
       <c r="B969" s="4"/>
       <c r="C969" s="4"/>
@@ -25129,7 +25135,7 @@
       <c r="BD969" s="4"/>
       <c r="BE969" s="4"/>
     </row>
-    <row r="970" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="970" spans="1:57" ht="15.95" customHeight="1">
       <c r="A970" s="4"/>
       <c r="B970" s="4"/>
       <c r="C970" s="4"/>
@@ -25153,7 +25159,7 @@
       <c r="BD970" s="4"/>
       <c r="BE970" s="4"/>
     </row>
-    <row r="971" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="971" spans="1:57" ht="15.95" customHeight="1">
       <c r="A971" s="4"/>
       <c r="B971" s="4"/>
       <c r="C971" s="4"/>
@@ -25177,7 +25183,7 @@
       <c r="BD971" s="4"/>
       <c r="BE971" s="4"/>
     </row>
-    <row r="972" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="972" spans="1:57" ht="15.95" customHeight="1">
       <c r="A972" s="4"/>
       <c r="B972" s="4"/>
       <c r="C972" s="4"/>
@@ -25201,7 +25207,7 @@
       <c r="BD972" s="4"/>
       <c r="BE972" s="4"/>
     </row>
-    <row r="973" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="973" spans="1:57" ht="15.95" customHeight="1">
       <c r="A973" s="4"/>
       <c r="B973" s="4"/>
       <c r="C973" s="4"/>
@@ -25225,7 +25231,7 @@
       <c r="BD973" s="4"/>
       <c r="BE973" s="4"/>
     </row>
-    <row r="974" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="974" spans="1:57" ht="15.95" customHeight="1">
       <c r="A974" s="4"/>
       <c r="B974" s="4"/>
       <c r="C974" s="4"/>
@@ -25249,7 +25255,7 @@
       <c r="BD974" s="4"/>
       <c r="BE974" s="4"/>
     </row>
-    <row r="975" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="975" spans="1:57" ht="15.95" customHeight="1">
       <c r="A975" s="4"/>
       <c r="B975" s="4"/>
       <c r="C975" s="4"/>
@@ -25273,7 +25279,7 @@
       <c r="BD975" s="4"/>
       <c r="BE975" s="4"/>
     </row>
-    <row r="976" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="976" spans="1:57" ht="15.95" customHeight="1">
       <c r="A976" s="4"/>
       <c r="B976" s="4"/>
       <c r="C976" s="4"/>
@@ -25297,7 +25303,7 @@
       <c r="BD976" s="4"/>
       <c r="BE976" s="4"/>
     </row>
-    <row r="977" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="977" spans="1:57" ht="15.95" customHeight="1">
       <c r="A977" s="4"/>
       <c r="B977" s="4"/>
       <c r="C977" s="4"/>
@@ -25321,7 +25327,7 @@
       <c r="BD977" s="4"/>
       <c r="BE977" s="4"/>
     </row>
-    <row r="978" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="978" spans="1:57" ht="15.95" customHeight="1">
       <c r="A978" s="4"/>
       <c r="B978" s="4"/>
       <c r="C978" s="4"/>
@@ -25345,7 +25351,7 @@
       <c r="BD978" s="4"/>
       <c r="BE978" s="4"/>
     </row>
-    <row r="979" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="979" spans="1:57" ht="15.95" customHeight="1">
       <c r="A979" s="4"/>
       <c r="B979" s="4"/>
       <c r="C979" s="4"/>
@@ -25369,7 +25375,7 @@
       <c r="BD979" s="4"/>
       <c r="BE979" s="4"/>
     </row>
-    <row r="980" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="980" spans="1:57" ht="15.95" customHeight="1">
       <c r="A980" s="4"/>
       <c r="B980" s="4"/>
       <c r="C980" s="4"/>
@@ -25393,7 +25399,7 @@
       <c r="BD980" s="4"/>
       <c r="BE980" s="4"/>
     </row>
-    <row r="981" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="981" spans="1:57" ht="15.95" customHeight="1">
       <c r="A981" s="4"/>
       <c r="B981" s="4"/>
       <c r="C981" s="4"/>
@@ -25417,7 +25423,7 @@
       <c r="BD981" s="4"/>
       <c r="BE981" s="4"/>
     </row>
-    <row r="982" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="982" spans="1:57" ht="15.95" customHeight="1">
       <c r="A982" s="4"/>
       <c r="B982" s="4"/>
       <c r="C982" s="4"/>
@@ -25441,7 +25447,7 @@
       <c r="BD982" s="4"/>
       <c r="BE982" s="4"/>
     </row>
-    <row r="983" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="983" spans="1:57" ht="15.95" customHeight="1">
       <c r="A983" s="4"/>
       <c r="B983" s="4"/>
       <c r="C983" s="4"/>
@@ -25465,7 +25471,7 @@
       <c r="BD983" s="4"/>
       <c r="BE983" s="4"/>
     </row>
-    <row r="984" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="984" spans="1:57" ht="15.95" customHeight="1">
       <c r="A984" s="4"/>
       <c r="B984" s="4"/>
       <c r="C984" s="4"/>
@@ -25489,7 +25495,7 @@
       <c r="BD984" s="4"/>
       <c r="BE984" s="4"/>
     </row>
-    <row r="985" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="985" spans="1:57" ht="15.95" customHeight="1">
       <c r="A985" s="4"/>
       <c r="B985" s="4"/>
       <c r="C985" s="4"/>
@@ -25513,7 +25519,7 @@
       <c r="BD985" s="4"/>
       <c r="BE985" s="4"/>
     </row>
-    <row r="986" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="986" spans="1:57" ht="15.95" customHeight="1">
       <c r="A986" s="4"/>
       <c r="B986" s="4"/>
       <c r="C986" s="4"/>
@@ -25537,7 +25543,7 @@
       <c r="BD986" s="4"/>
       <c r="BE986" s="4"/>
     </row>
-    <row r="987" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="987" spans="1:57" ht="15.95" customHeight="1">
       <c r="A987" s="4"/>
       <c r="B987" s="4"/>
       <c r="C987" s="4"/>
@@ -25561,7 +25567,7 @@
       <c r="BD987" s="4"/>
       <c r="BE987" s="4"/>
     </row>
-    <row r="988" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="988" spans="1:57" ht="15.95" customHeight="1">
       <c r="A988" s="4"/>
       <c r="B988" s="4"/>
       <c r="C988" s="4"/>
@@ -25585,7 +25591,7 @@
       <c r="BD988" s="4"/>
       <c r="BE988" s="4"/>
     </row>
-    <row r="989" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="989" spans="1:57" ht="15.95" customHeight="1">
       <c r="A989" s="4"/>
       <c r="B989" s="4"/>
       <c r="C989" s="4"/>
@@ -25609,7 +25615,7 @@
       <c r="BD989" s="4"/>
       <c r="BE989" s="4"/>
     </row>
-    <row r="990" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="990" spans="1:57" ht="15.95" customHeight="1">
       <c r="A990" s="4"/>
       <c r="B990" s="4"/>
       <c r="C990" s="4"/>
@@ -25633,7 +25639,7 @@
       <c r="BD990" s="4"/>
       <c r="BE990" s="4"/>
     </row>
-    <row r="991" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="991" spans="1:57" ht="15.95" customHeight="1">
       <c r="A991" s="4"/>
       <c r="B991" s="4"/>
       <c r="C991" s="4"/>
@@ -25657,7 +25663,7 @@
       <c r="BD991" s="4"/>
       <c r="BE991" s="4"/>
     </row>
-    <row r="992" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="992" spans="1:57" ht="15.95" customHeight="1">
       <c r="A992" s="4"/>
       <c r="B992" s="4"/>
       <c r="C992" s="4"/>
@@ -25681,7 +25687,7 @@
       <c r="BD992" s="4"/>
       <c r="BE992" s="4"/>
     </row>
-    <row r="993" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="993" spans="1:57" ht="15.95" customHeight="1">
       <c r="A993" s="4"/>
       <c r="B993" s="4"/>
       <c r="C993" s="4"/>
@@ -25705,7 +25711,7 @@
       <c r="BD993" s="4"/>
       <c r="BE993" s="4"/>
     </row>
-    <row r="994" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="994" spans="1:57" ht="15.95" customHeight="1">
       <c r="A994" s="4"/>
       <c r="B994" s="4"/>
       <c r="C994" s="4"/>
@@ -25729,7 +25735,7 @@
       <c r="BD994" s="4"/>
       <c r="BE994" s="4"/>
     </row>
-    <row r="995" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="995" spans="1:57" ht="15.95" customHeight="1">
       <c r="A995" s="4"/>
       <c r="B995" s="4"/>
       <c r="C995" s="4"/>
@@ -25753,7 +25759,7 @@
       <c r="BD995" s="4"/>
       <c r="BE995" s="4"/>
     </row>
-    <row r="996" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="996" spans="1:57" ht="15.95" customHeight="1">
       <c r="A996" s="4"/>
       <c r="B996" s="4"/>
       <c r="C996" s="4"/>
@@ -25777,7 +25783,7 @@
       <c r="BD996" s="4"/>
       <c r="BE996" s="4"/>
     </row>
-    <row r="997" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="997" spans="1:57" ht="15.95" customHeight="1">
       <c r="A997" s="4"/>
       <c r="B997" s="4"/>
       <c r="C997" s="4"/>
@@ -25801,7 +25807,7 @@
       <c r="BD997" s="4"/>
       <c r="BE997" s="4"/>
     </row>
-    <row r="998" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="998" spans="1:57" ht="15.95" customHeight="1">
       <c r="A998" s="4"/>
       <c r="B998" s="4"/>
       <c r="C998" s="4"/>
@@ -25825,7 +25831,7 @@
       <c r="BD998" s="4"/>
       <c r="BE998" s="4"/>
     </row>
-    <row r="999" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="999" spans="1:57" ht="15.95" customHeight="1">
       <c r="A999" s="4"/>
       <c r="B999" s="4"/>
       <c r="C999" s="4"/>
@@ -25849,7 +25855,7 @@
       <c r="BD999" s="4"/>
       <c r="BE999" s="4"/>
     </row>
-    <row r="1000" spans="1:57" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1000" spans="1:57" ht="15.95" customHeight="1">
       <c r="A1000" s="4"/>
       <c r="B1000" s="4"/>
       <c r="C1000" s="4"/>
@@ -25879,15 +25885,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100473DE4EA8FF5104F8456752DB619673A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e4fd7ef94a58df89505d05cd8f0789b1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="26f1519c-0a18-4175-bd8e-760b6597752e" xmlns:ns3="def454d3-7361-4a53-bd39-35a8c96a39c0" xmlns:ns4="06a0b0f5-ab3f-4382-8730-459fb424e421" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="14f03c0bfa8338aae8ff84ba27968e08" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -26144,6 +26141,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -26158,44 +26164,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D55B629F-9BAD-43E6-819F-B097A47F8C05}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7054DC5C-F1B5-45DA-8D63-B6556709A2A5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7054DC5C-F1B5-45DA-8D63-B6556709A2A5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="26f1519c-0a18-4175-bd8e-760b6597752e"/>
-    <ds:schemaRef ds:uri="def454d3-7361-4a53-bd39-35a8c96a39c0"/>
-    <ds:schemaRef ds:uri="06a0b0f5-ab3f-4382-8730-459fb424e421"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D55B629F-9BAD-43E6-819F-B097A47F8C05}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44B7B1D8-F3F2-46A8-A792-B679C78EEEEB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="06a0b0f5-ab3f-4382-8730-459fb424e421"/>
-    <ds:schemaRef ds:uri="26f1519c-0a18-4175-bd8e-760b6597752e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44B7B1D8-F3F2-46A8-A792-B679C78EEEEB}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
